--- a/Documents/Original/FlexChroma_site_map.xlsx
+++ b/Documents/Original/FlexChroma_site_map.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\j0814240\Documents\F-C\Git\FlexChroma\Documents\Original\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87B02260-2411-46CC-AB8B-64961011F21E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{398B0038-8815-4925-A18A-2378373F2D6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6120" yWindow="1695" windowWidth="21600" windowHeight="11295" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="構成" sheetId="5" r:id="rId1"/>
@@ -1273,10 +1273,6 @@
     <rPh sb="15" eb="16">
       <t>ア</t>
     </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Model (Bland)</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -1414,6 +1410,10 @@
       <t xml:space="preserve">
 (Web site)</t>
     </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Model (Brand)</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -3137,16 +3137,158 @@
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="93" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="12" fillId="6" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="12" fillId="6" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="12" fillId="6" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="12" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="12" fillId="6" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="12" fillId="6" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="12" fillId="6" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="12" fillId="6" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="12" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="12" fillId="6" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="19" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="92" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3155,6 +3297,39 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="50" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="52" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="53" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="46" fontId="2" fillId="2" borderId="20" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="46" fontId="2" fillId="2" borderId="22" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="46" fontId="2" fillId="2" borderId="21" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="49" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="51" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3164,34 +3339,43 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="49" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="51" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="46" fontId="2" fillId="2" borderId="20" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="46" fontId="2" fillId="2" borderId="22" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="46" fontId="2" fillId="2" borderId="21" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="52" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="53" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="20" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="22" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="89" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="21" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="90" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="91" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3209,154 +3393,199 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="20" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="22" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="21" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="90" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="91" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="89" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="90" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="91" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="89" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="67" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="58" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="76" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="77" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="78" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="79" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="65" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="74" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="61" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="75" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="64" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="57" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="66" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="60" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="59" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="29" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="30" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="32" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="44" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="45" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="35" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="37" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="70" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="40" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="68" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="69" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="73" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="62" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="63" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="72" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="60" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="80" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="82" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="83" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="86" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="81" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="87" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="84" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="88" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="85" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="23" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="24" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="25" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="26" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="27" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="28" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="36" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="38" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="34" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -3368,21 +3597,18 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="36" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="38" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="64" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="65" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="40" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="41" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="42" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3392,323 +3618,97 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="71" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="35" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="37" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="57" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="61" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="39" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="34" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="26" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="27" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="28" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="29" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="30" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="32" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="44" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="45" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="23" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="24" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="25" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="93" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="12" fillId="6" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="12" fillId="6" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="89" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="12" fillId="6" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="12" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="12" fillId="6" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="12" fillId="6" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="12" fillId="6" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="12" fillId="6" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="12" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="90" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="91" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="12" fillId="6" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="19" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="92" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="67" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="58" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="87" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="84" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="88" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="85" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="68" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="69" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="73" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="62" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="63" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="66" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="72" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="60" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="80" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="82" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="83" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="78" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="86" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="81" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="70" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="74" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="75" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="60" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="59" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="76" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="77" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="79" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -6689,16 +6689,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>219807</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>175846</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>373673</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>65942</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>109904</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>21982</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>630116</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6728,7 +6728,7 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="4454769" y="271096"/>
+          <a:off x="7041173" y="65942"/>
           <a:ext cx="6455020" cy="1436078"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -9975,22 +9975,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>66675</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>24</xdr:col>
-      <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>409575</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="28" name="図 27">
+        <xdr:cNvPr id="22" name="図 21">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9009135B-488D-18AD-33EE-2B2CFDC8097A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{31322046-DA05-E453-193E-B1947F2711C9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10013,7 +10013,7 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="8782050" y="7191375"/>
+          <a:off x="8848725" y="7143750"/>
           <a:ext cx="8353425" cy="1304925"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -10036,22 +10036,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>28575</xdr:colOff>
+      <xdr:colOff>180975</xdr:colOff>
       <xdr:row>40</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>24</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
+      <xdr:colOff>190500</xdr:colOff>
       <xdr:row>46</xdr:row>
       <xdr:rowOff>19050</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="29" name="図 28">
+        <xdr:cNvPr id="26" name="図 25">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{76986F67-8385-9975-4B3A-7A2976A9F576}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{65EBD496-4320-F95D-E4F6-46AE1204BBFD}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10074,7 +10074,7 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="8810625" y="8953500"/>
+          <a:off x="8963025" y="8953500"/>
           <a:ext cx="8353425" cy="1362075"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -11194,6 +11194,12 @@
         <a:prstGeom prst="roundRect">
           <a:avLst/>
         </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="3">
@@ -11233,22 +11239,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>364436</xdr:colOff>
+      <xdr:colOff>248479</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>107674</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>393010</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>143704</xdr:rowOff>
+      <xdr:colOff>99392</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>74543</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="図 3">
+        <xdr:cNvPr id="5" name="図 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3CA4C0E2-35C7-1340-C094-C4C5C416A183}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E88CF679-D4EB-1576-C474-F6F819FAB477}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -11256,7 +11262,7 @@
           <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
-      <xdr:blipFill>
+      <xdr:blipFill rotWithShape="1">
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
@@ -11264,15 +11270,15 @@
             </a:ext>
           </a:extLst>
         </a:blip>
-        <a:srcRect/>
+        <a:srcRect l="1200" t="1362" r="1373" b="1593"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="7255566" y="314739"/>
-          <a:ext cx="6903140" cy="4864791"/>
+          <a:off x="7139609" y="207065"/>
+          <a:ext cx="6725479" cy="4721087"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -11835,16 +11841,16 @@
     </row>
     <row r="4" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="3"/>
-      <c r="B4" s="92" t="s">
+      <c r="B4" s="146" t="s">
         <v>183</v>
       </c>
-      <c r="C4" s="83" t="s">
+      <c r="C4" s="137" t="s">
         <v>26</v>
       </c>
-      <c r="D4" s="83" t="s">
+      <c r="D4" s="137" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="84" t="s">
+      <c r="E4" s="145" t="s">
         <v>35</v>
       </c>
       <c r="F4" s="7">
@@ -11854,10 +11860,10 @@
     </row>
     <row r="5" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="3"/>
-      <c r="B5" s="92"/>
-      <c r="C5" s="83"/>
-      <c r="D5" s="83"/>
-      <c r="E5" s="85"/>
+      <c r="B5" s="146"/>
+      <c r="C5" s="137"/>
+      <c r="D5" s="137"/>
+      <c r="E5" s="141"/>
       <c r="F5" s="8">
         <v>0.55000000000000004</v>
       </c>
@@ -11865,10 +11871,10 @@
     </row>
     <row r="6" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="3"/>
-      <c r="B6" s="92"/>
-      <c r="C6" s="83"/>
-      <c r="D6" s="83"/>
-      <c r="E6" s="85"/>
+      <c r="B6" s="146"/>
+      <c r="C6" s="137"/>
+      <c r="D6" s="137"/>
+      <c r="E6" s="141"/>
       <c r="F6" s="8">
         <v>0.6</v>
       </c>
@@ -11876,10 +11882,10 @@
     </row>
     <row r="7" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="3"/>
-      <c r="B7" s="92"/>
-      <c r="C7" s="83"/>
-      <c r="D7" s="83"/>
-      <c r="E7" s="86"/>
+      <c r="B7" s="146"/>
+      <c r="C7" s="137"/>
+      <c r="D7" s="137"/>
+      <c r="E7" s="142"/>
       <c r="F7" s="9">
         <v>0.56000000000000005</v>
       </c>
@@ -11887,10 +11893,10 @@
     </row>
     <row r="8" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="3"/>
-      <c r="B8" s="92"/>
-      <c r="C8" s="83"/>
-      <c r="D8" s="83"/>
-      <c r="E8" s="84" t="s">
+      <c r="B8" s="146"/>
+      <c r="C8" s="137"/>
+      <c r="D8" s="137"/>
+      <c r="E8" s="145" t="s">
         <v>36</v>
       </c>
       <c r="F8" s="7">
@@ -11900,10 +11906,10 @@
     </row>
     <row r="9" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="3"/>
-      <c r="B9" s="92"/>
-      <c r="C9" s="83"/>
-      <c r="D9" s="83"/>
-      <c r="E9" s="85"/>
+      <c r="B9" s="146"/>
+      <c r="C9" s="137"/>
+      <c r="D9" s="137"/>
+      <c r="E9" s="141"/>
       <c r="F9" s="8">
         <v>0.75</v>
       </c>
@@ -11911,10 +11917,10 @@
     </row>
     <row r="10" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="3"/>
-      <c r="B10" s="92"/>
-      <c r="C10" s="83"/>
-      <c r="D10" s="83"/>
-      <c r="E10" s="85"/>
+      <c r="B10" s="146"/>
+      <c r="C10" s="137"/>
+      <c r="D10" s="137"/>
+      <c r="E10" s="141"/>
       <c r="F10" s="8">
         <v>0.8</v>
       </c>
@@ -11922,10 +11928,10 @@
     </row>
     <row r="11" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="3"/>
-      <c r="B11" s="92"/>
-      <c r="C11" s="83"/>
-      <c r="D11" s="83"/>
-      <c r="E11" s="85"/>
+      <c r="B11" s="146"/>
+      <c r="C11" s="137"/>
+      <c r="D11" s="137"/>
+      <c r="E11" s="141"/>
       <c r="F11" s="8">
         <v>0.85</v>
       </c>
@@ -11933,10 +11939,10 @@
     </row>
     <row r="12" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="3"/>
-      <c r="B12" s="92"/>
-      <c r="C12" s="83"/>
-      <c r="D12" s="83"/>
-      <c r="E12" s="85"/>
+      <c r="B12" s="146"/>
+      <c r="C12" s="137"/>
+      <c r="D12" s="137"/>
+      <c r="E12" s="141"/>
       <c r="F12" s="8">
         <v>0.9</v>
       </c>
@@ -11944,10 +11950,10 @@
     </row>
     <row r="13" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="3"/>
-      <c r="B13" s="92"/>
-      <c r="C13" s="83"/>
-      <c r="D13" s="83"/>
-      <c r="E13" s="86"/>
+      <c r="B13" s="146"/>
+      <c r="C13" s="137"/>
+      <c r="D13" s="137"/>
+      <c r="E13" s="142"/>
       <c r="F13" s="9">
         <v>0.95</v>
       </c>
@@ -11955,10 +11961,10 @@
     </row>
     <row r="14" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="3"/>
-      <c r="B14" s="92"/>
-      <c r="C14" s="83"/>
-      <c r="D14" s="83"/>
-      <c r="E14" s="84" t="s">
+      <c r="B14" s="146"/>
+      <c r="C14" s="137"/>
+      <c r="D14" s="137"/>
+      <c r="E14" s="145" t="s">
         <v>37</v>
       </c>
       <c r="F14" s="7">
@@ -11968,10 +11974,10 @@
     </row>
     <row r="15" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="3"/>
-      <c r="B15" s="92"/>
-      <c r="C15" s="83"/>
-      <c r="D15" s="83"/>
-      <c r="E15" s="85"/>
+      <c r="B15" s="146"/>
+      <c r="C15" s="137"/>
+      <c r="D15" s="137"/>
+      <c r="E15" s="141"/>
       <c r="F15" s="10">
         <v>0.92500000000000004</v>
       </c>
@@ -11979,10 +11985,10 @@
     </row>
     <row r="16" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="3"/>
-      <c r="B16" s="92"/>
-      <c r="C16" s="83"/>
-      <c r="D16" s="83"/>
-      <c r="E16" s="85"/>
+      <c r="B16" s="146"/>
+      <c r="C16" s="137"/>
+      <c r="D16" s="137"/>
+      <c r="E16" s="141"/>
       <c r="F16" s="8">
         <v>0.95</v>
       </c>
@@ -11990,10 +11996,10 @@
     </row>
     <row r="17" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="3"/>
-      <c r="B17" s="92"/>
-      <c r="C17" s="83"/>
-      <c r="D17" s="83"/>
-      <c r="E17" s="85"/>
+      <c r="B17" s="146"/>
+      <c r="C17" s="137"/>
+      <c r="D17" s="137"/>
+      <c r="E17" s="141"/>
       <c r="F17" s="8">
         <v>0.96</v>
       </c>
@@ -12001,10 +12007,10 @@
     </row>
     <row r="18" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="3"/>
-      <c r="B18" s="92"/>
-      <c r="C18" s="83"/>
-      <c r="D18" s="83"/>
-      <c r="E18" s="85"/>
+      <c r="B18" s="146"/>
+      <c r="C18" s="137"/>
+      <c r="D18" s="137"/>
+      <c r="E18" s="141"/>
       <c r="F18" s="8">
         <v>0.97</v>
       </c>
@@ -12012,10 +12018,10 @@
     </row>
     <row r="19" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="3"/>
-      <c r="B19" s="92"/>
-      <c r="C19" s="83"/>
-      <c r="D19" s="83"/>
-      <c r="E19" s="85"/>
+      <c r="B19" s="146"/>
+      <c r="C19" s="137"/>
+      <c r="D19" s="137"/>
+      <c r="E19" s="141"/>
       <c r="F19" s="8">
         <v>0.98</v>
       </c>
@@ -12023,10 +12029,10 @@
     </row>
     <row r="20" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="3"/>
-      <c r="B20" s="92"/>
-      <c r="C20" s="83"/>
-      <c r="D20" s="83"/>
-      <c r="E20" s="85"/>
+      <c r="B20" s="146"/>
+      <c r="C20" s="137"/>
+      <c r="D20" s="137"/>
+      <c r="E20" s="141"/>
       <c r="F20" s="10">
         <v>0.98499999999999999</v>
       </c>
@@ -12034,10 +12040,10 @@
     </row>
     <row r="21" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="3"/>
-      <c r="B21" s="92"/>
-      <c r="C21" s="83"/>
-      <c r="D21" s="83"/>
-      <c r="E21" s="85"/>
+      <c r="B21" s="146"/>
+      <c r="C21" s="137"/>
+      <c r="D21" s="137"/>
+      <c r="E21" s="141"/>
       <c r="F21" s="8">
         <v>0.99</v>
       </c>
@@ -12045,10 +12051,10 @@
     </row>
     <row r="22" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="3"/>
-      <c r="B22" s="92"/>
-      <c r="C22" s="83"/>
-      <c r="D22" s="83"/>
-      <c r="E22" s="86"/>
+      <c r="B22" s="146"/>
+      <c r="C22" s="137"/>
+      <c r="D22" s="137"/>
+      <c r="E22" s="142"/>
       <c r="F22" s="11">
         <v>0.995</v>
       </c>
@@ -12056,93 +12062,93 @@
     </row>
     <row r="23" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="3"/>
-      <c r="B23" s="92"/>
-      <c r="C23" s="83"/>
+      <c r="B23" s="146"/>
+      <c r="C23" s="137"/>
       <c r="D23" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E23" s="87" t="s">
+      <c r="E23" s="135" t="s">
         <v>11</v>
       </c>
-      <c r="F23" s="88"/>
+      <c r="F23" s="136"/>
       <c r="G23" s="3"/>
     </row>
     <row r="24" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="3"/>
-      <c r="B24" s="92"/>
-      <c r="C24" s="83"/>
+      <c r="B24" s="146"/>
+      <c r="C24" s="137"/>
       <c r="D24" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E24" s="83"/>
-      <c r="F24" s="88"/>
+      <c r="E24" s="137"/>
+      <c r="F24" s="136"/>
       <c r="G24" s="3"/>
     </row>
     <row r="25" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="3"/>
-      <c r="B25" s="92"/>
-      <c r="C25" s="83"/>
+      <c r="B25" s="146"/>
+      <c r="C25" s="137"/>
       <c r="D25" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E25" s="83"/>
-      <c r="F25" s="88"/>
+      <c r="E25" s="137"/>
+      <c r="F25" s="136"/>
       <c r="G25" s="3"/>
     </row>
     <row r="26" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="3"/>
-      <c r="B26" s="92"/>
-      <c r="C26" s="83"/>
+      <c r="B26" s="146"/>
+      <c r="C26" s="137"/>
       <c r="D26" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E26" s="83"/>
-      <c r="F26" s="88"/>
+      <c r="E26" s="137"/>
+      <c r="F26" s="136"/>
       <c r="G26" s="3"/>
     </row>
     <row r="27" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="3"/>
-      <c r="B27" s="92"/>
-      <c r="C27" s="83"/>
+      <c r="B27" s="146"/>
+      <c r="C27" s="137"/>
       <c r="D27" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="E27" s="83"/>
-      <c r="F27" s="88"/>
+      <c r="E27" s="137"/>
+      <c r="F27" s="136"/>
       <c r="G27" s="3"/>
     </row>
     <row r="28" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="3"/>
-      <c r="B28" s="92"/>
-      <c r="C28" s="83"/>
+      <c r="B28" s="146"/>
+      <c r="C28" s="137"/>
       <c r="D28" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="E28" s="83"/>
-      <c r="F28" s="88"/>
+      <c r="E28" s="137"/>
+      <c r="F28" s="136"/>
       <c r="G28" s="3"/>
     </row>
     <row r="29" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="3"/>
-      <c r="B29" s="92"/>
-      <c r="C29" s="83"/>
+      <c r="B29" s="146"/>
+      <c r="C29" s="137"/>
       <c r="D29" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="E29" s="83"/>
-      <c r="F29" s="88"/>
+      <c r="E29" s="137"/>
+      <c r="F29" s="136"/>
       <c r="G29" s="3"/>
     </row>
     <row r="30" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="3"/>
-      <c r="B30" s="92"/>
-      <c r="C30" s="83" t="s">
+      <c r="B30" s="146"/>
+      <c r="C30" s="137" t="s">
         <v>0</v>
       </c>
-      <c r="D30" s="83" t="s">
+      <c r="D30" s="137" t="s">
         <v>1</v>
       </c>
-      <c r="E30" s="84" t="s">
+      <c r="E30" s="145" t="s">
         <v>2</v>
       </c>
       <c r="F30" s="12" t="s">
@@ -12152,10 +12158,10 @@
     </row>
     <row r="31" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="3"/>
-      <c r="B31" s="92"/>
-      <c r="C31" s="83"/>
-      <c r="D31" s="83"/>
-      <c r="E31" s="85"/>
+      <c r="B31" s="146"/>
+      <c r="C31" s="137"/>
+      <c r="D31" s="137"/>
+      <c r="E31" s="141"/>
       <c r="F31" s="13" t="s">
         <v>4</v>
       </c>
@@ -12163,10 +12169,10 @@
     </row>
     <row r="32" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="3"/>
-      <c r="B32" s="92"/>
-      <c r="C32" s="83"/>
-      <c r="D32" s="83"/>
-      <c r="E32" s="85"/>
+      <c r="B32" s="146"/>
+      <c r="C32" s="137"/>
+      <c r="D32" s="137"/>
+      <c r="E32" s="141"/>
       <c r="F32" s="13" t="s">
         <v>5</v>
       </c>
@@ -12174,10 +12180,10 @@
     </row>
     <row r="33" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="3"/>
-      <c r="B33" s="92"/>
-      <c r="C33" s="83"/>
-      <c r="D33" s="83"/>
-      <c r="E33" s="86"/>
+      <c r="B33" s="146"/>
+      <c r="C33" s="137"/>
+      <c r="D33" s="137"/>
+      <c r="E33" s="142"/>
       <c r="F33" s="14" t="s">
         <v>6</v>
       </c>
@@ -12185,10 +12191,10 @@
     </row>
     <row r="34" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="3"/>
-      <c r="B34" s="92"/>
-      <c r="C34" s="83"/>
-      <c r="D34" s="83"/>
-      <c r="E34" s="84" t="s">
+      <c r="B34" s="146"/>
+      <c r="C34" s="137"/>
+      <c r="D34" s="137"/>
+      <c r="E34" s="145" t="s">
         <v>7</v>
       </c>
       <c r="F34" s="12" t="s">
@@ -12198,10 +12204,10 @@
     </row>
     <row r="35" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="3"/>
-      <c r="B35" s="92"/>
-      <c r="C35" s="83"/>
-      <c r="D35" s="83"/>
-      <c r="E35" s="85"/>
+      <c r="B35" s="146"/>
+      <c r="C35" s="137"/>
+      <c r="D35" s="137"/>
+      <c r="E35" s="141"/>
       <c r="F35" s="13" t="s">
         <v>4</v>
       </c>
@@ -12209,10 +12215,10 @@
     </row>
     <row r="36" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="3"/>
-      <c r="B36" s="92"/>
-      <c r="C36" s="83"/>
-      <c r="D36" s="83"/>
-      <c r="E36" s="85"/>
+      <c r="B36" s="146"/>
+      <c r="C36" s="137"/>
+      <c r="D36" s="137"/>
+      <c r="E36" s="141"/>
       <c r="F36" s="13" t="s">
         <v>5</v>
       </c>
@@ -12220,10 +12226,10 @@
     </row>
     <row r="37" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="3"/>
-      <c r="B37" s="92"/>
-      <c r="C37" s="83"/>
-      <c r="D37" s="83"/>
-      <c r="E37" s="86"/>
+      <c r="B37" s="146"/>
+      <c r="C37" s="137"/>
+      <c r="D37" s="137"/>
+      <c r="E37" s="142"/>
       <c r="F37" s="14" t="s">
         <v>6</v>
       </c>
@@ -12231,10 +12237,10 @@
     </row>
     <row r="38" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="3"/>
-      <c r="B38" s="92"/>
-      <c r="C38" s="83"/>
-      <c r="D38" s="83"/>
-      <c r="E38" s="84" t="s">
+      <c r="B38" s="146"/>
+      <c r="C38" s="137"/>
+      <c r="D38" s="137"/>
+      <c r="E38" s="145" t="s">
         <v>8</v>
       </c>
       <c r="F38" s="12" t="s">
@@ -12244,10 +12250,10 @@
     </row>
     <row r="39" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="3"/>
-      <c r="B39" s="92"/>
-      <c r="C39" s="83"/>
-      <c r="D39" s="83"/>
-      <c r="E39" s="85"/>
+      <c r="B39" s="146"/>
+      <c r="C39" s="137"/>
+      <c r="D39" s="137"/>
+      <c r="E39" s="141"/>
       <c r="F39" s="13" t="s">
         <v>4</v>
       </c>
@@ -12255,10 +12261,10 @@
     </row>
     <row r="40" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="3"/>
-      <c r="B40" s="92"/>
-      <c r="C40" s="83"/>
-      <c r="D40" s="83"/>
-      <c r="E40" s="85"/>
+      <c r="B40" s="146"/>
+      <c r="C40" s="137"/>
+      <c r="D40" s="137"/>
+      <c r="E40" s="141"/>
       <c r="F40" s="13" t="s">
         <v>5</v>
       </c>
@@ -12266,10 +12272,10 @@
     </row>
     <row r="41" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="3"/>
-      <c r="B41" s="92"/>
-      <c r="C41" s="83"/>
-      <c r="D41" s="83"/>
-      <c r="E41" s="86"/>
+      <c r="B41" s="146"/>
+      <c r="C41" s="137"/>
+      <c r="D41" s="137"/>
+      <c r="E41" s="142"/>
       <c r="F41" s="14" t="s">
         <v>6</v>
       </c>
@@ -12277,10 +12283,10 @@
     </row>
     <row r="42" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="3"/>
-      <c r="B42" s="92"/>
-      <c r="C42" s="83"/>
-      <c r="D42" s="83"/>
-      <c r="E42" s="84" t="s">
+      <c r="B42" s="146"/>
+      <c r="C42" s="137"/>
+      <c r="D42" s="137"/>
+      <c r="E42" s="145" t="s">
         <v>9</v>
       </c>
       <c r="F42" s="12" t="s">
@@ -12290,10 +12296,10 @@
     </row>
     <row r="43" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="3"/>
-      <c r="B43" s="92"/>
-      <c r="C43" s="83"/>
-      <c r="D43" s="83"/>
-      <c r="E43" s="85"/>
+      <c r="B43" s="146"/>
+      <c r="C43" s="137"/>
+      <c r="D43" s="137"/>
+      <c r="E43" s="141"/>
       <c r="F43" s="13" t="s">
         <v>4</v>
       </c>
@@ -12301,10 +12307,10 @@
     </row>
     <row r="44" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="3"/>
-      <c r="B44" s="92"/>
-      <c r="C44" s="83"/>
-      <c r="D44" s="83"/>
-      <c r="E44" s="85"/>
+      <c r="B44" s="146"/>
+      <c r="C44" s="137"/>
+      <c r="D44" s="137"/>
+      <c r="E44" s="141"/>
       <c r="F44" s="13" t="s">
         <v>5</v>
       </c>
@@ -12312,10 +12318,10 @@
     </row>
     <row r="45" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="3"/>
-      <c r="B45" s="92"/>
-      <c r="C45" s="83"/>
-      <c r="D45" s="83"/>
-      <c r="E45" s="86"/>
+      <c r="B45" s="146"/>
+      <c r="C45" s="137"/>
+      <c r="D45" s="137"/>
+      <c r="E45" s="142"/>
       <c r="F45" s="14" t="s">
         <v>6</v>
       </c>
@@ -12323,93 +12329,93 @@
     </row>
     <row r="46" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="3"/>
-      <c r="B46" s="92"/>
-      <c r="C46" s="83"/>
+      <c r="B46" s="146"/>
+      <c r="C46" s="137"/>
       <c r="D46" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E46" s="87" t="s">
+      <c r="E46" s="135" t="s">
         <v>11</v>
       </c>
-      <c r="F46" s="88"/>
+      <c r="F46" s="136"/>
       <c r="G46" s="3"/>
     </row>
     <row r="47" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="3"/>
-      <c r="B47" s="92"/>
-      <c r="C47" s="83"/>
+      <c r="B47" s="146"/>
+      <c r="C47" s="137"/>
       <c r="D47" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E47" s="83"/>
-      <c r="F47" s="88"/>
+      <c r="E47" s="137"/>
+      <c r="F47" s="136"/>
       <c r="G47" s="3"/>
     </row>
     <row r="48" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="3"/>
-      <c r="B48" s="92"/>
-      <c r="C48" s="83"/>
+      <c r="B48" s="146"/>
+      <c r="C48" s="137"/>
       <c r="D48" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E48" s="83"/>
-      <c r="F48" s="88"/>
+      <c r="E48" s="137"/>
+      <c r="F48" s="136"/>
       <c r="G48" s="3"/>
     </row>
     <row r="49" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="3"/>
-      <c r="B49" s="92"/>
-      <c r="C49" s="83"/>
+      <c r="B49" s="146"/>
+      <c r="C49" s="137"/>
       <c r="D49" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E49" s="83"/>
-      <c r="F49" s="88"/>
+      <c r="E49" s="137"/>
+      <c r="F49" s="136"/>
       <c r="G49" s="3"/>
     </row>
     <row r="50" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="3"/>
-      <c r="B50" s="92"/>
-      <c r="C50" s="83"/>
+      <c r="B50" s="146"/>
+      <c r="C50" s="137"/>
       <c r="D50" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E50" s="83"/>
-      <c r="F50" s="88"/>
+      <c r="E50" s="137"/>
+      <c r="F50" s="136"/>
       <c r="G50" s="3"/>
     </row>
     <row r="51" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="3"/>
-      <c r="B51" s="92"/>
-      <c r="C51" s="83"/>
+      <c r="B51" s="146"/>
+      <c r="C51" s="137"/>
       <c r="D51" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E51" s="83"/>
-      <c r="F51" s="88"/>
+      <c r="E51" s="137"/>
+      <c r="F51" s="136"/>
       <c r="G51" s="3"/>
     </row>
     <row r="52" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="3"/>
-      <c r="B52" s="92"/>
-      <c r="C52" s="83"/>
+      <c r="B52" s="146"/>
+      <c r="C52" s="137"/>
       <c r="D52" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E52" s="83"/>
-      <c r="F52" s="88"/>
+      <c r="E52" s="137"/>
+      <c r="F52" s="136"/>
       <c r="G52" s="3"/>
     </row>
     <row r="53" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="3"/>
-      <c r="B53" s="92"/>
-      <c r="C53" s="83" t="s">
+      <c r="B53" s="146"/>
+      <c r="C53" s="137" t="s">
         <v>55</v>
       </c>
-      <c r="D53" s="83" t="s">
+      <c r="D53" s="137" t="s">
         <v>56</v>
       </c>
-      <c r="E53" s="94" t="s">
+      <c r="E53" s="140" t="s">
         <v>102</v>
       </c>
       <c r="F53" s="7" t="s">
@@ -12419,10 +12425,10 @@
     </row>
     <row r="54" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="3"/>
-      <c r="B54" s="92"/>
-      <c r="C54" s="83"/>
-      <c r="D54" s="83"/>
-      <c r="E54" s="85"/>
+      <c r="B54" s="146"/>
+      <c r="C54" s="137"/>
+      <c r="D54" s="137"/>
+      <c r="E54" s="141"/>
       <c r="F54" s="8" t="s">
         <v>41</v>
       </c>
@@ -12430,10 +12436,10 @@
     </row>
     <row r="55" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="3"/>
-      <c r="B55" s="92"/>
-      <c r="C55" s="83"/>
-      <c r="D55" s="83"/>
-      <c r="E55" s="85"/>
+      <c r="B55" s="146"/>
+      <c r="C55" s="137"/>
+      <c r="D55" s="137"/>
+      <c r="E55" s="141"/>
       <c r="F55" s="8" t="s">
         <v>38</v>
       </c>
@@ -12441,10 +12447,10 @@
     </row>
     <row r="56" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="3"/>
-      <c r="B56" s="92"/>
-      <c r="C56" s="83"/>
-      <c r="D56" s="83"/>
-      <c r="E56" s="86"/>
+      <c r="B56" s="146"/>
+      <c r="C56" s="137"/>
+      <c r="D56" s="137"/>
+      <c r="E56" s="142"/>
       <c r="F56" s="9" t="s">
         <v>103</v>
       </c>
@@ -12452,10 +12458,10 @@
     </row>
     <row r="57" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="3"/>
-      <c r="B57" s="92"/>
-      <c r="C57" s="83"/>
-      <c r="D57" s="83"/>
-      <c r="E57" s="94" t="s">
+      <c r="B57" s="146"/>
+      <c r="C57" s="137"/>
+      <c r="D57" s="137"/>
+      <c r="E57" s="140" t="s">
         <v>105</v>
       </c>
       <c r="F57" s="7" t="s">
@@ -12465,10 +12471,10 @@
     </row>
     <row r="58" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="3"/>
-      <c r="B58" s="92"/>
-      <c r="C58" s="83"/>
-      <c r="D58" s="83"/>
-      <c r="E58" s="85"/>
+      <c r="B58" s="146"/>
+      <c r="C58" s="137"/>
+      <c r="D58" s="137"/>
+      <c r="E58" s="141"/>
       <c r="F58" s="8" t="s">
         <v>42</v>
       </c>
@@ -12476,10 +12482,10 @@
     </row>
     <row r="59" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="3"/>
-      <c r="B59" s="92"/>
-      <c r="C59" s="83"/>
-      <c r="D59" s="83"/>
-      <c r="E59" s="85"/>
+      <c r="B59" s="146"/>
+      <c r="C59" s="137"/>
+      <c r="D59" s="137"/>
+      <c r="E59" s="141"/>
       <c r="F59" s="8" t="s">
         <v>39</v>
       </c>
@@ -12487,10 +12493,10 @@
     </row>
     <row r="60" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="3"/>
-      <c r="B60" s="92"/>
-      <c r="C60" s="83"/>
-      <c r="D60" s="83"/>
-      <c r="E60" s="86"/>
+      <c r="B60" s="146"/>
+      <c r="C60" s="137"/>
+      <c r="D60" s="137"/>
+      <c r="E60" s="142"/>
       <c r="F60" s="9" t="s">
         <v>106</v>
       </c>
@@ -12498,10 +12504,10 @@
     </row>
     <row r="61" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="3"/>
-      <c r="B61" s="92"/>
-      <c r="C61" s="83"/>
-      <c r="D61" s="83"/>
-      <c r="E61" s="94" t="s">
+      <c r="B61" s="146"/>
+      <c r="C61" s="137"/>
+      <c r="D61" s="137"/>
+      <c r="E61" s="140" t="s">
         <v>108</v>
       </c>
       <c r="F61" s="7" t="s">
@@ -12511,10 +12517,10 @@
     </row>
     <row r="62" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="3"/>
-      <c r="B62" s="92"/>
-      <c r="C62" s="83"/>
-      <c r="D62" s="83"/>
-      <c r="E62" s="85"/>
+      <c r="B62" s="146"/>
+      <c r="C62" s="137"/>
+      <c r="D62" s="137"/>
+      <c r="E62" s="141"/>
       <c r="F62" s="8" t="s">
         <v>43</v>
       </c>
@@ -12522,10 +12528,10 @@
     </row>
     <row r="63" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="3"/>
-      <c r="B63" s="92"/>
-      <c r="C63" s="83"/>
-      <c r="D63" s="83"/>
-      <c r="E63" s="85"/>
+      <c r="B63" s="146"/>
+      <c r="C63" s="137"/>
+      <c r="D63" s="137"/>
+      <c r="E63" s="141"/>
       <c r="F63" s="8" t="s">
         <v>40</v>
       </c>
@@ -12533,10 +12539,10 @@
     </row>
     <row r="64" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="3"/>
-      <c r="B64" s="92"/>
-      <c r="C64" s="83"/>
-      <c r="D64" s="83"/>
-      <c r="E64" s="86"/>
+      <c r="B64" s="146"/>
+      <c r="C64" s="137"/>
+      <c r="D64" s="137"/>
+      <c r="E64" s="142"/>
       <c r="F64" s="9" t="s">
         <v>110</v>
       </c>
@@ -12544,10 +12550,10 @@
     </row>
     <row r="65" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="3"/>
-      <c r="B65" s="92"/>
-      <c r="C65" s="83"/>
-      <c r="D65" s="83"/>
-      <c r="E65" s="94" t="s">
+      <c r="B65" s="146"/>
+      <c r="C65" s="137"/>
+      <c r="D65" s="137"/>
+      <c r="E65" s="140" t="s">
         <v>128</v>
       </c>
       <c r="F65" s="7" t="s">
@@ -12557,10 +12563,10 @@
     </row>
     <row r="66" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="3"/>
-      <c r="B66" s="92"/>
-      <c r="C66" s="83"/>
-      <c r="D66" s="83"/>
-      <c r="E66" s="85"/>
+      <c r="B66" s="146"/>
+      <c r="C66" s="137"/>
+      <c r="D66" s="137"/>
+      <c r="E66" s="141"/>
       <c r="F66" s="8" t="s">
         <v>44</v>
       </c>
@@ -12568,10 +12574,10 @@
     </row>
     <row r="67" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" s="3"/>
-      <c r="B67" s="92"/>
-      <c r="C67" s="83"/>
-      <c r="D67" s="83"/>
-      <c r="E67" s="85"/>
+      <c r="B67" s="146"/>
+      <c r="C67" s="137"/>
+      <c r="D67" s="137"/>
+      <c r="E67" s="141"/>
       <c r="F67" s="8" t="s">
         <v>46</v>
       </c>
@@ -12579,10 +12585,10 @@
     </row>
     <row r="68" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="3"/>
-      <c r="B68" s="92"/>
-      <c r="C68" s="83"/>
-      <c r="D68" s="83"/>
-      <c r="E68" s="86"/>
+      <c r="B68" s="146"/>
+      <c r="C68" s="137"/>
+      <c r="D68" s="137"/>
+      <c r="E68" s="142"/>
       <c r="F68" s="9" t="s">
         <v>123</v>
       </c>
@@ -12590,10 +12596,10 @@
     </row>
     <row r="69" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69" s="3"/>
-      <c r="B69" s="92"/>
-      <c r="C69" s="83"/>
-      <c r="D69" s="83"/>
-      <c r="E69" s="94" t="s">
+      <c r="B69" s="146"/>
+      <c r="C69" s="137"/>
+      <c r="D69" s="137"/>
+      <c r="E69" s="140" t="s">
         <v>130</v>
       </c>
       <c r="F69" s="7" t="s">
@@ -12603,10 +12609,10 @@
     </row>
     <row r="70" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="3"/>
-      <c r="B70" s="92"/>
-      <c r="C70" s="83"/>
-      <c r="D70" s="83"/>
-      <c r="E70" s="85"/>
+      <c r="B70" s="146"/>
+      <c r="C70" s="137"/>
+      <c r="D70" s="137"/>
+      <c r="E70" s="141"/>
       <c r="F70" s="8" t="s">
         <v>45</v>
       </c>
@@ -12614,10 +12620,10 @@
     </row>
     <row r="71" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A71" s="3"/>
-      <c r="B71" s="92"/>
-      <c r="C71" s="83"/>
-      <c r="D71" s="83"/>
-      <c r="E71" s="85"/>
+      <c r="B71" s="146"/>
+      <c r="C71" s="137"/>
+      <c r="D71" s="137"/>
+      <c r="E71" s="141"/>
       <c r="F71" s="8" t="s">
         <v>47</v>
       </c>
@@ -12625,10 +12631,10 @@
     </row>
     <row r="72" spans="1:7" ht="9.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="3"/>
-      <c r="B72" s="92"/>
-      <c r="C72" s="83"/>
-      <c r="D72" s="83"/>
-      <c r="E72" s="86"/>
+      <c r="B72" s="146"/>
+      <c r="C72" s="137"/>
+      <c r="D72" s="137"/>
+      <c r="E72" s="142"/>
       <c r="F72" s="9" t="s">
         <v>132</v>
       </c>
@@ -12636,10 +12642,10 @@
     </row>
     <row r="73" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73" s="3"/>
-      <c r="B73" s="92"/>
-      <c r="C73" s="83"/>
-      <c r="D73" s="83"/>
-      <c r="E73" s="94" t="s">
+      <c r="B73" s="146"/>
+      <c r="C73" s="137"/>
+      <c r="D73" s="137"/>
+      <c r="E73" s="140" t="s">
         <v>137</v>
       </c>
       <c r="F73" s="7" t="s">
@@ -12649,10 +12655,10 @@
     </row>
     <row r="74" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="3"/>
-      <c r="B74" s="92"/>
-      <c r="C74" s="83"/>
-      <c r="D74" s="83"/>
-      <c r="E74" s="85"/>
+      <c r="B74" s="146"/>
+      <c r="C74" s="137"/>
+      <c r="D74" s="137"/>
+      <c r="E74" s="141"/>
       <c r="F74" s="8" t="s">
         <v>140</v>
       </c>
@@ -12660,10 +12666,10 @@
     </row>
     <row r="75" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="3"/>
-      <c r="B75" s="92"/>
-      <c r="C75" s="83"/>
-      <c r="D75" s="83"/>
-      <c r="E75" s="85"/>
+      <c r="B75" s="146"/>
+      <c r="C75" s="137"/>
+      <c r="D75" s="137"/>
+      <c r="E75" s="141"/>
       <c r="F75" s="8" t="s">
         <v>141</v>
       </c>
@@ -12671,10 +12677,10 @@
     </row>
     <row r="76" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" s="3"/>
-      <c r="B76" s="92"/>
-      <c r="C76" s="83"/>
-      <c r="D76" s="83"/>
-      <c r="E76" s="86"/>
+      <c r="B76" s="146"/>
+      <c r="C76" s="137"/>
+      <c r="D76" s="137"/>
+      <c r="E76" s="142"/>
       <c r="F76" s="9" t="s">
         <v>142</v>
       </c>
@@ -12682,10 +12688,10 @@
     </row>
     <row r="77" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="3"/>
-      <c r="B77" s="92"/>
-      <c r="C77" s="83"/>
-      <c r="D77" s="83"/>
-      <c r="E77" s="94" t="s">
+      <c r="B77" s="146"/>
+      <c r="C77" s="137"/>
+      <c r="D77" s="137"/>
+      <c r="E77" s="140" t="s">
         <v>104</v>
       </c>
       <c r="F77" s="7" t="s">
@@ -12695,10 +12701,10 @@
     </row>
     <row r="78" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78" s="3"/>
-      <c r="B78" s="92"/>
-      <c r="C78" s="83"/>
-      <c r="D78" s="83"/>
-      <c r="E78" s="85"/>
+      <c r="B78" s="146"/>
+      <c r="C78" s="137"/>
+      <c r="D78" s="137"/>
+      <c r="E78" s="141"/>
       <c r="F78" s="8" t="s">
         <v>112</v>
       </c>
@@ -12706,10 +12712,10 @@
     </row>
     <row r="79" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" s="3"/>
-      <c r="B79" s="92"/>
-      <c r="C79" s="83"/>
-      <c r="D79" s="83"/>
-      <c r="E79" s="85"/>
+      <c r="B79" s="146"/>
+      <c r="C79" s="137"/>
+      <c r="D79" s="137"/>
+      <c r="E79" s="141"/>
       <c r="F79" s="8" t="s">
         <v>113</v>
       </c>
@@ -12717,10 +12723,10 @@
     </row>
     <row r="80" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="3"/>
-      <c r="B80" s="92"/>
-      <c r="C80" s="83"/>
-      <c r="D80" s="83"/>
-      <c r="E80" s="86"/>
+      <c r="B80" s="146"/>
+      <c r="C80" s="137"/>
+      <c r="D80" s="137"/>
+      <c r="E80" s="142"/>
       <c r="F80" s="9" t="s">
         <v>114</v>
       </c>
@@ -12728,10 +12734,10 @@
     </row>
     <row r="81" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A81" s="3"/>
-      <c r="B81" s="92"/>
-      <c r="C81" s="83"/>
-      <c r="D81" s="83"/>
-      <c r="E81" s="94" t="s">
+      <c r="B81" s="146"/>
+      <c r="C81" s="137"/>
+      <c r="D81" s="137"/>
+      <c r="E81" s="140" t="s">
         <v>107</v>
       </c>
       <c r="F81" s="7" t="s">
@@ -12741,10 +12747,10 @@
     </row>
     <row r="82" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A82" s="3"/>
-      <c r="B82" s="92"/>
-      <c r="C82" s="83"/>
-      <c r="D82" s="83"/>
-      <c r="E82" s="85"/>
+      <c r="B82" s="146"/>
+      <c r="C82" s="137"/>
+      <c r="D82" s="137"/>
+      <c r="E82" s="141"/>
       <c r="F82" s="8" t="s">
         <v>116</v>
       </c>
@@ -12752,10 +12758,10 @@
     </row>
     <row r="83" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A83" s="3"/>
-      <c r="B83" s="92"/>
-      <c r="C83" s="83"/>
-      <c r="D83" s="83"/>
-      <c r="E83" s="85"/>
+      <c r="B83" s="146"/>
+      <c r="C83" s="137"/>
+      <c r="D83" s="137"/>
+      <c r="E83" s="141"/>
       <c r="F83" s="8" t="s">
         <v>117</v>
       </c>
@@ -12763,10 +12769,10 @@
     </row>
     <row r="84" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A84" s="3"/>
-      <c r="B84" s="92"/>
-      <c r="C84" s="83"/>
-      <c r="D84" s="83"/>
-      <c r="E84" s="86"/>
+      <c r="B84" s="146"/>
+      <c r="C84" s="137"/>
+      <c r="D84" s="137"/>
+      <c r="E84" s="142"/>
       <c r="F84" s="9" t="s">
         <v>118</v>
       </c>
@@ -12774,10 +12780,10 @@
     </row>
     <row r="85" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A85" s="3"/>
-      <c r="B85" s="92"/>
-      <c r="C85" s="83"/>
-      <c r="D85" s="83"/>
-      <c r="E85" s="94" t="s">
+      <c r="B85" s="146"/>
+      <c r="C85" s="137"/>
+      <c r="D85" s="137"/>
+      <c r="E85" s="140" t="s">
         <v>109</v>
       </c>
       <c r="F85" s="7" t="s">
@@ -12787,10 +12793,10 @@
     </row>
     <row r="86" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="3"/>
-      <c r="B86" s="92"/>
-      <c r="C86" s="83"/>
-      <c r="D86" s="83"/>
-      <c r="E86" s="85"/>
+      <c r="B86" s="146"/>
+      <c r="C86" s="137"/>
+      <c r="D86" s="137"/>
+      <c r="E86" s="141"/>
       <c r="F86" s="8" t="s">
         <v>120</v>
       </c>
@@ -12798,10 +12804,10 @@
     </row>
     <row r="87" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A87" s="3"/>
-      <c r="B87" s="92"/>
-      <c r="C87" s="83"/>
-      <c r="D87" s="83"/>
-      <c r="E87" s="85"/>
+      <c r="B87" s="146"/>
+      <c r="C87" s="137"/>
+      <c r="D87" s="137"/>
+      <c r="E87" s="141"/>
       <c r="F87" s="8" t="s">
         <v>121</v>
       </c>
@@ -12809,10 +12815,10 @@
     </row>
     <row r="88" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A88" s="3"/>
-      <c r="B88" s="92"/>
-      <c r="C88" s="83"/>
-      <c r="D88" s="83"/>
-      <c r="E88" s="86"/>
+      <c r="B88" s="146"/>
+      <c r="C88" s="137"/>
+      <c r="D88" s="137"/>
+      <c r="E88" s="142"/>
       <c r="F88" s="9" t="s">
         <v>122</v>
       </c>
@@ -12820,10 +12826,10 @@
     </row>
     <row r="89" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A89" s="3"/>
-      <c r="B89" s="92"/>
-      <c r="C89" s="83"/>
-      <c r="D89" s="83"/>
-      <c r="E89" s="94" t="s">
+      <c r="B89" s="146"/>
+      <c r="C89" s="137"/>
+      <c r="D89" s="137"/>
+      <c r="E89" s="140" t="s">
         <v>129</v>
       </c>
       <c r="F89" s="7" t="s">
@@ -12833,10 +12839,10 @@
     </row>
     <row r="90" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A90" s="3"/>
-      <c r="B90" s="92"/>
-      <c r="C90" s="83"/>
-      <c r="D90" s="83"/>
-      <c r="E90" s="95"/>
+      <c r="B90" s="146"/>
+      <c r="C90" s="137"/>
+      <c r="D90" s="137"/>
+      <c r="E90" s="143"/>
       <c r="F90" s="8" t="s">
         <v>125</v>
       </c>
@@ -12844,10 +12850,10 @@
     </row>
     <row r="91" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A91" s="3"/>
-      <c r="B91" s="92"/>
-      <c r="C91" s="83"/>
-      <c r="D91" s="83"/>
-      <c r="E91" s="95"/>
+      <c r="B91" s="146"/>
+      <c r="C91" s="137"/>
+      <c r="D91" s="137"/>
+      <c r="E91" s="143"/>
       <c r="F91" s="8" t="s">
         <v>126</v>
       </c>
@@ -12855,10 +12861,10 @@
     </row>
     <row r="92" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A92" s="3"/>
-      <c r="B92" s="92"/>
-      <c r="C92" s="83"/>
-      <c r="D92" s="83"/>
-      <c r="E92" s="96"/>
+      <c r="B92" s="146"/>
+      <c r="C92" s="137"/>
+      <c r="D92" s="137"/>
+      <c r="E92" s="144"/>
       <c r="F92" s="9" t="s">
         <v>127</v>
       </c>
@@ -12866,10 +12872,10 @@
     </row>
     <row r="93" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A93" s="3"/>
-      <c r="B93" s="92"/>
-      <c r="C93" s="83"/>
-      <c r="D93" s="83"/>
-      <c r="E93" s="94" t="s">
+      <c r="B93" s="146"/>
+      <c r="C93" s="137"/>
+      <c r="D93" s="137"/>
+      <c r="E93" s="140" t="s">
         <v>131</v>
       </c>
       <c r="F93" s="7" t="s">
@@ -12879,10 +12885,10 @@
     </row>
     <row r="94" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A94" s="3"/>
-      <c r="B94" s="92"/>
-      <c r="C94" s="83"/>
-      <c r="D94" s="83"/>
-      <c r="E94" s="95"/>
+      <c r="B94" s="146"/>
+      <c r="C94" s="137"/>
+      <c r="D94" s="137"/>
+      <c r="E94" s="143"/>
       <c r="F94" s="8" t="s">
         <v>134</v>
       </c>
@@ -12890,10 +12896,10 @@
     </row>
     <row r="95" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A95" s="3"/>
-      <c r="B95" s="92"/>
-      <c r="C95" s="83"/>
-      <c r="D95" s="83"/>
-      <c r="E95" s="95"/>
+      <c r="B95" s="146"/>
+      <c r="C95" s="137"/>
+      <c r="D95" s="137"/>
+      <c r="E95" s="143"/>
       <c r="F95" s="8" t="s">
         <v>135</v>
       </c>
@@ -12901,10 +12907,10 @@
     </row>
     <row r="96" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A96" s="3"/>
-      <c r="B96" s="92"/>
-      <c r="C96" s="83"/>
-      <c r="D96" s="83"/>
-      <c r="E96" s="96"/>
+      <c r="B96" s="146"/>
+      <c r="C96" s="137"/>
+      <c r="D96" s="137"/>
+      <c r="E96" s="144"/>
       <c r="F96" s="9" t="s">
         <v>136</v>
       </c>
@@ -12912,10 +12918,10 @@
     </row>
     <row r="97" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A97" s="3"/>
-      <c r="B97" s="92"/>
-      <c r="C97" s="83"/>
-      <c r="D97" s="83"/>
-      <c r="E97" s="94" t="s">
+      <c r="B97" s="146"/>
+      <c r="C97" s="137"/>
+      <c r="D97" s="137"/>
+      <c r="E97" s="140" t="s">
         <v>138</v>
       </c>
       <c r="F97" s="7" t="s">
@@ -12925,10 +12931,10 @@
     </row>
     <row r="98" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A98" s="3"/>
-      <c r="B98" s="92"/>
-      <c r="C98" s="83"/>
-      <c r="D98" s="83"/>
-      <c r="E98" s="95"/>
+      <c r="B98" s="146"/>
+      <c r="C98" s="137"/>
+      <c r="D98" s="137"/>
+      <c r="E98" s="143"/>
       <c r="F98" s="8" t="s">
         <v>144</v>
       </c>
@@ -12936,10 +12942,10 @@
     </row>
     <row r="99" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A99" s="3"/>
-      <c r="B99" s="92"/>
-      <c r="C99" s="83"/>
-      <c r="D99" s="83"/>
-      <c r="E99" s="95"/>
+      <c r="B99" s="146"/>
+      <c r="C99" s="137"/>
+      <c r="D99" s="137"/>
+      <c r="E99" s="143"/>
       <c r="F99" s="8" t="s">
         <v>145</v>
       </c>
@@ -12947,10 +12953,10 @@
     </row>
     <row r="100" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A100" s="3"/>
-      <c r="B100" s="92"/>
-      <c r="C100" s="83"/>
-      <c r="D100" s="83"/>
-      <c r="E100" s="96"/>
+      <c r="B100" s="146"/>
+      <c r="C100" s="137"/>
+      <c r="D100" s="137"/>
+      <c r="E100" s="144"/>
       <c r="F100" s="9" t="s">
         <v>146</v>
       </c>
@@ -12958,93 +12964,93 @@
     </row>
     <row r="101" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A101" s="3"/>
-      <c r="B101" s="92"/>
-      <c r="C101" s="83"/>
+      <c r="B101" s="146"/>
+      <c r="C101" s="137"/>
       <c r="D101" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="E101" s="87" t="s">
+      <c r="E101" s="135" t="s">
         <v>11</v>
       </c>
-      <c r="F101" s="88"/>
+      <c r="F101" s="136"/>
       <c r="G101" s="3"/>
     </row>
     <row r="102" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A102" s="3"/>
-      <c r="B102" s="92"/>
-      <c r="C102" s="83"/>
+      <c r="B102" s="146"/>
+      <c r="C102" s="137"/>
       <c r="D102" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="E102" s="83"/>
-      <c r="F102" s="88"/>
+      <c r="E102" s="137"/>
+      <c r="F102" s="136"/>
       <c r="G102" s="3"/>
     </row>
     <row r="103" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A103" s="3"/>
-      <c r="B103" s="92"/>
-      <c r="C103" s="83"/>
+      <c r="B103" s="146"/>
+      <c r="C103" s="137"/>
       <c r="D103" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="E103" s="83"/>
-      <c r="F103" s="88"/>
+      <c r="E103" s="137"/>
+      <c r="F103" s="136"/>
       <c r="G103" s="3"/>
     </row>
     <row r="104" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A104" s="3"/>
-      <c r="B104" s="92"/>
-      <c r="C104" s="83"/>
+      <c r="B104" s="146"/>
+      <c r="C104" s="137"/>
       <c r="D104" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="E104" s="83"/>
-      <c r="F104" s="88"/>
+      <c r="E104" s="137"/>
+      <c r="F104" s="136"/>
       <c r="G104" s="3"/>
     </row>
     <row r="105" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A105" s="3"/>
-      <c r="B105" s="92"/>
-      <c r="C105" s="83"/>
+      <c r="B105" s="146"/>
+      <c r="C105" s="137"/>
       <c r="D105" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="E105" s="83"/>
-      <c r="F105" s="88"/>
+      <c r="E105" s="137"/>
+      <c r="F105" s="136"/>
       <c r="G105" s="3"/>
     </row>
     <row r="106" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A106" s="3"/>
-      <c r="B106" s="92"/>
-      <c r="C106" s="83"/>
+      <c r="B106" s="146"/>
+      <c r="C106" s="137"/>
       <c r="D106" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="E106" s="83"/>
-      <c r="F106" s="88"/>
+      <c r="E106" s="137"/>
+      <c r="F106" s="136"/>
       <c r="G106" s="3"/>
     </row>
     <row r="107" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A107" s="3"/>
-      <c r="B107" s="92"/>
-      <c r="C107" s="83"/>
+      <c r="B107" s="146"/>
+      <c r="C107" s="137"/>
       <c r="D107" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="E107" s="83"/>
-      <c r="F107" s="88"/>
+      <c r="E107" s="137"/>
+      <c r="F107" s="136"/>
       <c r="G107" s="3"/>
     </row>
     <row r="108" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A108" s="3"/>
-      <c r="B108" s="92"/>
-      <c r="C108" s="83" t="s">
+      <c r="B108" s="146"/>
+      <c r="C108" s="137" t="s">
         <v>64</v>
       </c>
-      <c r="D108" s="89" t="s">
+      <c r="D108" s="148" t="s">
         <v>65</v>
       </c>
-      <c r="E108" s="84" t="s">
+      <c r="E108" s="145" t="s">
         <v>167</v>
       </c>
       <c r="F108" s="12" t="s">
@@ -13054,10 +13060,10 @@
     </row>
     <row r="109" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A109" s="3"/>
-      <c r="B109" s="92"/>
-      <c r="C109" s="83"/>
-      <c r="D109" s="90"/>
-      <c r="E109" s="85"/>
+      <c r="B109" s="146"/>
+      <c r="C109" s="137"/>
+      <c r="D109" s="149"/>
+      <c r="E109" s="141"/>
       <c r="F109" s="13" t="s">
         <v>4</v>
       </c>
@@ -13065,10 +13071,10 @@
     </row>
     <row r="110" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A110" s="3"/>
-      <c r="B110" s="92"/>
-      <c r="C110" s="83"/>
-      <c r="D110" s="90"/>
-      <c r="E110" s="85"/>
+      <c r="B110" s="146"/>
+      <c r="C110" s="137"/>
+      <c r="D110" s="149"/>
+      <c r="E110" s="141"/>
       <c r="F110" s="13" t="s">
         <v>5</v>
       </c>
@@ -13076,10 +13082,10 @@
     </row>
     <row r="111" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A111" s="3"/>
-      <c r="B111" s="92"/>
-      <c r="C111" s="83"/>
-      <c r="D111" s="90"/>
-      <c r="E111" s="86"/>
+      <c r="B111" s="146"/>
+      <c r="C111" s="137"/>
+      <c r="D111" s="149"/>
+      <c r="E111" s="142"/>
       <c r="F111" s="14" t="s">
         <v>6</v>
       </c>
@@ -13087,10 +13093,10 @@
     </row>
     <row r="112" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A112" s="3"/>
-      <c r="B112" s="92"/>
-      <c r="C112" s="83"/>
-      <c r="D112" s="90"/>
-      <c r="E112" s="84" t="s">
+      <c r="B112" s="146"/>
+      <c r="C112" s="137"/>
+      <c r="D112" s="149"/>
+      <c r="E112" s="145" t="s">
         <v>73</v>
       </c>
       <c r="F112" s="12" t="s">
@@ -13100,10 +13106,10 @@
     </row>
     <row r="113" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A113" s="3"/>
-      <c r="B113" s="92"/>
-      <c r="C113" s="83"/>
-      <c r="D113" s="90"/>
-      <c r="E113" s="85"/>
+      <c r="B113" s="146"/>
+      <c r="C113" s="137"/>
+      <c r="D113" s="149"/>
+      <c r="E113" s="141"/>
       <c r="F113" s="13" t="s">
         <v>4</v>
       </c>
@@ -13111,10 +13117,10 @@
     </row>
     <row r="114" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A114" s="3"/>
-      <c r="B114" s="92"/>
-      <c r="C114" s="83"/>
-      <c r="D114" s="90"/>
-      <c r="E114" s="85"/>
+      <c r="B114" s="146"/>
+      <c r="C114" s="137"/>
+      <c r="D114" s="149"/>
+      <c r="E114" s="141"/>
       <c r="F114" s="13" t="s">
         <v>5</v>
       </c>
@@ -13122,10 +13128,10 @@
     </row>
     <row r="115" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A115" s="3"/>
-      <c r="B115" s="92"/>
-      <c r="C115" s="83"/>
-      <c r="D115" s="90"/>
-      <c r="E115" s="86"/>
+      <c r="B115" s="146"/>
+      <c r="C115" s="137"/>
+      <c r="D115" s="149"/>
+      <c r="E115" s="142"/>
       <c r="F115" s="14" t="s">
         <v>6</v>
       </c>
@@ -13133,10 +13139,10 @@
     </row>
     <row r="116" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A116" s="3"/>
-      <c r="B116" s="92"/>
-      <c r="C116" s="83"/>
-      <c r="D116" s="90"/>
-      <c r="E116" s="84" t="s">
+      <c r="B116" s="146"/>
+      <c r="C116" s="137"/>
+      <c r="D116" s="149"/>
+      <c r="E116" s="145" t="s">
         <v>74</v>
       </c>
       <c r="F116" s="12" t="s">
@@ -13146,10 +13152,10 @@
     </row>
     <row r="117" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A117" s="3"/>
-      <c r="B117" s="92"/>
-      <c r="C117" s="83"/>
-      <c r="D117" s="90"/>
-      <c r="E117" s="85"/>
+      <c r="B117" s="146"/>
+      <c r="C117" s="137"/>
+      <c r="D117" s="149"/>
+      <c r="E117" s="141"/>
       <c r="F117" s="13" t="s">
         <v>4</v>
       </c>
@@ -13157,10 +13163,10 @@
     </row>
     <row r="118" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A118" s="3"/>
-      <c r="B118" s="92"/>
-      <c r="C118" s="83"/>
-      <c r="D118" s="90"/>
-      <c r="E118" s="85"/>
+      <c r="B118" s="146"/>
+      <c r="C118" s="137"/>
+      <c r="D118" s="149"/>
+      <c r="E118" s="141"/>
       <c r="F118" s="13" t="s">
         <v>5</v>
       </c>
@@ -13168,10 +13174,10 @@
     </row>
     <row r="119" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A119" s="3"/>
-      <c r="B119" s="92"/>
-      <c r="C119" s="83"/>
-      <c r="D119" s="90"/>
-      <c r="E119" s="86"/>
+      <c r="B119" s="146"/>
+      <c r="C119" s="137"/>
+      <c r="D119" s="149"/>
+      <c r="E119" s="142"/>
       <c r="F119" s="14" t="s">
         <v>6</v>
       </c>
@@ -13179,10 +13185,10 @@
     </row>
     <row r="120" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A120" s="3"/>
-      <c r="B120" s="92"/>
-      <c r="C120" s="83"/>
-      <c r="D120" s="90"/>
-      <c r="E120" s="84" t="s">
+      <c r="B120" s="146"/>
+      <c r="C120" s="137"/>
+      <c r="D120" s="149"/>
+      <c r="E120" s="145" t="s">
         <v>9</v>
       </c>
       <c r="F120" s="12" t="s">
@@ -13192,10 +13198,10 @@
     </row>
     <row r="121" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A121" s="3"/>
-      <c r="B121" s="92"/>
-      <c r="C121" s="83"/>
-      <c r="D121" s="90"/>
-      <c r="E121" s="85"/>
+      <c r="B121" s="146"/>
+      <c r="C121" s="137"/>
+      <c r="D121" s="149"/>
+      <c r="E121" s="141"/>
       <c r="F121" s="13" t="s">
         <v>4</v>
       </c>
@@ -13203,10 +13209,10 @@
     </row>
     <row r="122" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A122" s="3"/>
-      <c r="B122" s="92"/>
-      <c r="C122" s="83"/>
-      <c r="D122" s="90"/>
-      <c r="E122" s="85"/>
+      <c r="B122" s="146"/>
+      <c r="C122" s="137"/>
+      <c r="D122" s="149"/>
+      <c r="E122" s="141"/>
       <c r="F122" s="13" t="s">
         <v>5</v>
       </c>
@@ -13214,10 +13220,10 @@
     </row>
     <row r="123" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A123" s="3"/>
-      <c r="B123" s="92"/>
-      <c r="C123" s="83"/>
-      <c r="D123" s="90"/>
-      <c r="E123" s="86"/>
+      <c r="B123" s="146"/>
+      <c r="C123" s="137"/>
+      <c r="D123" s="149"/>
+      <c r="E123" s="142"/>
       <c r="F123" s="14" t="s">
         <v>6</v>
       </c>
@@ -13225,10 +13231,10 @@
     </row>
     <row r="124" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A124" s="3"/>
-      <c r="B124" s="92"/>
-      <c r="C124" s="83"/>
-      <c r="D124" s="90"/>
-      <c r="E124" s="84" t="s">
+      <c r="B124" s="146"/>
+      <c r="C124" s="137"/>
+      <c r="D124" s="149"/>
+      <c r="E124" s="145" t="s">
         <v>75</v>
       </c>
       <c r="F124" s="12" t="s">
@@ -13238,10 +13244,10 @@
     </row>
     <row r="125" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A125" s="3"/>
-      <c r="B125" s="92"/>
-      <c r="C125" s="83"/>
-      <c r="D125" s="90"/>
-      <c r="E125" s="85"/>
+      <c r="B125" s="146"/>
+      <c r="C125" s="137"/>
+      <c r="D125" s="149"/>
+      <c r="E125" s="141"/>
       <c r="F125" s="13" t="s">
         <v>4</v>
       </c>
@@ -13249,10 +13255,10 @@
     </row>
     <row r="126" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A126" s="3"/>
-      <c r="B126" s="92"/>
-      <c r="C126" s="83"/>
-      <c r="D126" s="90"/>
-      <c r="E126" s="85"/>
+      <c r="B126" s="146"/>
+      <c r="C126" s="137"/>
+      <c r="D126" s="149"/>
+      <c r="E126" s="141"/>
       <c r="F126" s="13" t="s">
         <v>5</v>
       </c>
@@ -13260,10 +13266,10 @@
     </row>
     <row r="127" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A127" s="3"/>
-      <c r="B127" s="92"/>
-      <c r="C127" s="83"/>
-      <c r="D127" s="91"/>
-      <c r="E127" s="86"/>
+      <c r="B127" s="146"/>
+      <c r="C127" s="137"/>
+      <c r="D127" s="150"/>
+      <c r="E127" s="142"/>
       <c r="F127" s="14" t="s">
         <v>6</v>
       </c>
@@ -13271,93 +13277,93 @@
     </row>
     <row r="128" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A128" s="3"/>
-      <c r="B128" s="92"/>
-      <c r="C128" s="83"/>
+      <c r="B128" s="146"/>
+      <c r="C128" s="137"/>
       <c r="D128" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="E128" s="87" t="s">
+      <c r="E128" s="135" t="s">
         <v>11</v>
       </c>
-      <c r="F128" s="88"/>
+      <c r="F128" s="136"/>
       <c r="G128" s="3"/>
     </row>
     <row r="129" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A129" s="3"/>
-      <c r="B129" s="92"/>
-      <c r="C129" s="83"/>
+      <c r="B129" s="146"/>
+      <c r="C129" s="137"/>
       <c r="D129" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="E129" s="83"/>
-      <c r="F129" s="88"/>
+      <c r="E129" s="137"/>
+      <c r="F129" s="136"/>
       <c r="G129" s="3"/>
     </row>
     <row r="130" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A130" s="3"/>
-      <c r="B130" s="92"/>
-      <c r="C130" s="83"/>
+      <c r="B130" s="146"/>
+      <c r="C130" s="137"/>
       <c r="D130" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="E130" s="83"/>
-      <c r="F130" s="88"/>
+      <c r="E130" s="137"/>
+      <c r="F130" s="136"/>
       <c r="G130" s="3"/>
     </row>
     <row r="131" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A131" s="3"/>
-      <c r="B131" s="92"/>
-      <c r="C131" s="83"/>
+      <c r="B131" s="146"/>
+      <c r="C131" s="137"/>
       <c r="D131" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="E131" s="83"/>
-      <c r="F131" s="88"/>
+      <c r="E131" s="137"/>
+      <c r="F131" s="136"/>
       <c r="G131" s="3"/>
     </row>
     <row r="132" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A132" s="3"/>
-      <c r="B132" s="92"/>
-      <c r="C132" s="83"/>
+      <c r="B132" s="146"/>
+      <c r="C132" s="137"/>
       <c r="D132" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="E132" s="83"/>
-      <c r="F132" s="88"/>
+      <c r="E132" s="137"/>
+      <c r="F132" s="136"/>
       <c r="G132" s="3"/>
     </row>
     <row r="133" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A133" s="3"/>
-      <c r="B133" s="92"/>
-      <c r="C133" s="83"/>
+      <c r="B133" s="146"/>
+      <c r="C133" s="137"/>
       <c r="D133" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="E133" s="83"/>
-      <c r="F133" s="88"/>
+      <c r="E133" s="137"/>
+      <c r="F133" s="136"/>
       <c r="G133" s="3"/>
     </row>
     <row r="134" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A134" s="3"/>
-      <c r="B134" s="92"/>
-      <c r="C134" s="83"/>
+      <c r="B134" s="146"/>
+      <c r="C134" s="137"/>
       <c r="D134" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="E134" s="83"/>
-      <c r="F134" s="88"/>
+      <c r="E134" s="137"/>
+      <c r="F134" s="136"/>
       <c r="G134" s="3"/>
     </row>
     <row r="135" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A135" s="3"/>
-      <c r="B135" s="92"/>
-      <c r="C135" s="83" t="s">
+      <c r="B135" s="146"/>
+      <c r="C135" s="137" t="s">
         <v>18</v>
       </c>
-      <c r="D135" s="83" t="s">
+      <c r="D135" s="137" t="s">
         <v>19</v>
       </c>
-      <c r="E135" s="84" t="s">
+      <c r="E135" s="145" t="s">
         <v>20</v>
       </c>
       <c r="F135" s="7">
@@ -13367,10 +13373,10 @@
     </row>
     <row r="136" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A136" s="3"/>
-      <c r="B136" s="92"/>
-      <c r="C136" s="83"/>
-      <c r="D136" s="83"/>
-      <c r="E136" s="85"/>
+      <c r="B136" s="146"/>
+      <c r="C136" s="137"/>
+      <c r="D136" s="137"/>
+      <c r="E136" s="141"/>
       <c r="F136" s="8">
         <v>0.6</v>
       </c>
@@ -13378,10 +13384,10 @@
     </row>
     <row r="137" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A137" s="3"/>
-      <c r="B137" s="92"/>
-      <c r="C137" s="83"/>
-      <c r="D137" s="83"/>
-      <c r="E137" s="85"/>
+      <c r="B137" s="146"/>
+      <c r="C137" s="137"/>
+      <c r="D137" s="137"/>
+      <c r="E137" s="141"/>
       <c r="F137" s="8">
         <v>0.7</v>
       </c>
@@ -13389,10 +13395,10 @@
     </row>
     <row r="138" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A138" s="3"/>
-      <c r="B138" s="92"/>
-      <c r="C138" s="83"/>
-      <c r="D138" s="83"/>
-      <c r="E138" s="85"/>
+      <c r="B138" s="146"/>
+      <c r="C138" s="137"/>
+      <c r="D138" s="137"/>
+      <c r="E138" s="141"/>
       <c r="F138" s="8">
         <v>0.8</v>
       </c>
@@ -13400,10 +13406,10 @@
     </row>
     <row r="139" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A139" s="3"/>
-      <c r="B139" s="92"/>
-      <c r="C139" s="83"/>
-      <c r="D139" s="83"/>
-      <c r="E139" s="86"/>
+      <c r="B139" s="146"/>
+      <c r="C139" s="137"/>
+      <c r="D139" s="137"/>
+      <c r="E139" s="142"/>
       <c r="F139" s="9">
         <v>0.9</v>
       </c>
@@ -13411,10 +13417,10 @@
     </row>
     <row r="140" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A140" s="3"/>
-      <c r="B140" s="92"/>
-      <c r="C140" s="83"/>
-      <c r="D140" s="83"/>
-      <c r="E140" s="84" t="s">
+      <c r="B140" s="146"/>
+      <c r="C140" s="137"/>
+      <c r="D140" s="137"/>
+      <c r="E140" s="145" t="s">
         <v>86</v>
       </c>
       <c r="F140" s="12" t="s">
@@ -13424,10 +13430,10 @@
     </row>
     <row r="141" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A141" s="3"/>
-      <c r="B141" s="92"/>
-      <c r="C141" s="83"/>
-      <c r="D141" s="83"/>
-      <c r="E141" s="85"/>
+      <c r="B141" s="146"/>
+      <c r="C141" s="137"/>
+      <c r="D141" s="137"/>
+      <c r="E141" s="141"/>
       <c r="F141" s="13" t="s">
         <v>23</v>
       </c>
@@ -13435,10 +13441,10 @@
     </row>
     <row r="142" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A142" s="3"/>
-      <c r="B142" s="92"/>
-      <c r="C142" s="83"/>
-      <c r="D142" s="83"/>
-      <c r="E142" s="86"/>
+      <c r="B142" s="146"/>
+      <c r="C142" s="137"/>
+      <c r="D142" s="137"/>
+      <c r="E142" s="142"/>
       <c r="F142" s="14" t="s">
         <v>25</v>
       </c>
@@ -13446,10 +13452,10 @@
     </row>
     <row r="143" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A143" s="3"/>
-      <c r="B143" s="92"/>
-      <c r="C143" s="83"/>
-      <c r="D143" s="83"/>
-      <c r="E143" s="84" t="s">
+      <c r="B143" s="146"/>
+      <c r="C143" s="137"/>
+      <c r="D143" s="137"/>
+      <c r="E143" s="145" t="s">
         <v>87</v>
       </c>
       <c r="F143" s="12" t="s">
@@ -13459,10 +13465,10 @@
     </row>
     <row r="144" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A144" s="3"/>
-      <c r="B144" s="92"/>
-      <c r="C144" s="83"/>
-      <c r="D144" s="83"/>
-      <c r="E144" s="85"/>
+      <c r="B144" s="146"/>
+      <c r="C144" s="137"/>
+      <c r="D144" s="137"/>
+      <c r="E144" s="141"/>
       <c r="F144" s="13" t="s">
         <v>24</v>
       </c>
@@ -13470,10 +13476,10 @@
     </row>
     <row r="145" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A145" s="3"/>
-      <c r="B145" s="92"/>
-      <c r="C145" s="83"/>
-      <c r="D145" s="83"/>
-      <c r="E145" s="86"/>
+      <c r="B145" s="146"/>
+      <c r="C145" s="137"/>
+      <c r="D145" s="137"/>
+      <c r="E145" s="142"/>
       <c r="F145" s="14" t="s">
         <v>85</v>
       </c>
@@ -13481,93 +13487,93 @@
     </row>
     <row r="146" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A146" s="3"/>
-      <c r="B146" s="92"/>
-      <c r="C146" s="83"/>
+      <c r="B146" s="146"/>
+      <c r="C146" s="137"/>
       <c r="D146" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="E146" s="87" t="s">
+      <c r="E146" s="135" t="s">
         <v>11</v>
       </c>
-      <c r="F146" s="88"/>
+      <c r="F146" s="136"/>
       <c r="G146" s="3"/>
     </row>
     <row r="147" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A147" s="3"/>
-      <c r="B147" s="92"/>
-      <c r="C147" s="83"/>
+      <c r="B147" s="146"/>
+      <c r="C147" s="137"/>
       <c r="D147" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="E147" s="83"/>
-      <c r="F147" s="88"/>
+      <c r="E147" s="137"/>
+      <c r="F147" s="136"/>
       <c r="G147" s="3"/>
     </row>
     <row r="148" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A148" s="3"/>
-      <c r="B148" s="92"/>
-      <c r="C148" s="83"/>
+      <c r="B148" s="146"/>
+      <c r="C148" s="137"/>
       <c r="D148" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="E148" s="83"/>
-      <c r="F148" s="88"/>
+      <c r="E148" s="137"/>
+      <c r="F148" s="136"/>
       <c r="G148" s="3"/>
     </row>
     <row r="149" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A149" s="3"/>
-      <c r="B149" s="92"/>
-      <c r="C149" s="83"/>
+      <c r="B149" s="146"/>
+      <c r="C149" s="137"/>
       <c r="D149" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E149" s="83"/>
-      <c r="F149" s="88"/>
+      <c r="E149" s="137"/>
+      <c r="F149" s="136"/>
       <c r="G149" s="3"/>
     </row>
     <row r="150" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A150" s="3"/>
-      <c r="B150" s="92"/>
-      <c r="C150" s="83"/>
+      <c r="B150" s="146"/>
+      <c r="C150" s="137"/>
       <c r="D150" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="E150" s="83"/>
-      <c r="F150" s="88"/>
+      <c r="E150" s="137"/>
+      <c r="F150" s="136"/>
       <c r="G150" s="3"/>
     </row>
     <row r="151" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A151" s="3"/>
-      <c r="B151" s="92"/>
-      <c r="C151" s="83"/>
+      <c r="B151" s="146"/>
+      <c r="C151" s="137"/>
       <c r="D151" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="E151" s="83"/>
-      <c r="F151" s="88"/>
+      <c r="E151" s="137"/>
+      <c r="F151" s="136"/>
       <c r="G151" s="3"/>
     </row>
     <row r="152" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A152" s="3"/>
-      <c r="B152" s="92"/>
-      <c r="C152" s="83"/>
+      <c r="B152" s="146"/>
+      <c r="C152" s="137"/>
       <c r="D152" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="E152" s="83"/>
-      <c r="F152" s="88"/>
+      <c r="E152" s="137"/>
+      <c r="F152" s="136"/>
       <c r="G152" s="3"/>
     </row>
     <row r="153" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A153" s="3"/>
-      <c r="B153" s="92"/>
-      <c r="C153" s="83" t="s">
+      <c r="B153" s="146"/>
+      <c r="C153" s="137" t="s">
         <v>76</v>
       </c>
-      <c r="D153" s="83" t="s">
+      <c r="D153" s="137" t="s">
         <v>77</v>
       </c>
-      <c r="E153" s="84" t="s">
+      <c r="E153" s="145" t="s">
         <v>88</v>
       </c>
       <c r="F153" s="12" t="s">
@@ -13577,10 +13583,10 @@
     </row>
     <row r="154" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A154" s="3"/>
-      <c r="B154" s="92"/>
-      <c r="C154" s="83"/>
-      <c r="D154" s="83"/>
-      <c r="E154" s="85"/>
+      <c r="B154" s="146"/>
+      <c r="C154" s="137"/>
+      <c r="D154" s="137"/>
+      <c r="E154" s="141"/>
       <c r="F154" s="13" t="s">
         <v>23</v>
       </c>
@@ -13588,10 +13594,10 @@
     </row>
     <row r="155" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A155" s="3"/>
-      <c r="B155" s="92"/>
-      <c r="C155" s="83"/>
-      <c r="D155" s="83"/>
-      <c r="E155" s="86"/>
+      <c r="B155" s="146"/>
+      <c r="C155" s="137"/>
+      <c r="D155" s="137"/>
+      <c r="E155" s="142"/>
       <c r="F155" s="14" t="s">
         <v>25</v>
       </c>
@@ -13599,10 +13605,10 @@
     </row>
     <row r="156" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A156" s="3"/>
-      <c r="B156" s="92"/>
-      <c r="C156" s="83"/>
-      <c r="D156" s="83"/>
-      <c r="E156" s="84" t="s">
+      <c r="B156" s="146"/>
+      <c r="C156" s="137"/>
+      <c r="D156" s="137"/>
+      <c r="E156" s="145" t="s">
         <v>89</v>
       </c>
       <c r="F156" s="12" t="s">
@@ -13612,10 +13618,10 @@
     </row>
     <row r="157" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A157" s="3"/>
-      <c r="B157" s="92"/>
-      <c r="C157" s="83"/>
-      <c r="D157" s="83"/>
-      <c r="E157" s="85"/>
+      <c r="B157" s="146"/>
+      <c r="C157" s="137"/>
+      <c r="D157" s="137"/>
+      <c r="E157" s="141"/>
       <c r="F157" s="13" t="s">
         <v>24</v>
       </c>
@@ -13623,10 +13629,10 @@
     </row>
     <row r="158" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A158" s="3"/>
-      <c r="B158" s="92"/>
-      <c r="C158" s="83"/>
-      <c r="D158" s="83"/>
-      <c r="E158" s="86"/>
+      <c r="B158" s="146"/>
+      <c r="C158" s="137"/>
+      <c r="D158" s="137"/>
+      <c r="E158" s="142"/>
       <c r="F158" s="14" t="s">
         <v>85</v>
       </c>
@@ -13634,10 +13640,10 @@
     </row>
     <row r="159" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A159" s="3"/>
-      <c r="B159" s="92"/>
-      <c r="C159" s="83"/>
-      <c r="D159" s="83"/>
-      <c r="E159" s="84" t="s">
+      <c r="B159" s="146"/>
+      <c r="C159" s="137"/>
+      <c r="D159" s="137"/>
+      <c r="E159" s="145" t="s">
         <v>90</v>
       </c>
       <c r="F159" s="12" t="s">
@@ -13647,10 +13653,10 @@
     </row>
     <row r="160" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A160" s="3"/>
-      <c r="B160" s="92"/>
-      <c r="C160" s="83"/>
-      <c r="D160" s="83"/>
-      <c r="E160" s="85"/>
+      <c r="B160" s="146"/>
+      <c r="C160" s="137"/>
+      <c r="D160" s="137"/>
+      <c r="E160" s="141"/>
       <c r="F160" s="13" t="s">
         <v>23</v>
       </c>
@@ -13658,10 +13664,10 @@
     </row>
     <row r="161" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A161" s="3"/>
-      <c r="B161" s="92"/>
-      <c r="C161" s="83"/>
-      <c r="D161" s="83"/>
-      <c r="E161" s="86"/>
+      <c r="B161" s="146"/>
+      <c r="C161" s="137"/>
+      <c r="D161" s="137"/>
+      <c r="E161" s="142"/>
       <c r="F161" s="14" t="s">
         <v>25</v>
       </c>
@@ -13669,10 +13675,10 @@
     </row>
     <row r="162" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A162" s="3"/>
-      <c r="B162" s="92"/>
-      <c r="C162" s="83"/>
-      <c r="D162" s="83"/>
-      <c r="E162" s="84" t="s">
+      <c r="B162" s="146"/>
+      <c r="C162" s="137"/>
+      <c r="D162" s="137"/>
+      <c r="E162" s="145" t="s">
         <v>91</v>
       </c>
       <c r="F162" s="12" t="s">
@@ -13682,10 +13688,10 @@
     </row>
     <row r="163" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A163" s="3"/>
-      <c r="B163" s="92"/>
-      <c r="C163" s="83"/>
-      <c r="D163" s="83"/>
-      <c r="E163" s="85"/>
+      <c r="B163" s="146"/>
+      <c r="C163" s="137"/>
+      <c r="D163" s="137"/>
+      <c r="E163" s="141"/>
       <c r="F163" s="13" t="s">
         <v>24</v>
       </c>
@@ -13693,10 +13699,10 @@
     </row>
     <row r="164" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A164" s="3"/>
-      <c r="B164" s="92"/>
-      <c r="C164" s="83"/>
-      <c r="D164" s="83"/>
-      <c r="E164" s="86"/>
+      <c r="B164" s="146"/>
+      <c r="C164" s="137"/>
+      <c r="D164" s="137"/>
+      <c r="E164" s="142"/>
       <c r="F164" s="14" t="s">
         <v>85</v>
       </c>
@@ -13704,81 +13710,81 @@
     </row>
     <row r="165" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A165" s="3"/>
-      <c r="B165" s="92"/>
-      <c r="C165" s="83"/>
+      <c r="B165" s="146"/>
+      <c r="C165" s="137"/>
       <c r="D165" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="E165" s="87" t="s">
+      <c r="E165" s="135" t="s">
         <v>11</v>
       </c>
-      <c r="F165" s="88"/>
+      <c r="F165" s="136"/>
       <c r="G165" s="3"/>
     </row>
     <row r="166" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A166" s="3"/>
-      <c r="B166" s="92"/>
-      <c r="C166" s="83"/>
+      <c r="B166" s="146"/>
+      <c r="C166" s="137"/>
       <c r="D166" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="E166" s="83"/>
-      <c r="F166" s="88"/>
+      <c r="E166" s="137"/>
+      <c r="F166" s="136"/>
       <c r="G166" s="3"/>
     </row>
     <row r="167" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A167" s="3"/>
-      <c r="B167" s="92"/>
-      <c r="C167" s="83"/>
+      <c r="B167" s="146"/>
+      <c r="C167" s="137"/>
       <c r="D167" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="E167" s="83"/>
-      <c r="F167" s="88"/>
+      <c r="E167" s="137"/>
+      <c r="F167" s="136"/>
       <c r="G167" s="3"/>
     </row>
     <row r="168" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A168" s="3"/>
-      <c r="B168" s="92"/>
-      <c r="C168" s="83"/>
+      <c r="B168" s="146"/>
+      <c r="C168" s="137"/>
       <c r="D168" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="E168" s="83"/>
-      <c r="F168" s="88"/>
+      <c r="E168" s="137"/>
+      <c r="F168" s="136"/>
       <c r="G168" s="3"/>
     </row>
     <row r="169" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A169" s="3"/>
-      <c r="B169" s="92"/>
-      <c r="C169" s="83"/>
+      <c r="B169" s="146"/>
+      <c r="C169" s="137"/>
       <c r="D169" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="E169" s="83"/>
-      <c r="F169" s="88"/>
+      <c r="E169" s="137"/>
+      <c r="F169" s="136"/>
       <c r="G169" s="3"/>
     </row>
     <row r="170" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A170" s="3"/>
-      <c r="B170" s="92"/>
-      <c r="C170" s="83"/>
+      <c r="B170" s="146"/>
+      <c r="C170" s="137"/>
       <c r="D170" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="E170" s="83"/>
-      <c r="F170" s="88"/>
+      <c r="E170" s="137"/>
+      <c r="F170" s="136"/>
       <c r="G170" s="3"/>
     </row>
     <row r="171" spans="1:7" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A171" s="3"/>
-      <c r="B171" s="93"/>
-      <c r="C171" s="97"/>
+      <c r="B171" s="147"/>
+      <c r="C171" s="138"/>
       <c r="D171" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="E171" s="97"/>
-      <c r="F171" s="98"/>
+      <c r="E171" s="138"/>
+      <c r="F171" s="139"/>
       <c r="G171" s="3"/>
     </row>
     <row r="172" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15">
@@ -13794,6 +13800,40 @@
     <row r="174" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <mergeCells count="50">
+    <mergeCell ref="C30:C52"/>
+    <mergeCell ref="D30:D45"/>
+    <mergeCell ref="E30:E33"/>
+    <mergeCell ref="E34:E37"/>
+    <mergeCell ref="E38:E41"/>
+    <mergeCell ref="E42:E45"/>
+    <mergeCell ref="E46:F52"/>
+    <mergeCell ref="E4:E7"/>
+    <mergeCell ref="E8:E13"/>
+    <mergeCell ref="E14:E22"/>
+    <mergeCell ref="D4:D22"/>
+    <mergeCell ref="C4:C29"/>
+    <mergeCell ref="E23:F29"/>
+    <mergeCell ref="E116:E119"/>
+    <mergeCell ref="E120:E123"/>
+    <mergeCell ref="E128:F134"/>
+    <mergeCell ref="E124:E127"/>
+    <mergeCell ref="D108:D127"/>
+    <mergeCell ref="B4:B171"/>
+    <mergeCell ref="E140:E142"/>
+    <mergeCell ref="E153:E155"/>
+    <mergeCell ref="E156:E158"/>
+    <mergeCell ref="E159:E161"/>
+    <mergeCell ref="E162:E164"/>
+    <mergeCell ref="E57:E60"/>
+    <mergeCell ref="E81:E84"/>
+    <mergeCell ref="E61:E64"/>
+    <mergeCell ref="E85:E88"/>
+    <mergeCell ref="E65:E68"/>
+    <mergeCell ref="E89:E92"/>
+    <mergeCell ref="E69:E72"/>
+    <mergeCell ref="E93:E96"/>
+    <mergeCell ref="C153:C171"/>
+    <mergeCell ref="D153:D164"/>
     <mergeCell ref="E165:F171"/>
     <mergeCell ref="C53:C107"/>
     <mergeCell ref="D53:D100"/>
@@ -13810,40 +13850,6 @@
     <mergeCell ref="C108:C134"/>
     <mergeCell ref="E108:E111"/>
     <mergeCell ref="E112:E115"/>
-    <mergeCell ref="B4:B171"/>
-    <mergeCell ref="E140:E142"/>
-    <mergeCell ref="E153:E155"/>
-    <mergeCell ref="E156:E158"/>
-    <mergeCell ref="E159:E161"/>
-    <mergeCell ref="E162:E164"/>
-    <mergeCell ref="E57:E60"/>
-    <mergeCell ref="E81:E84"/>
-    <mergeCell ref="E61:E64"/>
-    <mergeCell ref="E85:E88"/>
-    <mergeCell ref="E65:E68"/>
-    <mergeCell ref="E89:E92"/>
-    <mergeCell ref="E69:E72"/>
-    <mergeCell ref="E93:E96"/>
-    <mergeCell ref="C153:C171"/>
-    <mergeCell ref="D153:D164"/>
-    <mergeCell ref="E116:E119"/>
-    <mergeCell ref="E120:E123"/>
-    <mergeCell ref="E128:F134"/>
-    <mergeCell ref="E124:E127"/>
-    <mergeCell ref="D108:D127"/>
-    <mergeCell ref="E4:E7"/>
-    <mergeCell ref="E8:E13"/>
-    <mergeCell ref="E14:E22"/>
-    <mergeCell ref="D4:D22"/>
-    <mergeCell ref="C4:C29"/>
-    <mergeCell ref="E23:F29"/>
-    <mergeCell ref="C30:C52"/>
-    <mergeCell ref="D30:D45"/>
-    <mergeCell ref="E30:E33"/>
-    <mergeCell ref="E34:E37"/>
-    <mergeCell ref="E38:E41"/>
-    <mergeCell ref="E42:E45"/>
-    <mergeCell ref="E46:F52"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13932,19 +13938,19 @@
     </row>
     <row r="5" spans="1:11" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="3"/>
-      <c r="B5" s="107" t="s">
+      <c r="B5" s="151" t="s">
         <v>239</v>
       </c>
       <c r="C5" s="28"/>
-      <c r="D5" s="99" t="s">
+      <c r="D5" s="154" t="s">
         <v>26</v>
       </c>
       <c r="E5" s="28"/>
-      <c r="F5" s="113" t="s">
+      <c r="F5" s="155" t="s">
         <v>27</v>
       </c>
       <c r="G5" s="28"/>
-      <c r="H5" s="108" t="s">
+      <c r="H5" s="156" t="s">
         <v>35</v>
       </c>
       <c r="I5" s="45">
@@ -13954,13 +13960,13 @@
     </row>
     <row r="6" spans="1:11" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="3"/>
-      <c r="B6" s="100"/>
+      <c r="B6" s="152"/>
       <c r="C6" s="28"/>
-      <c r="D6" s="100"/>
+      <c r="D6" s="152"/>
       <c r="E6" s="28"/>
-      <c r="F6" s="113"/>
+      <c r="F6" s="155"/>
       <c r="G6" s="28"/>
-      <c r="H6" s="109"/>
+      <c r="H6" s="157"/>
       <c r="I6" s="46">
         <v>0.55000000000000004</v>
       </c>
@@ -13968,13 +13974,13 @@
     </row>
     <row r="7" spans="1:11" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="3"/>
-      <c r="B7" s="100"/>
+      <c r="B7" s="152"/>
       <c r="C7" s="28"/>
-      <c r="D7" s="100"/>
+      <c r="D7" s="152"/>
       <c r="E7" s="28"/>
-      <c r="F7" s="113"/>
+      <c r="F7" s="155"/>
       <c r="G7" s="28"/>
-      <c r="H7" s="114"/>
+      <c r="H7" s="158"/>
       <c r="I7" s="46">
         <v>0.6</v>
       </c>
@@ -13982,13 +13988,13 @@
     </row>
     <row r="8" spans="1:11" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="3"/>
-      <c r="B8" s="100"/>
+      <c r="B8" s="152"/>
       <c r="C8" s="28"/>
-      <c r="D8" s="100"/>
+      <c r="D8" s="152"/>
       <c r="E8" s="28"/>
-      <c r="F8" s="113"/>
+      <c r="F8" s="155"/>
       <c r="G8" s="28"/>
-      <c r="H8" s="110"/>
+      <c r="H8" s="159"/>
       <c r="I8" s="47">
         <v>0.6</v>
       </c>
@@ -13996,11 +14002,11 @@
     </row>
     <row r="9" spans="1:11" ht="4.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="3"/>
-      <c r="B9" s="100"/>
+      <c r="B9" s="152"/>
       <c r="C9" s="28"/>
-      <c r="D9" s="100"/>
+      <c r="D9" s="152"/>
       <c r="E9" s="28"/>
-      <c r="F9" s="113"/>
+      <c r="F9" s="155"/>
       <c r="G9" s="28"/>
       <c r="H9" s="28"/>
       <c r="I9" s="30"/>
@@ -14009,13 +14015,13 @@
     </row>
     <row r="10" spans="1:11" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="3"/>
-      <c r="B10" s="100"/>
+      <c r="B10" s="152"/>
       <c r="C10" s="28"/>
-      <c r="D10" s="100"/>
+      <c r="D10" s="152"/>
       <c r="E10" s="28"/>
-      <c r="F10" s="113"/>
+      <c r="F10" s="155"/>
       <c r="G10" s="28"/>
-      <c r="H10" s="108" t="s">
+      <c r="H10" s="156" t="s">
         <v>36</v>
       </c>
       <c r="I10" s="41">
@@ -14025,13 +14031,13 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A11" s="3"/>
-      <c r="B11" s="101"/>
+      <c r="B11" s="153"/>
       <c r="C11" s="28"/>
-      <c r="D11" s="100"/>
+      <c r="D11" s="152"/>
       <c r="E11" s="28"/>
-      <c r="F11" s="113"/>
+      <c r="F11" s="155"/>
       <c r="G11" s="28"/>
-      <c r="H11" s="109"/>
+      <c r="H11" s="157"/>
       <c r="I11" s="42" t="s">
         <v>230</v>
       </c>
@@ -14041,11 +14047,11 @@
       <c r="A12" s="3"/>
       <c r="B12" s="32"/>
       <c r="C12" s="28"/>
-      <c r="D12" s="100"/>
+      <c r="D12" s="152"/>
       <c r="E12" s="28"/>
-      <c r="F12" s="113"/>
+      <c r="F12" s="155"/>
       <c r="G12" s="28"/>
-      <c r="H12" s="110"/>
+      <c r="H12" s="159"/>
       <c r="I12" s="44">
         <v>0.95</v>
       </c>
@@ -14055,9 +14061,9 @@
       <c r="A13" s="3"/>
       <c r="B13" s="32"/>
       <c r="C13" s="28"/>
-      <c r="D13" s="100"/>
+      <c r="D13" s="152"/>
       <c r="E13" s="28"/>
-      <c r="F13" s="113"/>
+      <c r="F13" s="155"/>
       <c r="G13" s="28"/>
       <c r="H13" s="28"/>
       <c r="I13" s="30"/>
@@ -14068,11 +14074,11 @@
       <c r="A14" s="3"/>
       <c r="B14" s="31"/>
       <c r="C14" s="28"/>
-      <c r="D14" s="100"/>
+      <c r="D14" s="152"/>
       <c r="E14" s="28"/>
-      <c r="F14" s="113"/>
+      <c r="F14" s="155"/>
       <c r="G14" s="28"/>
-      <c r="H14" s="108" t="s">
+      <c r="H14" s="156" t="s">
         <v>37</v>
       </c>
       <c r="I14" s="41">
@@ -14082,15 +14088,15 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A15" s="3"/>
-      <c r="B15" s="99" t="s">
+      <c r="B15" s="154" t="s">
         <v>183</v>
       </c>
       <c r="C15" s="28"/>
-      <c r="D15" s="100"/>
+      <c r="D15" s="152"/>
       <c r="E15" s="28"/>
-      <c r="F15" s="113"/>
+      <c r="F15" s="155"/>
       <c r="G15" s="28"/>
-      <c r="H15" s="109"/>
+      <c r="H15" s="157"/>
       <c r="I15" s="42" t="s">
         <v>230</v>
       </c>
@@ -14098,13 +14104,13 @@
     </row>
     <row r="16" spans="1:11" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="3"/>
-      <c r="B16" s="100"/>
+      <c r="B16" s="152"/>
       <c r="C16" s="28"/>
-      <c r="D16" s="100"/>
+      <c r="D16" s="152"/>
       <c r="E16" s="28"/>
-      <c r="F16" s="113"/>
+      <c r="F16" s="155"/>
       <c r="G16" s="28"/>
-      <c r="H16" s="110"/>
+      <c r="H16" s="159"/>
       <c r="I16" s="43">
         <v>0.995</v>
       </c>
@@ -14112,9 +14118,9 @@
     </row>
     <row r="17" spans="1:11" ht="4.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="3"/>
-      <c r="B17" s="100"/>
+      <c r="B17" s="152"/>
       <c r="C17" s="28"/>
-      <c r="D17" s="100"/>
+      <c r="D17" s="152"/>
       <c r="E17" s="28"/>
       <c r="F17" s="19"/>
       <c r="G17" s="28"/>
@@ -14125,181 +14131,181 @@
     </row>
     <row r="18" spans="1:11" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="3"/>
-      <c r="B18" s="100"/>
+      <c r="B18" s="152"/>
       <c r="C18" s="28"/>
-      <c r="D18" s="100"/>
+      <c r="D18" s="152"/>
       <c r="E18" s="28"/>
       <c r="F18" s="40" t="s">
         <v>28</v>
       </c>
       <c r="G18" s="28"/>
-      <c r="H18" s="115" t="s">
+      <c r="H18" s="160" t="s">
         <v>241</v>
       </c>
-      <c r="I18" s="116"/>
+      <c r="I18" s="161"/>
       <c r="J18" s="3"/>
     </row>
     <row r="19" spans="1:11" ht="4.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="3"/>
-      <c r="B19" s="100"/>
+      <c r="B19" s="152"/>
       <c r="C19" s="28"/>
-      <c r="D19" s="100"/>
+      <c r="D19" s="152"/>
       <c r="E19" s="28"/>
       <c r="F19" s="19"/>
       <c r="G19" s="28"/>
-      <c r="H19" s="115"/>
-      <c r="I19" s="116"/>
+      <c r="H19" s="160"/>
+      <c r="I19" s="161"/>
       <c r="J19" s="3"/>
     </row>
     <row r="20" spans="1:11" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="3"/>
-      <c r="B20" s="100"/>
+      <c r="B20" s="152"/>
       <c r="C20" s="28"/>
-      <c r="D20" s="100"/>
+      <c r="D20" s="152"/>
       <c r="E20" s="28"/>
       <c r="F20" s="40" t="s">
         <v>29</v>
       </c>
       <c r="G20" s="28"/>
-      <c r="H20" s="116"/>
-      <c r="I20" s="116"/>
+      <c r="H20" s="161"/>
+      <c r="I20" s="161"/>
       <c r="J20" s="3"/>
     </row>
     <row r="21" spans="1:11" ht="4.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="3"/>
-      <c r="B21" s="100"/>
+      <c r="B21" s="152"/>
       <c r="C21" s="28"/>
-      <c r="D21" s="100"/>
+      <c r="D21" s="152"/>
       <c r="E21" s="28"/>
       <c r="F21" s="19"/>
       <c r="G21" s="28"/>
-      <c r="H21" s="116"/>
-      <c r="I21" s="116"/>
+      <c r="H21" s="161"/>
+      <c r="I21" s="161"/>
       <c r="J21" s="3"/>
     </row>
     <row r="22" spans="1:11" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="3"/>
-      <c r="B22" s="100"/>
+      <c r="B22" s="152"/>
       <c r="C22" s="28"/>
-      <c r="D22" s="100"/>
+      <c r="D22" s="152"/>
       <c r="E22" s="28"/>
       <c r="F22" s="40" t="s">
         <v>30</v>
       </c>
       <c r="G22" s="28"/>
-      <c r="H22" s="116"/>
-      <c r="I22" s="116"/>
+      <c r="H22" s="161"/>
+      <c r="I22" s="161"/>
       <c r="J22" s="3"/>
     </row>
     <row r="23" spans="1:11" ht="4.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="3"/>
-      <c r="B23" s="100"/>
+      <c r="B23" s="152"/>
       <c r="C23" s="28"/>
-      <c r="D23" s="100"/>
+      <c r="D23" s="152"/>
       <c r="E23" s="28"/>
       <c r="F23" s="19"/>
       <c r="G23" s="28"/>
-      <c r="H23" s="116"/>
-      <c r="I23" s="116"/>
+      <c r="H23" s="161"/>
+      <c r="I23" s="161"/>
       <c r="J23" s="3"/>
     </row>
     <row r="24" spans="1:11" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="3"/>
-      <c r="B24" s="100"/>
+      <c r="B24" s="152"/>
       <c r="C24" s="28"/>
-      <c r="D24" s="100"/>
+      <c r="D24" s="152"/>
       <c r="E24" s="28"/>
       <c r="F24" s="40" t="s">
         <v>31</v>
       </c>
       <c r="G24" s="28"/>
-      <c r="H24" s="116"/>
-      <c r="I24" s="116"/>
+      <c r="H24" s="161"/>
+      <c r="I24" s="161"/>
       <c r="J24" s="3"/>
     </row>
     <row r="25" spans="1:11" ht="4.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="3"/>
-      <c r="B25" s="100"/>
+      <c r="B25" s="152"/>
       <c r="C25" s="28"/>
-      <c r="D25" s="100"/>
+      <c r="D25" s="152"/>
       <c r="E25" s="28"/>
       <c r="F25" s="19"/>
       <c r="G25" s="28"/>
-      <c r="H25" s="116"/>
-      <c r="I25" s="116"/>
+      <c r="H25" s="161"/>
+      <c r="I25" s="161"/>
       <c r="J25" s="3"/>
     </row>
     <row r="26" spans="1:11" ht="9.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="3"/>
-      <c r="B26" s="100"/>
+      <c r="B26" s="152"/>
       <c r="C26" s="28"/>
-      <c r="D26" s="100"/>
+      <c r="D26" s="152"/>
       <c r="E26" s="28"/>
       <c r="F26" s="40" t="s">
         <v>32</v>
       </c>
       <c r="G26" s="28"/>
-      <c r="H26" s="116"/>
-      <c r="I26" s="116"/>
+      <c r="H26" s="161"/>
+      <c r="I26" s="161"/>
       <c r="J26" s="3"/>
     </row>
     <row r="27" spans="1:11" ht="4.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="3"/>
-      <c r="B27" s="100"/>
+      <c r="B27" s="152"/>
       <c r="C27" s="28"/>
-      <c r="D27" s="100"/>
+      <c r="D27" s="152"/>
       <c r="E27" s="28"/>
       <c r="F27" s="19"/>
       <c r="G27" s="28"/>
-      <c r="H27" s="116"/>
-      <c r="I27" s="116"/>
+      <c r="H27" s="161"/>
+      <c r="I27" s="161"/>
       <c r="J27" s="3"/>
     </row>
     <row r="28" spans="1:11" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="3"/>
-      <c r="B28" s="100"/>
+      <c r="B28" s="152"/>
       <c r="C28" s="28"/>
-      <c r="D28" s="100"/>
+      <c r="D28" s="152"/>
       <c r="E28" s="28"/>
       <c r="F28" s="40" t="s">
         <v>33</v>
       </c>
       <c r="G28" s="28"/>
-      <c r="H28" s="116"/>
-      <c r="I28" s="116"/>
+      <c r="H28" s="161"/>
+      <c r="I28" s="161"/>
       <c r="J28" s="3"/>
     </row>
     <row r="29" spans="1:11" ht="4.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="3"/>
-      <c r="B29" s="100"/>
+      <c r="B29" s="152"/>
       <c r="C29" s="28"/>
-      <c r="D29" s="100"/>
+      <c r="D29" s="152"/>
       <c r="E29" s="28"/>
       <c r="F29" s="19"/>
       <c r="G29" s="28"/>
-      <c r="H29" s="116"/>
-      <c r="I29" s="116"/>
+      <c r="H29" s="161"/>
+      <c r="I29" s="161"/>
       <c r="J29" s="3"/>
     </row>
     <row r="30" spans="1:11" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="3"/>
-      <c r="B30" s="100"/>
+      <c r="B30" s="152"/>
       <c r="C30" s="28"/>
-      <c r="D30" s="100"/>
+      <c r="D30" s="152"/>
       <c r="E30" s="28"/>
       <c r="F30" s="40" t="s">
         <v>34</v>
       </c>
       <c r="G30" s="28"/>
-      <c r="H30" s="116"/>
-      <c r="I30" s="116"/>
+      <c r="H30" s="161"/>
+      <c r="I30" s="161"/>
       <c r="J30" s="3"/>
     </row>
     <row r="31" spans="1:11" ht="4.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="3"/>
-      <c r="B31" s="100"/>
+      <c r="B31" s="152"/>
       <c r="C31" s="28"/>
-      <c r="D31" s="100"/>
+      <c r="D31" s="152"/>
       <c r="E31" s="28"/>
       <c r="F31" s="28"/>
       <c r="G31" s="28"/>
@@ -14310,27 +14316,27 @@
     </row>
     <row r="32" spans="1:11" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="3"/>
-      <c r="B32" s="100"/>
+      <c r="B32" s="152"/>
       <c r="C32" s="28"/>
-      <c r="D32" s="100"/>
+      <c r="D32" s="152"/>
       <c r="E32" s="28"/>
-      <c r="F32" s="99" t="s">
+      <c r="F32" s="154" t="s">
         <v>234</v>
       </c>
       <c r="G32" s="28"/>
-      <c r="H32" s="111" t="s">
+      <c r="H32" s="162" t="s">
         <v>238</v>
       </c>
-      <c r="I32" s="112"/>
+      <c r="I32" s="163"/>
       <c r="J32" s="3"/>
     </row>
     <row r="33" spans="1:11" ht="4.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="3"/>
-      <c r="B33" s="100"/>
+      <c r="B33" s="152"/>
       <c r="C33" s="28"/>
-      <c r="D33" s="100"/>
+      <c r="D33" s="152"/>
       <c r="E33" s="28"/>
-      <c r="F33" s="100"/>
+      <c r="F33" s="152"/>
       <c r="G33" s="28"/>
       <c r="H33" s="28"/>
       <c r="I33" s="28"/>
@@ -14339,25 +14345,25 @@
     </row>
     <row r="34" spans="1:11" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="3"/>
-      <c r="B34" s="100"/>
+      <c r="B34" s="152"/>
       <c r="C34" s="28"/>
-      <c r="D34" s="100"/>
+      <c r="D34" s="152"/>
       <c r="E34" s="28"/>
-      <c r="F34" s="100"/>
+      <c r="F34" s="152"/>
       <c r="G34" s="28"/>
-      <c r="H34" s="111" t="s">
+      <c r="H34" s="162" t="s">
         <v>237</v>
       </c>
-      <c r="I34" s="112"/>
+      <c r="I34" s="163"/>
       <c r="J34" s="3"/>
     </row>
     <row r="35" spans="1:11" ht="4.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="3"/>
-      <c r="B35" s="100"/>
+      <c r="B35" s="152"/>
       <c r="C35" s="28"/>
-      <c r="D35" s="100"/>
+      <c r="D35" s="152"/>
       <c r="E35" s="28"/>
-      <c r="F35" s="100"/>
+      <c r="F35" s="152"/>
       <c r="G35" s="28"/>
       <c r="H35" s="31"/>
       <c r="I35" s="19"/>
@@ -14366,25 +14372,25 @@
     </row>
     <row r="36" spans="1:11" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="3"/>
-      <c r="B36" s="100"/>
+      <c r="B36" s="152"/>
       <c r="C36" s="28"/>
-      <c r="D36" s="100"/>
+      <c r="D36" s="152"/>
       <c r="E36" s="28"/>
-      <c r="F36" s="100"/>
+      <c r="F36" s="152"/>
       <c r="G36" s="28"/>
-      <c r="H36" s="111" t="s">
+      <c r="H36" s="162" t="s">
         <v>236</v>
       </c>
-      <c r="I36" s="112"/>
+      <c r="I36" s="163"/>
       <c r="J36" s="3"/>
     </row>
     <row r="37" spans="1:11" ht="4.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="3"/>
-      <c r="B37" s="100"/>
+      <c r="B37" s="152"/>
       <c r="C37" s="28"/>
-      <c r="D37" s="100"/>
+      <c r="D37" s="152"/>
       <c r="E37" s="28"/>
-      <c r="F37" s="100"/>
+      <c r="F37" s="152"/>
       <c r="G37" s="28"/>
       <c r="H37" s="19"/>
       <c r="I37" s="19"/>
@@ -14393,16 +14399,16 @@
     </row>
     <row r="38" spans="1:11" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="3"/>
-      <c r="B38" s="100"/>
+      <c r="B38" s="152"/>
       <c r="C38" s="28"/>
-      <c r="D38" s="101"/>
+      <c r="D38" s="153"/>
       <c r="E38" s="28"/>
-      <c r="F38" s="101"/>
+      <c r="F38" s="153"/>
       <c r="G38" s="28"/>
-      <c r="H38" s="111" t="s">
+      <c r="H38" s="162" t="s">
         <v>235</v>
       </c>
-      <c r="I38" s="112"/>
+      <c r="I38" s="163"/>
       <c r="J38" s="3"/>
     </row>
     <row r="39" spans="1:11" ht="10.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
@@ -14448,15 +14454,15 @@
       <c r="A42" s="3"/>
       <c r="B42" s="52"/>
       <c r="C42" s="28"/>
-      <c r="D42" s="99" t="s">
+      <c r="D42" s="154" t="s">
         <v>0</v>
       </c>
       <c r="E42" s="21"/>
-      <c r="F42" s="102" t="s">
+      <c r="F42" s="164" t="s">
         <v>1</v>
       </c>
       <c r="G42" s="23"/>
-      <c r="H42" s="103" t="s">
+      <c r="H42" s="165" t="s">
         <v>2</v>
       </c>
       <c r="I42" s="22" t="s">
@@ -14468,11 +14474,11 @@
       <c r="A43" s="3"/>
       <c r="B43" s="52"/>
       <c r="C43" s="28"/>
-      <c r="D43" s="100"/>
+      <c r="D43" s="152"/>
       <c r="E43" s="21"/>
-      <c r="F43" s="102"/>
+      <c r="F43" s="164"/>
       <c r="G43" s="23"/>
-      <c r="H43" s="104"/>
+      <c r="H43" s="166"/>
       <c r="I43" s="50" t="s">
         <v>230</v>
       </c>
@@ -14482,11 +14488,11 @@
       <c r="A44" s="3"/>
       <c r="B44" s="52"/>
       <c r="C44" s="28"/>
-      <c r="D44" s="100"/>
+      <c r="D44" s="152"/>
       <c r="E44" s="21"/>
-      <c r="F44" s="102"/>
+      <c r="F44" s="164"/>
       <c r="G44" s="23"/>
-      <c r="H44" s="105"/>
+      <c r="H44" s="167"/>
       <c r="I44" s="24" t="s">
         <v>6</v>
       </c>
@@ -14496,9 +14502,9 @@
       <c r="A45" s="3"/>
       <c r="B45" s="52"/>
       <c r="C45" s="28"/>
-      <c r="D45" s="100"/>
+      <c r="D45" s="152"/>
       <c r="E45" s="21"/>
-      <c r="F45" s="102"/>
+      <c r="F45" s="164"/>
       <c r="G45" s="25"/>
       <c r="H45" s="33"/>
       <c r="I45" s="33"/>
@@ -14508,11 +14514,11 @@
       <c r="A46" s="3"/>
       <c r="B46" s="52"/>
       <c r="C46" s="28"/>
-      <c r="D46" s="100"/>
+      <c r="D46" s="152"/>
       <c r="E46" s="21"/>
-      <c r="F46" s="102"/>
+      <c r="F46" s="164"/>
       <c r="G46" s="23"/>
-      <c r="H46" s="103" t="s">
+      <c r="H46" s="165" t="s">
         <v>7</v>
       </c>
       <c r="I46" s="22" t="s">
@@ -14524,11 +14530,11 @@
       <c r="A47" s="3"/>
       <c r="B47" s="52"/>
       <c r="C47" s="28"/>
-      <c r="D47" s="100"/>
+      <c r="D47" s="152"/>
       <c r="E47" s="21"/>
-      <c r="F47" s="102"/>
+      <c r="F47" s="164"/>
       <c r="G47" s="23"/>
-      <c r="H47" s="104"/>
+      <c r="H47" s="166"/>
       <c r="I47" s="50" t="s">
         <v>230</v>
       </c>
@@ -14538,11 +14544,11 @@
       <c r="A48" s="3"/>
       <c r="B48" s="52"/>
       <c r="C48" s="28"/>
-      <c r="D48" s="100"/>
+      <c r="D48" s="152"/>
       <c r="E48" s="21"/>
-      <c r="F48" s="102"/>
+      <c r="F48" s="164"/>
       <c r="G48" s="23"/>
-      <c r="H48" s="105"/>
+      <c r="H48" s="167"/>
       <c r="I48" s="24" t="s">
         <v>6</v>
       </c>
@@ -14552,9 +14558,9 @@
       <c r="A49" s="3"/>
       <c r="B49" s="52"/>
       <c r="C49" s="28"/>
-      <c r="D49" s="100"/>
+      <c r="D49" s="152"/>
       <c r="E49" s="21"/>
-      <c r="F49" s="102"/>
+      <c r="F49" s="164"/>
       <c r="G49" s="25"/>
       <c r="H49" s="33"/>
       <c r="I49" s="33"/>
@@ -14564,11 +14570,11 @@
       <c r="A50" s="3"/>
       <c r="B50" s="52"/>
       <c r="C50" s="28"/>
-      <c r="D50" s="100"/>
+      <c r="D50" s="152"/>
       <c r="E50" s="21"/>
-      <c r="F50" s="102"/>
+      <c r="F50" s="164"/>
       <c r="G50" s="23"/>
-      <c r="H50" s="103" t="s">
+      <c r="H50" s="165" t="s">
         <v>8</v>
       </c>
       <c r="I50" s="22" t="s">
@@ -14580,11 +14586,11 @@
       <c r="A51" s="3"/>
       <c r="B51" s="52"/>
       <c r="C51" s="28"/>
-      <c r="D51" s="100"/>
+      <c r="D51" s="152"/>
       <c r="E51" s="21"/>
-      <c r="F51" s="102"/>
+      <c r="F51" s="164"/>
       <c r="G51" s="23"/>
-      <c r="H51" s="104"/>
+      <c r="H51" s="166"/>
       <c r="I51" s="50" t="s">
         <v>230</v>
       </c>
@@ -14594,11 +14600,11 @@
       <c r="A52" s="3"/>
       <c r="B52" s="52"/>
       <c r="C52" s="28"/>
-      <c r="D52" s="100"/>
+      <c r="D52" s="152"/>
       <c r="E52" s="21"/>
-      <c r="F52" s="102"/>
+      <c r="F52" s="164"/>
       <c r="G52" s="23"/>
-      <c r="H52" s="105"/>
+      <c r="H52" s="167"/>
       <c r="I52" s="24" t="s">
         <v>6</v>
       </c>
@@ -14608,9 +14614,9 @@
       <c r="A53" s="3"/>
       <c r="B53" s="52"/>
       <c r="C53" s="28"/>
-      <c r="D53" s="100"/>
+      <c r="D53" s="152"/>
       <c r="E53" s="21"/>
-      <c r="F53" s="102"/>
+      <c r="F53" s="164"/>
       <c r="G53" s="25"/>
       <c r="H53" s="33"/>
       <c r="I53" s="33"/>
@@ -14620,11 +14626,11 @@
       <c r="A54" s="3"/>
       <c r="B54" s="52"/>
       <c r="C54" s="28"/>
-      <c r="D54" s="100"/>
+      <c r="D54" s="152"/>
       <c r="E54" s="21"/>
-      <c r="F54" s="102"/>
+      <c r="F54" s="164"/>
       <c r="G54" s="23"/>
-      <c r="H54" s="103" t="s">
+      <c r="H54" s="165" t="s">
         <v>9</v>
       </c>
       <c r="I54" s="22" t="s">
@@ -14636,11 +14642,11 @@
       <c r="A55" s="3"/>
       <c r="B55" s="52"/>
       <c r="C55" s="28"/>
-      <c r="D55" s="100"/>
+      <c r="D55" s="152"/>
       <c r="E55" s="21"/>
-      <c r="F55" s="102"/>
+      <c r="F55" s="164"/>
       <c r="G55" s="23"/>
-      <c r="H55" s="104"/>
+      <c r="H55" s="166"/>
       <c r="I55" s="50" t="s">
         <v>230</v>
       </c>
@@ -14650,11 +14656,11 @@
       <c r="A56" s="3"/>
       <c r="B56" s="52"/>
       <c r="C56" s="28"/>
-      <c r="D56" s="100"/>
+      <c r="D56" s="152"/>
       <c r="E56" s="21"/>
-      <c r="F56" s="102"/>
+      <c r="F56" s="164"/>
       <c r="G56" s="23"/>
-      <c r="H56" s="105"/>
+      <c r="H56" s="167"/>
       <c r="I56" s="24" t="s">
         <v>6</v>
       </c>
@@ -14664,7 +14670,7 @@
       <c r="A57" s="3"/>
       <c r="B57" s="52"/>
       <c r="C57" s="28"/>
-      <c r="D57" s="100"/>
+      <c r="D57" s="152"/>
       <c r="E57" s="28"/>
       <c r="F57" s="34"/>
       <c r="G57" s="33"/>
@@ -14676,179 +14682,179 @@
       <c r="A58" s="3"/>
       <c r="B58" s="52"/>
       <c r="C58" s="28"/>
-      <c r="D58" s="100"/>
+      <c r="D58" s="152"/>
       <c r="E58" s="21"/>
       <c r="F58" s="20" t="s">
         <v>10</v>
       </c>
       <c r="G58" s="25"/>
-      <c r="H58" s="106" t="s">
+      <c r="H58" s="168" t="s">
         <v>241</v>
       </c>
-      <c r="I58" s="106"/>
+      <c r="I58" s="168"/>
       <c r="J58" s="3"/>
     </row>
     <row r="59" spans="1:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="3"/>
       <c r="B59" s="52"/>
       <c r="C59" s="28"/>
-      <c r="D59" s="100"/>
+      <c r="D59" s="152"/>
       <c r="E59" s="28"/>
       <c r="F59" s="34"/>
       <c r="G59" s="33"/>
-      <c r="H59" s="106"/>
-      <c r="I59" s="106"/>
+      <c r="H59" s="168"/>
+      <c r="I59" s="168"/>
       <c r="J59" s="3"/>
     </row>
     <row r="60" spans="1:10" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="3"/>
       <c r="B60" s="52"/>
       <c r="C60" s="28"/>
-      <c r="D60" s="100"/>
+      <c r="D60" s="152"/>
       <c r="E60" s="21"/>
       <c r="F60" s="20" t="s">
         <v>12</v>
       </c>
       <c r="G60" s="25"/>
-      <c r="H60" s="106"/>
-      <c r="I60" s="106"/>
+      <c r="H60" s="168"/>
+      <c r="I60" s="168"/>
       <c r="J60" s="3"/>
     </row>
     <row r="61" spans="1:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="3"/>
       <c r="B61" s="52"/>
       <c r="C61" s="28"/>
-      <c r="D61" s="100"/>
+      <c r="D61" s="152"/>
       <c r="E61" s="28"/>
       <c r="F61" s="34"/>
       <c r="G61" s="33"/>
-      <c r="H61" s="106"/>
-      <c r="I61" s="106"/>
+      <c r="H61" s="168"/>
+      <c r="I61" s="168"/>
       <c r="J61" s="3"/>
     </row>
     <row r="62" spans="1:10" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="3"/>
       <c r="B62" s="52"/>
       <c r="C62" s="28"/>
-      <c r="D62" s="100"/>
+      <c r="D62" s="152"/>
       <c r="E62" s="21"/>
       <c r="F62" s="20" t="s">
         <v>13</v>
       </c>
       <c r="G62" s="25"/>
-      <c r="H62" s="106"/>
-      <c r="I62" s="106"/>
+      <c r="H62" s="168"/>
+      <c r="I62" s="168"/>
       <c r="J62" s="3"/>
     </row>
     <row r="63" spans="1:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="3"/>
       <c r="B63" s="52"/>
       <c r="C63" s="28"/>
-      <c r="D63" s="100"/>
+      <c r="D63" s="152"/>
       <c r="E63" s="28"/>
       <c r="F63" s="34"/>
       <c r="G63" s="33"/>
-      <c r="H63" s="106"/>
-      <c r="I63" s="106"/>
+      <c r="H63" s="168"/>
+      <c r="I63" s="168"/>
       <c r="J63" s="3"/>
     </row>
     <row r="64" spans="1:10" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="3"/>
       <c r="B64" s="52"/>
       <c r="C64" s="28"/>
-      <c r="D64" s="100"/>
+      <c r="D64" s="152"/>
       <c r="E64" s="21"/>
       <c r="F64" s="20" t="s">
         <v>14</v>
       </c>
       <c r="G64" s="25"/>
-      <c r="H64" s="106"/>
-      <c r="I64" s="106"/>
+      <c r="H64" s="168"/>
+      <c r="I64" s="168"/>
       <c r="J64" s="3"/>
     </row>
     <row r="65" spans="1:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="3"/>
       <c r="B65" s="52"/>
       <c r="C65" s="28"/>
-      <c r="D65" s="100"/>
+      <c r="D65" s="152"/>
       <c r="E65" s="28"/>
       <c r="F65" s="34"/>
       <c r="G65" s="33"/>
-      <c r="H65" s="106"/>
-      <c r="I65" s="106"/>
+      <c r="H65" s="168"/>
+      <c r="I65" s="168"/>
       <c r="J65" s="3"/>
     </row>
     <row r="66" spans="1:10" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="3"/>
       <c r="B66" s="52"/>
       <c r="C66" s="28"/>
-      <c r="D66" s="100"/>
+      <c r="D66" s="152"/>
       <c r="E66" s="21"/>
       <c r="F66" s="20" t="s">
         <v>15</v>
       </c>
       <c r="G66" s="25"/>
-      <c r="H66" s="106"/>
-      <c r="I66" s="106"/>
+      <c r="H66" s="168"/>
+      <c r="I66" s="168"/>
       <c r="J66" s="3"/>
     </row>
     <row r="67" spans="1:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" s="3"/>
       <c r="B67" s="52"/>
       <c r="C67" s="28"/>
-      <c r="D67" s="100"/>
+      <c r="D67" s="152"/>
       <c r="E67" s="28"/>
       <c r="F67" s="34"/>
       <c r="G67" s="33"/>
-      <c r="H67" s="106"/>
-      <c r="I67" s="106"/>
+      <c r="H67" s="168"/>
+      <c r="I67" s="168"/>
       <c r="J67" s="3"/>
     </row>
     <row r="68" spans="1:10" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="3"/>
       <c r="B68" s="52"/>
       <c r="C68" s="28"/>
-      <c r="D68" s="100"/>
+      <c r="D68" s="152"/>
       <c r="E68" s="21"/>
       <c r="F68" s="20" t="s">
         <v>16</v>
       </c>
       <c r="G68" s="25"/>
-      <c r="H68" s="106"/>
-      <c r="I68" s="106"/>
+      <c r="H68" s="168"/>
+      <c r="I68" s="168"/>
       <c r="J68" s="3"/>
     </row>
     <row r="69" spans="1:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69" s="3"/>
       <c r="B69" s="52"/>
       <c r="C69" s="28"/>
-      <c r="D69" s="100"/>
+      <c r="D69" s="152"/>
       <c r="E69" s="28"/>
       <c r="F69" s="34"/>
       <c r="G69" s="33"/>
-      <c r="H69" s="106"/>
-      <c r="I69" s="106"/>
+      <c r="H69" s="168"/>
+      <c r="I69" s="168"/>
       <c r="J69" s="3"/>
     </row>
     <row r="70" spans="1:10" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="3"/>
       <c r="B70" s="52"/>
       <c r="C70" s="28"/>
-      <c r="D70" s="100"/>
+      <c r="D70" s="152"/>
       <c r="E70" s="21"/>
       <c r="F70" s="20" t="s">
         <v>233</v>
       </c>
       <c r="G70" s="25"/>
-      <c r="H70" s="106"/>
-      <c r="I70" s="106"/>
+      <c r="H70" s="168"/>
+      <c r="I70" s="168"/>
       <c r="J70" s="3"/>
     </row>
     <row r="71" spans="1:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A71" s="3"/>
       <c r="B71" s="52"/>
       <c r="C71" s="28"/>
-      <c r="D71" s="100"/>
+      <c r="D71" s="152"/>
       <c r="E71" s="28"/>
       <c r="F71" s="35"/>
       <c r="G71" s="33"/>
@@ -14860,13 +14866,13 @@
       <c r="A72" s="3"/>
       <c r="B72" s="52"/>
       <c r="C72" s="28"/>
-      <c r="D72" s="100"/>
+      <c r="D72" s="152"/>
       <c r="E72" s="28"/>
-      <c r="F72" s="107" t="s">
+      <c r="F72" s="151" t="s">
         <v>232</v>
       </c>
       <c r="G72" s="39"/>
-      <c r="H72" s="108" t="s">
+      <c r="H72" s="156" t="s">
         <v>7</v>
       </c>
       <c r="I72" s="48" t="s">
@@ -14878,11 +14884,11 @@
       <c r="A73" s="3"/>
       <c r="B73" s="52"/>
       <c r="C73" s="28"/>
-      <c r="D73" s="100"/>
+      <c r="D73" s="152"/>
       <c r="E73" s="28"/>
-      <c r="F73" s="100"/>
+      <c r="F73" s="152"/>
       <c r="G73" s="28"/>
-      <c r="H73" s="109"/>
+      <c r="H73" s="157"/>
       <c r="I73" s="42" t="s">
         <v>230</v>
       </c>
@@ -14892,11 +14898,11 @@
       <c r="A74" s="3"/>
       <c r="B74" s="52"/>
       <c r="C74" s="28"/>
-      <c r="D74" s="100"/>
+      <c r="D74" s="152"/>
       <c r="E74" s="28"/>
-      <c r="F74" s="100"/>
+      <c r="F74" s="152"/>
       <c r="G74" s="28"/>
-      <c r="H74" s="110"/>
+      <c r="H74" s="159"/>
       <c r="I74" s="49" t="s">
         <v>6</v>
       </c>
@@ -14906,9 +14912,9 @@
       <c r="A75" s="3"/>
       <c r="B75" s="52"/>
       <c r="C75" s="28"/>
-      <c r="D75" s="100"/>
+      <c r="D75" s="152"/>
       <c r="E75" s="28"/>
-      <c r="F75" s="100"/>
+      <c r="F75" s="152"/>
       <c r="G75" s="28"/>
       <c r="H75" s="28"/>
       <c r="I75" s="28"/>
@@ -14918,11 +14924,11 @@
       <c r="A76" s="3"/>
       <c r="B76" s="52"/>
       <c r="C76" s="28"/>
-      <c r="D76" s="100"/>
+      <c r="D76" s="152"/>
       <c r="E76" s="28"/>
-      <c r="F76" s="100"/>
+      <c r="F76" s="152"/>
       <c r="G76" s="28"/>
-      <c r="H76" s="108" t="s">
+      <c r="H76" s="156" t="s">
         <v>8</v>
       </c>
       <c r="I76" s="48" t="s">
@@ -14934,11 +14940,11 @@
       <c r="A77" s="3"/>
       <c r="B77" s="52"/>
       <c r="C77" s="28"/>
-      <c r="D77" s="100"/>
+      <c r="D77" s="152"/>
       <c r="E77" s="28"/>
-      <c r="F77" s="100"/>
+      <c r="F77" s="152"/>
       <c r="G77" s="28"/>
-      <c r="H77" s="109"/>
+      <c r="H77" s="157"/>
       <c r="I77" s="42" t="s">
         <v>230</v>
       </c>
@@ -14948,11 +14954,11 @@
       <c r="A78" s="3"/>
       <c r="B78" s="52"/>
       <c r="C78" s="28"/>
-      <c r="D78" s="100"/>
+      <c r="D78" s="152"/>
       <c r="E78" s="28"/>
-      <c r="F78" s="101"/>
+      <c r="F78" s="153"/>
       <c r="G78" s="28"/>
-      <c r="H78" s="110"/>
+      <c r="H78" s="159"/>
       <c r="I78" s="49" t="s">
         <v>5</v>
       </c>
@@ -14962,7 +14968,7 @@
       <c r="A79" s="3"/>
       <c r="B79" s="52"/>
       <c r="C79" s="28"/>
-      <c r="D79" s="100"/>
+      <c r="D79" s="152"/>
       <c r="E79" s="28"/>
       <c r="F79" s="28"/>
       <c r="G79" s="28"/>
@@ -14974,14 +14980,14 @@
       <c r="A80" s="3"/>
       <c r="B80" s="52"/>
       <c r="C80" s="28"/>
-      <c r="D80" s="101"/>
+      <c r="D80" s="153"/>
       <c r="E80" s="28"/>
       <c r="F80" s="40" t="s">
         <v>240</v>
       </c>
       <c r="G80" s="28"/>
-      <c r="H80" s="111"/>
-      <c r="I80" s="112"/>
+      <c r="H80" s="162"/>
+      <c r="I80" s="163"/>
       <c r="J80" s="3"/>
     </row>
     <row r="81" spans="1:11" ht="4.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -15025,6 +15031,17 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="D42:D80"/>
+    <mergeCell ref="F42:F56"/>
+    <mergeCell ref="H42:H44"/>
+    <mergeCell ref="H46:H48"/>
+    <mergeCell ref="H50:H52"/>
+    <mergeCell ref="H54:H56"/>
+    <mergeCell ref="H58:I70"/>
+    <mergeCell ref="F72:F78"/>
+    <mergeCell ref="H72:H74"/>
+    <mergeCell ref="H76:H78"/>
+    <mergeCell ref="H80:I80"/>
     <mergeCell ref="B5:B11"/>
     <mergeCell ref="D5:D38"/>
     <mergeCell ref="F5:F16"/>
@@ -15038,17 +15055,6 @@
     <mergeCell ref="H34:I34"/>
     <mergeCell ref="H36:I36"/>
     <mergeCell ref="H38:I38"/>
-    <mergeCell ref="D42:D80"/>
-    <mergeCell ref="F42:F56"/>
-    <mergeCell ref="H42:H44"/>
-    <mergeCell ref="H46:H48"/>
-    <mergeCell ref="H50:H52"/>
-    <mergeCell ref="H54:H56"/>
-    <mergeCell ref="H58:I70"/>
-    <mergeCell ref="F72:F78"/>
-    <mergeCell ref="H72:H74"/>
-    <mergeCell ref="H76:H78"/>
-    <mergeCell ref="H80:I80"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -15083,89 +15089,89 @@
     </row>
     <row r="2" spans="1:9" ht="18.75" x14ac:dyDescent="0.15">
       <c r="A2" s="3"/>
-      <c r="B2" s="209" t="s">
+      <c r="B2" s="176" t="s">
         <v>182</v>
       </c>
-      <c r="C2" s="209"/>
-      <c r="D2" s="209"/>
-      <c r="E2" s="202"/>
-      <c r="F2" s="203"/>
+      <c r="C2" s="176"/>
+      <c r="D2" s="176"/>
+      <c r="E2" s="90"/>
+      <c r="F2" s="91"/>
       <c r="G2" s="3"/>
     </row>
     <row r="3" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="3"/>
-      <c r="B3" s="208" t="s">
+      <c r="B3" s="175" t="s">
         <v>92</v>
       </c>
-      <c r="C3" s="208"/>
-      <c r="D3" s="208"/>
-      <c r="E3" s="205"/>
-      <c r="F3" s="204" t="s">
+      <c r="C3" s="175"/>
+      <c r="D3" s="175"/>
+      <c r="E3" s="93"/>
+      <c r="F3" s="92" t="s">
         <v>94</v>
       </c>
       <c r="G3" s="3"/>
-      <c r="I3" s="194"/>
+      <c r="I3" s="83"/>
     </row>
     <row r="4" spans="1:9" s="27" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="26"/>
-      <c r="B4" s="202"/>
-      <c r="C4" s="202"/>
-      <c r="D4" s="205"/>
-      <c r="E4" s="205"/>
-      <c r="F4" s="205"/>
+      <c r="B4" s="90"/>
+      <c r="C4" s="90"/>
+      <c r="D4" s="93"/>
+      <c r="E4" s="93"/>
+      <c r="F4" s="93"/>
       <c r="G4" s="26"/>
     </row>
     <row r="5" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="3"/>
-      <c r="B5" s="217" t="s">
-        <v>303</v>
-      </c>
-      <c r="C5" s="201"/>
-      <c r="D5" s="216" t="s">
-        <v>301</v>
-      </c>
-      <c r="E5" s="206"/>
-      <c r="F5" s="212" t="s">
+      <c r="B5" s="172" t="s">
+        <v>302</v>
+      </c>
+      <c r="C5" s="89"/>
+      <c r="D5" s="169" t="s">
+        <v>300</v>
+      </c>
+      <c r="E5" s="94"/>
+      <c r="F5" s="96" t="s">
         <v>26</v>
       </c>
       <c r="G5" s="3"/>
     </row>
     <row r="6" spans="1:9" ht="3.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="3"/>
-      <c r="B6" s="214"/>
-      <c r="C6" s="201"/>
-      <c r="D6" s="210"/>
-      <c r="E6" s="205"/>
-      <c r="F6" s="207"/>
+      <c r="B6" s="173"/>
+      <c r="C6" s="89"/>
+      <c r="D6" s="170"/>
+      <c r="E6" s="93"/>
+      <c r="F6" s="95"/>
       <c r="G6" s="26"/>
     </row>
     <row r="7" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="3"/>
-      <c r="B7" s="214"/>
-      <c r="C7" s="201"/>
-      <c r="D7" s="210"/>
-      <c r="E7" s="206"/>
-      <c r="F7" s="213" t="s">
+      <c r="B7" s="173"/>
+      <c r="C7" s="89"/>
+      <c r="D7" s="170"/>
+      <c r="E7" s="94"/>
+      <c r="F7" s="97" t="s">
         <v>0</v>
       </c>
       <c r="G7" s="3"/>
     </row>
     <row r="8" spans="1:9" ht="3.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="3"/>
-      <c r="B8" s="214"/>
-      <c r="C8" s="201"/>
-      <c r="D8" s="210"/>
-      <c r="E8" s="205"/>
-      <c r="F8" s="207"/>
+      <c r="B8" s="173"/>
+      <c r="C8" s="89"/>
+      <c r="D8" s="170"/>
+      <c r="E8" s="93"/>
+      <c r="F8" s="95"/>
       <c r="G8" s="26"/>
     </row>
     <row r="9" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="3"/>
-      <c r="B9" s="215"/>
-      <c r="C9" s="201"/>
-      <c r="D9" s="211"/>
-      <c r="E9" s="205"/>
-      <c r="F9" s="274" t="s">
+      <c r="B9" s="174"/>
+      <c r="C9" s="89"/>
+      <c r="D9" s="171"/>
+      <c r="E9" s="93"/>
+      <c r="F9" s="134" t="s">
         <v>231</v>
       </c>
       <c r="G9" s="3"/>
@@ -15238,446 +15244,446 @@
     </row>
     <row r="2" spans="1:9" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A2" s="26"/>
-      <c r="B2" s="195" t="s">
+      <c r="B2" s="84" t="s">
         <v>243</v>
       </c>
-      <c r="C2" s="198"/>
-      <c r="D2" s="196"/>
-      <c r="E2" s="198"/>
-      <c r="F2" s="196"/>
-      <c r="G2" s="196"/>
+      <c r="C2" s="87"/>
+      <c r="D2" s="85"/>
+      <c r="E2" s="87"/>
+      <c r="F2" s="85"/>
+      <c r="G2" s="85"/>
       <c r="H2" s="3"/>
     </row>
     <row r="3" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="28"/>
-      <c r="B3" s="197" t="s">
+      <c r="B3" s="86" t="s">
         <v>94</v>
       </c>
-      <c r="C3" s="198"/>
-      <c r="D3" s="197" t="s">
+      <c r="C3" s="87"/>
+      <c r="D3" s="86" t="s">
         <v>95</v>
       </c>
-      <c r="E3" s="198"/>
-      <c r="F3" s="218" t="s">
+      <c r="E3" s="87"/>
+      <c r="F3" s="98" t="s">
         <v>244</v>
       </c>
-      <c r="G3" s="197" t="s">
+      <c r="G3" s="86" t="s">
         <v>96</v>
       </c>
       <c r="H3" s="3"/>
     </row>
     <row r="4" spans="1:9" ht="7.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="28"/>
-      <c r="B4" s="198"/>
-      <c r="C4" s="198"/>
-      <c r="D4" s="219"/>
-      <c r="E4" s="198"/>
-      <c r="F4" s="198"/>
-      <c r="G4" s="198"/>
+      <c r="B4" s="87"/>
+      <c r="C4" s="87"/>
+      <c r="D4" s="99"/>
+      <c r="E4" s="87"/>
+      <c r="F4" s="87"/>
+      <c r="G4" s="87"/>
       <c r="H4" s="26"/>
       <c r="I4" s="27"/>
     </row>
     <row r="5" spans="1:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="28"/>
-      <c r="B5" s="220" t="s">
+      <c r="B5" s="177" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="198"/>
-      <c r="D5" s="221" t="s">
+      <c r="C5" s="87"/>
+      <c r="D5" s="187" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="198"/>
-      <c r="F5" s="222" t="s">
+      <c r="E5" s="87"/>
+      <c r="F5" s="184" t="s">
         <v>35</v>
       </c>
-      <c r="G5" s="223">
+      <c r="G5" s="100">
         <v>0.5</v>
       </c>
       <c r="H5" s="3"/>
     </row>
     <row r="6" spans="1:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="28"/>
-      <c r="B6" s="224"/>
-      <c r="C6" s="198"/>
-      <c r="D6" s="221"/>
-      <c r="E6" s="198"/>
-      <c r="F6" s="225"/>
-      <c r="G6" s="226">
+      <c r="B6" s="178"/>
+      <c r="C6" s="87"/>
+      <c r="D6" s="187"/>
+      <c r="E6" s="87"/>
+      <c r="F6" s="185"/>
+      <c r="G6" s="101">
         <v>0.55000000000000004</v>
       </c>
       <c r="H6" s="3"/>
     </row>
     <row r="7" spans="1:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="28"/>
-      <c r="B7" s="224"/>
-      <c r="C7" s="198"/>
-      <c r="D7" s="221"/>
-      <c r="E7" s="198"/>
-      <c r="F7" s="227"/>
-      <c r="G7" s="226">
+      <c r="B7" s="178"/>
+      <c r="C7" s="87"/>
+      <c r="D7" s="187"/>
+      <c r="E7" s="87"/>
+      <c r="F7" s="188"/>
+      <c r="G7" s="101">
         <v>0.6</v>
       </c>
       <c r="H7" s="3"/>
     </row>
     <row r="8" spans="1:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="28"/>
-      <c r="B8" s="224"/>
-      <c r="C8" s="198"/>
-      <c r="D8" s="221"/>
-      <c r="E8" s="198"/>
-      <c r="F8" s="228"/>
-      <c r="G8" s="229">
+      <c r="B8" s="178"/>
+      <c r="C8" s="87"/>
+      <c r="D8" s="187"/>
+      <c r="E8" s="87"/>
+      <c r="F8" s="186"/>
+      <c r="G8" s="102">
         <v>0.6</v>
       </c>
       <c r="H8" s="3"/>
     </row>
     <row r="9" spans="1:9" ht="3" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="28"/>
-      <c r="B9" s="224"/>
-      <c r="C9" s="198"/>
-      <c r="D9" s="221"/>
-      <c r="E9" s="198"/>
-      <c r="F9" s="198"/>
-      <c r="G9" s="230"/>
+      <c r="B9" s="178"/>
+      <c r="C9" s="87"/>
+      <c r="D9" s="187"/>
+      <c r="E9" s="87"/>
+      <c r="F9" s="87"/>
+      <c r="G9" s="103"/>
       <c r="H9" s="26"/>
       <c r="I9" s="27"/>
     </row>
     <row r="10" spans="1:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="28"/>
-      <c r="B10" s="224"/>
-      <c r="C10" s="198"/>
-      <c r="D10" s="221"/>
-      <c r="E10" s="198"/>
-      <c r="F10" s="222" t="s">
+      <c r="B10" s="178"/>
+      <c r="C10" s="87"/>
+      <c r="D10" s="187"/>
+      <c r="E10" s="87"/>
+      <c r="F10" s="184" t="s">
         <v>36</v>
       </c>
-      <c r="G10" s="231">
+      <c r="G10" s="104">
         <v>0.7</v>
       </c>
       <c r="H10" s="3"/>
     </row>
     <row r="11" spans="1:9" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A11" s="28"/>
-      <c r="B11" s="224"/>
-      <c r="C11" s="198"/>
-      <c r="D11" s="221"/>
-      <c r="E11" s="198"/>
-      <c r="F11" s="225"/>
-      <c r="G11" s="242" t="s">
+      <c r="B11" s="178"/>
+      <c r="C11" s="87"/>
+      <c r="D11" s="187"/>
+      <c r="E11" s="87"/>
+      <c r="F11" s="185"/>
+      <c r="G11" s="110" t="s">
         <v>230</v>
       </c>
       <c r="H11" s="3"/>
     </row>
     <row r="12" spans="1:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="28"/>
-      <c r="B12" s="224"/>
-      <c r="C12" s="198"/>
-      <c r="D12" s="221"/>
-      <c r="E12" s="198"/>
-      <c r="F12" s="228"/>
-      <c r="G12" s="233">
+      <c r="B12" s="178"/>
+      <c r="C12" s="87"/>
+      <c r="D12" s="187"/>
+      <c r="E12" s="87"/>
+      <c r="F12" s="186"/>
+      <c r="G12" s="106">
         <v>0.95</v>
       </c>
       <c r="H12" s="3"/>
     </row>
     <row r="13" spans="1:9" ht="3" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="28"/>
-      <c r="B13" s="224"/>
-      <c r="C13" s="198"/>
-      <c r="D13" s="221"/>
-      <c r="E13" s="198"/>
-      <c r="F13" s="198"/>
-      <c r="G13" s="230"/>
+      <c r="B13" s="178"/>
+      <c r="C13" s="87"/>
+      <c r="D13" s="187"/>
+      <c r="E13" s="87"/>
+      <c r="F13" s="87"/>
+      <c r="G13" s="103"/>
       <c r="H13" s="26"/>
       <c r="I13" s="27"/>
     </row>
     <row r="14" spans="1:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="28"/>
-      <c r="B14" s="224"/>
-      <c r="C14" s="198"/>
-      <c r="D14" s="221"/>
-      <c r="E14" s="198"/>
-      <c r="F14" s="222" t="s">
+      <c r="B14" s="178"/>
+      <c r="C14" s="87"/>
+      <c r="D14" s="187"/>
+      <c r="E14" s="87"/>
+      <c r="F14" s="184" t="s">
         <v>37</v>
       </c>
-      <c r="G14" s="231">
+      <c r="G14" s="104">
         <v>0.9</v>
       </c>
       <c r="H14" s="3"/>
     </row>
     <row r="15" spans="1:9" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A15" s="28"/>
-      <c r="B15" s="224"/>
-      <c r="C15" s="198"/>
-      <c r="D15" s="221"/>
-      <c r="E15" s="198"/>
-      <c r="F15" s="225"/>
-      <c r="G15" s="242" t="s">
+      <c r="B15" s="178"/>
+      <c r="C15" s="87"/>
+      <c r="D15" s="187"/>
+      <c r="E15" s="87"/>
+      <c r="F15" s="185"/>
+      <c r="G15" s="110" t="s">
         <v>230</v>
       </c>
       <c r="H15" s="3"/>
     </row>
     <row r="16" spans="1:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="28"/>
-      <c r="B16" s="224"/>
-      <c r="C16" s="198"/>
-      <c r="D16" s="221"/>
-      <c r="E16" s="198"/>
-      <c r="F16" s="228"/>
-      <c r="G16" s="234">
+      <c r="B16" s="178"/>
+      <c r="C16" s="87"/>
+      <c r="D16" s="187"/>
+      <c r="E16" s="87"/>
+      <c r="F16" s="186"/>
+      <c r="G16" s="107">
         <v>0.995</v>
       </c>
       <c r="H16" s="3"/>
     </row>
     <row r="17" spans="1:9" ht="3" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="28"/>
-      <c r="B17" s="224"/>
-      <c r="C17" s="198"/>
-      <c r="D17" s="219"/>
-      <c r="E17" s="198"/>
-      <c r="F17" s="198"/>
-      <c r="G17" s="235"/>
+      <c r="B17" s="178"/>
+      <c r="C17" s="87"/>
+      <c r="D17" s="99"/>
+      <c r="E17" s="87"/>
+      <c r="F17" s="87"/>
+      <c r="G17" s="108"/>
       <c r="H17" s="26"/>
       <c r="I17" s="27"/>
     </row>
     <row r="18" spans="1:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="28"/>
-      <c r="B18" s="224"/>
-      <c r="C18" s="198"/>
-      <c r="D18" s="236" t="s">
+      <c r="B18" s="178"/>
+      <c r="C18" s="87"/>
+      <c r="D18" s="109" t="s">
         <v>28</v>
       </c>
-      <c r="E18" s="198"/>
-      <c r="F18" s="237" t="s">
+      <c r="E18" s="87"/>
+      <c r="F18" s="182" t="s">
         <v>241</v>
       </c>
-      <c r="G18" s="238"/>
+      <c r="G18" s="183"/>
       <c r="H18" s="3"/>
     </row>
     <row r="19" spans="1:9" ht="3" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="28"/>
-      <c r="B19" s="224"/>
-      <c r="C19" s="198"/>
-      <c r="D19" s="219"/>
-      <c r="E19" s="198"/>
-      <c r="F19" s="237"/>
-      <c r="G19" s="238"/>
+      <c r="B19" s="178"/>
+      <c r="C19" s="87"/>
+      <c r="D19" s="99"/>
+      <c r="E19" s="87"/>
+      <c r="F19" s="182"/>
+      <c r="G19" s="183"/>
       <c r="H19" s="3"/>
     </row>
     <row r="20" spans="1:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="28"/>
-      <c r="B20" s="224"/>
-      <c r="C20" s="198"/>
-      <c r="D20" s="236" t="s">
+      <c r="B20" s="178"/>
+      <c r="C20" s="87"/>
+      <c r="D20" s="109" t="s">
         <v>29</v>
       </c>
-      <c r="E20" s="198"/>
-      <c r="F20" s="238"/>
-      <c r="G20" s="238"/>
+      <c r="E20" s="87"/>
+      <c r="F20" s="183"/>
+      <c r="G20" s="183"/>
       <c r="H20" s="3"/>
     </row>
     <row r="21" spans="1:9" ht="3" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="28"/>
-      <c r="B21" s="224"/>
-      <c r="C21" s="198"/>
-      <c r="D21" s="219"/>
-      <c r="E21" s="198"/>
-      <c r="F21" s="238"/>
-      <c r="G21" s="238"/>
+      <c r="B21" s="178"/>
+      <c r="C21" s="87"/>
+      <c r="D21" s="99"/>
+      <c r="E21" s="87"/>
+      <c r="F21" s="183"/>
+      <c r="G21" s="183"/>
       <c r="H21" s="3"/>
     </row>
     <row r="22" spans="1:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="28"/>
-      <c r="B22" s="224"/>
-      <c r="C22" s="198"/>
-      <c r="D22" s="236" t="s">
+      <c r="B22" s="178"/>
+      <c r="C22" s="87"/>
+      <c r="D22" s="109" t="s">
         <v>30</v>
       </c>
-      <c r="E22" s="198"/>
-      <c r="F22" s="238"/>
-      <c r="G22" s="238"/>
+      <c r="E22" s="87"/>
+      <c r="F22" s="183"/>
+      <c r="G22" s="183"/>
       <c r="H22" s="3"/>
     </row>
     <row r="23" spans="1:9" ht="3" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="28"/>
-      <c r="B23" s="224"/>
-      <c r="C23" s="198"/>
-      <c r="D23" s="219"/>
-      <c r="E23" s="198"/>
-      <c r="F23" s="238"/>
-      <c r="G23" s="238"/>
+      <c r="B23" s="178"/>
+      <c r="C23" s="87"/>
+      <c r="D23" s="99"/>
+      <c r="E23" s="87"/>
+      <c r="F23" s="183"/>
+      <c r="G23" s="183"/>
       <c r="H23" s="3"/>
     </row>
     <row r="24" spans="1:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="28"/>
-      <c r="B24" s="224"/>
-      <c r="C24" s="198"/>
-      <c r="D24" s="236" t="s">
+      <c r="B24" s="178"/>
+      <c r="C24" s="87"/>
+      <c r="D24" s="109" t="s">
         <v>31</v>
       </c>
-      <c r="E24" s="198"/>
-      <c r="F24" s="238"/>
-      <c r="G24" s="238"/>
+      <c r="E24" s="87"/>
+      <c r="F24" s="183"/>
+      <c r="G24" s="183"/>
       <c r="H24" s="3"/>
     </row>
     <row r="25" spans="1:9" ht="3" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="28"/>
-      <c r="B25" s="224"/>
-      <c r="C25" s="198"/>
-      <c r="D25" s="219"/>
-      <c r="E25" s="198"/>
-      <c r="F25" s="238"/>
-      <c r="G25" s="238"/>
+      <c r="B25" s="178"/>
+      <c r="C25" s="87"/>
+      <c r="D25" s="99"/>
+      <c r="E25" s="87"/>
+      <c r="F25" s="183"/>
+      <c r="G25" s="183"/>
       <c r="H25" s="3"/>
     </row>
     <row r="26" spans="1:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="28"/>
-      <c r="B26" s="224"/>
-      <c r="C26" s="198"/>
-      <c r="D26" s="236" t="s">
+      <c r="B26" s="178"/>
+      <c r="C26" s="87"/>
+      <c r="D26" s="109" t="s">
         <v>32</v>
       </c>
-      <c r="E26" s="198"/>
-      <c r="F26" s="238"/>
-      <c r="G26" s="238"/>
+      <c r="E26" s="87"/>
+      <c r="F26" s="183"/>
+      <c r="G26" s="183"/>
       <c r="H26" s="3"/>
     </row>
     <row r="27" spans="1:9" ht="3" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="28"/>
-      <c r="B27" s="224"/>
-      <c r="C27" s="198"/>
-      <c r="D27" s="219"/>
-      <c r="E27" s="198"/>
-      <c r="F27" s="238"/>
-      <c r="G27" s="238"/>
+      <c r="B27" s="178"/>
+      <c r="C27" s="87"/>
+      <c r="D27" s="99"/>
+      <c r="E27" s="87"/>
+      <c r="F27" s="183"/>
+      <c r="G27" s="183"/>
       <c r="H27" s="3"/>
     </row>
     <row r="28" spans="1:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="28"/>
-      <c r="B28" s="224"/>
-      <c r="C28" s="198"/>
-      <c r="D28" s="236" t="s">
+      <c r="B28" s="178"/>
+      <c r="C28" s="87"/>
+      <c r="D28" s="109" t="s">
         <v>33</v>
       </c>
-      <c r="E28" s="198"/>
-      <c r="F28" s="238"/>
-      <c r="G28" s="238"/>
+      <c r="E28" s="87"/>
+      <c r="F28" s="183"/>
+      <c r="G28" s="183"/>
       <c r="H28" s="3"/>
     </row>
     <row r="29" spans="1:9" ht="3" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="28"/>
-      <c r="B29" s="224"/>
-      <c r="C29" s="198"/>
-      <c r="D29" s="219"/>
-      <c r="E29" s="198"/>
-      <c r="F29" s="238"/>
-      <c r="G29" s="238"/>
+      <c r="B29" s="178"/>
+      <c r="C29" s="87"/>
+      <c r="D29" s="99"/>
+      <c r="E29" s="87"/>
+      <c r="F29" s="183"/>
+      <c r="G29" s="183"/>
       <c r="H29" s="3"/>
     </row>
     <row r="30" spans="1:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="28"/>
-      <c r="B30" s="224"/>
-      <c r="C30" s="198"/>
-      <c r="D30" s="236" t="s">
+      <c r="B30" s="178"/>
+      <c r="C30" s="87"/>
+      <c r="D30" s="109" t="s">
         <v>34</v>
       </c>
-      <c r="E30" s="198"/>
-      <c r="F30" s="238"/>
-      <c r="G30" s="238"/>
+      <c r="E30" s="87"/>
+      <c r="F30" s="183"/>
+      <c r="G30" s="183"/>
       <c r="H30" s="3"/>
     </row>
     <row r="31" spans="1:9" ht="3" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="28"/>
-      <c r="B31" s="224"/>
-      <c r="C31" s="198"/>
-      <c r="D31" s="198"/>
-      <c r="E31" s="198"/>
-      <c r="F31" s="198"/>
-      <c r="G31" s="198"/>
+      <c r="B31" s="178"/>
+      <c r="C31" s="87"/>
+      <c r="D31" s="87"/>
+      <c r="E31" s="87"/>
+      <c r="F31" s="87"/>
+      <c r="G31" s="87"/>
       <c r="H31" s="26"/>
       <c r="I31" s="27"/>
     </row>
     <row r="32" spans="1:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="28"/>
-      <c r="B32" s="224"/>
-      <c r="C32" s="198"/>
-      <c r="D32" s="220" t="s">
+      <c r="B32" s="178"/>
+      <c r="C32" s="87"/>
+      <c r="D32" s="177" t="s">
         <v>234</v>
       </c>
-      <c r="E32" s="198"/>
-      <c r="F32" s="239" t="s">
+      <c r="E32" s="87"/>
+      <c r="F32" s="180" t="s">
         <v>238</v>
       </c>
-      <c r="G32" s="240"/>
+      <c r="G32" s="181"/>
       <c r="H32" s="3"/>
     </row>
     <row r="33" spans="1:9" ht="3" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="28"/>
-      <c r="B33" s="224"/>
-      <c r="C33" s="198"/>
-      <c r="D33" s="224"/>
-      <c r="E33" s="198"/>
-      <c r="F33" s="198"/>
-      <c r="G33" s="198"/>
+      <c r="B33" s="178"/>
+      <c r="C33" s="87"/>
+      <c r="D33" s="178"/>
+      <c r="E33" s="87"/>
+      <c r="F33" s="87"/>
+      <c r="G33" s="87"/>
       <c r="H33" s="26"/>
       <c r="I33" s="27"/>
     </row>
     <row r="34" spans="1:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="28"/>
-      <c r="B34" s="224"/>
-      <c r="C34" s="198"/>
-      <c r="D34" s="224"/>
-      <c r="E34" s="198"/>
-      <c r="F34" s="239" t="s">
+      <c r="B34" s="178"/>
+      <c r="C34" s="87"/>
+      <c r="D34" s="178"/>
+      <c r="E34" s="87"/>
+      <c r="F34" s="180" t="s">
         <v>237</v>
       </c>
-      <c r="G34" s="240"/>
+      <c r="G34" s="181"/>
       <c r="H34" s="3"/>
     </row>
     <row r="35" spans="1:9" ht="3" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="28"/>
-      <c r="B35" s="224"/>
-      <c r="C35" s="198"/>
-      <c r="D35" s="224"/>
-      <c r="E35" s="198"/>
-      <c r="F35" s="219"/>
-      <c r="G35" s="219"/>
+      <c r="B35" s="178"/>
+      <c r="C35" s="87"/>
+      <c r="D35" s="178"/>
+      <c r="E35" s="87"/>
+      <c r="F35" s="99"/>
+      <c r="G35" s="99"/>
       <c r="H35" s="26"/>
       <c r="I35" s="27"/>
     </row>
     <row r="36" spans="1:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="28"/>
-      <c r="B36" s="224"/>
-      <c r="C36" s="198"/>
-      <c r="D36" s="224"/>
-      <c r="E36" s="198"/>
-      <c r="F36" s="239" t="s">
+      <c r="B36" s="178"/>
+      <c r="C36" s="87"/>
+      <c r="D36" s="178"/>
+      <c r="E36" s="87"/>
+      <c r="F36" s="180" t="s">
         <v>236</v>
       </c>
-      <c r="G36" s="240"/>
+      <c r="G36" s="181"/>
       <c r="H36" s="3"/>
     </row>
     <row r="37" spans="1:9" ht="3" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="28"/>
-      <c r="B37" s="224"/>
-      <c r="C37" s="198"/>
-      <c r="D37" s="224"/>
-      <c r="E37" s="198"/>
-      <c r="F37" s="219"/>
-      <c r="G37" s="219"/>
+      <c r="B37" s="178"/>
+      <c r="C37" s="87"/>
+      <c r="D37" s="178"/>
+      <c r="E37" s="87"/>
+      <c r="F37" s="99"/>
+      <c r="G37" s="99"/>
       <c r="H37" s="26"/>
       <c r="I37" s="27"/>
     </row>
     <row r="38" spans="1:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="28"/>
-      <c r="B38" s="241"/>
-      <c r="C38" s="198"/>
-      <c r="D38" s="241"/>
-      <c r="E38" s="198"/>
-      <c r="F38" s="239" t="s">
+      <c r="B38" s="179"/>
+      <c r="C38" s="87"/>
+      <c r="D38" s="179"/>
+      <c r="E38" s="87"/>
+      <c r="F38" s="180" t="s">
         <v>235</v>
       </c>
-      <c r="G38" s="240"/>
+      <c r="G38" s="181"/>
       <c r="H38" s="3"/>
     </row>
     <row r="39" spans="1:9" ht="6" customHeight="1" x14ac:dyDescent="0.15">
@@ -15852,7 +15858,7 @@
       <c r="M4" s="75"/>
       <c r="N4" s="68"/>
       <c r="O4" s="69" t="s">
-        <v>287</v>
+        <v>303</v>
       </c>
       <c r="P4" s="70"/>
       <c r="Q4" s="78" t="s">
@@ -15888,19 +15894,19 @@
       <c r="L5" s="76"/>
       <c r="M5" s="73"/>
       <c r="N5" s="58"/>
-      <c r="O5" s="117" t="s">
+      <c r="O5" s="195" t="s">
         <v>247</v>
       </c>
       <c r="P5" s="60"/>
-      <c r="Q5" s="118" t="s">
+      <c r="Q5" s="189" t="s">
         <v>285</v>
       </c>
       <c r="R5" s="62"/>
-      <c r="S5" s="118" t="s">
+      <c r="S5" s="189" t="s">
         <v>265</v>
       </c>
       <c r="T5" s="62"/>
-      <c r="U5" s="118" t="s">
+      <c r="U5" s="189" t="s">
         <v>267</v>
       </c>
       <c r="V5" s="60"/>
@@ -15925,13 +15931,13 @@
       <c r="L6" s="76"/>
       <c r="M6" s="73"/>
       <c r="N6" s="58"/>
-      <c r="O6" s="118"/>
+      <c r="O6" s="189"/>
       <c r="P6" s="60"/>
-      <c r="Q6" s="120"/>
+      <c r="Q6" s="190"/>
       <c r="R6" s="62"/>
-      <c r="S6" s="120"/>
+      <c r="S6" s="190"/>
       <c r="T6" s="62"/>
-      <c r="U6" s="119"/>
+      <c r="U6" s="191"/>
       <c r="V6" s="60"/>
       <c r="W6" s="79" t="s">
         <v>252</v>
@@ -16048,7 +16054,7 @@
       <c r="M10" s="75"/>
       <c r="N10" s="68"/>
       <c r="O10" s="69" t="s">
-        <v>287</v>
+        <v>303</v>
       </c>
       <c r="P10" s="70"/>
       <c r="Q10" s="78" t="s">
@@ -16084,19 +16090,19 @@
       <c r="L11" s="76"/>
       <c r="M11" s="73"/>
       <c r="N11" s="58"/>
-      <c r="O11" s="117" t="s">
+      <c r="O11" s="195" t="s">
         <v>247</v>
       </c>
       <c r="P11" s="60"/>
-      <c r="Q11" s="118" t="s">
+      <c r="Q11" s="189" t="s">
         <v>285</v>
       </c>
       <c r="R11" s="62"/>
-      <c r="S11" s="118" t="s">
+      <c r="S11" s="189" t="s">
         <v>265</v>
       </c>
       <c r="T11" s="62"/>
-      <c r="U11" s="118" t="s">
+      <c r="U11" s="189" t="s">
         <v>283</v>
       </c>
       <c r="V11" s="60"/>
@@ -16121,13 +16127,13 @@
       <c r="L12" s="76"/>
       <c r="M12" s="73"/>
       <c r="N12" s="58"/>
-      <c r="O12" s="118"/>
+      <c r="O12" s="189"/>
       <c r="P12" s="60"/>
-      <c r="Q12" s="120"/>
+      <c r="Q12" s="190"/>
       <c r="R12" s="62"/>
-      <c r="S12" s="120"/>
+      <c r="S12" s="190"/>
       <c r="T12" s="62"/>
-      <c r="U12" s="119"/>
+      <c r="U12" s="191"/>
       <c r="V12" s="60"/>
       <c r="W12" s="79" t="s">
         <v>252</v>
@@ -16248,7 +16254,7 @@
     <row r="17" spans="1:25" s="57" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="68"/>
       <c r="B17" s="69" t="s">
-        <v>287</v>
+        <v>303</v>
       </c>
       <c r="C17" s="70"/>
       <c r="D17" s="69" t="s">
@@ -16286,23 +16292,23 @@
     </row>
     <row r="18" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="58"/>
-      <c r="B18" s="119" t="s">
+      <c r="B18" s="191" t="s">
         <v>247</v>
       </c>
       <c r="C18" s="60"/>
-      <c r="D18" s="119" t="s">
+      <c r="D18" s="191" t="s">
         <v>275</v>
       </c>
       <c r="E18" s="62"/>
-      <c r="F18" s="120" t="s">
+      <c r="F18" s="190" t="s">
         <v>276</v>
       </c>
       <c r="G18" s="62"/>
-      <c r="H18" s="120" t="s">
+      <c r="H18" s="190" t="s">
         <v>36</v>
       </c>
       <c r="I18" s="62"/>
-      <c r="J18" s="121" t="s">
+      <c r="J18" s="196" t="s">
         <v>253</v>
       </c>
       <c r="K18" s="60"/>
@@ -16325,15 +16331,15 @@
     </row>
     <row r="19" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="58"/>
-      <c r="B19" s="119"/>
+      <c r="B19" s="191"/>
       <c r="C19" s="60"/>
-      <c r="D19" s="120"/>
+      <c r="D19" s="190"/>
       <c r="E19" s="62"/>
-      <c r="F19" s="120"/>
+      <c r="F19" s="190"/>
       <c r="G19" s="62"/>
-      <c r="H19" s="120"/>
+      <c r="H19" s="190"/>
       <c r="I19" s="62"/>
-      <c r="J19" s="121"/>
+      <c r="J19" s="196"/>
       <c r="K19" s="60"/>
       <c r="L19" s="67" t="s">
         <v>256</v>
@@ -16354,7 +16360,7 @@
     </row>
     <row r="20" spans="1:25" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="58"/>
-      <c r="B20" s="119"/>
+      <c r="B20" s="191"/>
       <c r="C20" s="60"/>
       <c r="D20" s="61" t="s">
         <v>248</v>
@@ -16529,7 +16535,7 @@
     <row r="26" spans="1:25" s="57" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="68"/>
       <c r="B26" s="69" t="s">
-        <v>287</v>
+        <v>303</v>
       </c>
       <c r="C26" s="70"/>
       <c r="D26" s="69" t="s">
@@ -16567,23 +16573,23 @@
     </row>
     <row r="27" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="58"/>
-      <c r="B27" s="119" t="s">
+      <c r="B27" s="191" t="s">
         <v>247</v>
       </c>
       <c r="C27" s="60"/>
-      <c r="D27" s="119" t="s">
+      <c r="D27" s="191" t="s">
         <v>278</v>
       </c>
       <c r="E27" s="62"/>
-      <c r="F27" s="120" t="s">
+      <c r="F27" s="190" t="s">
         <v>277</v>
       </c>
       <c r="G27" s="62"/>
-      <c r="H27" s="120" t="s">
+      <c r="H27" s="190" t="s">
         <v>260</v>
       </c>
       <c r="I27" s="62"/>
-      <c r="J27" s="121" t="s">
+      <c r="J27" s="196" t="s">
         <v>261</v>
       </c>
       <c r="K27" s="60"/>
@@ -16606,15 +16612,15 @@
     </row>
     <row r="28" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="58"/>
-      <c r="B28" s="119"/>
+      <c r="B28" s="191"/>
       <c r="C28" s="60"/>
-      <c r="D28" s="120"/>
+      <c r="D28" s="190"/>
       <c r="E28" s="62"/>
-      <c r="F28" s="120"/>
+      <c r="F28" s="190"/>
       <c r="G28" s="62"/>
-      <c r="H28" s="120"/>
+      <c r="H28" s="190"/>
       <c r="I28" s="62"/>
-      <c r="J28" s="121"/>
+      <c r="J28" s="196"/>
       <c r="K28" s="60"/>
       <c r="L28" s="67" t="s">
         <v>264</v>
@@ -16635,7 +16641,7 @@
     </row>
     <row r="29" spans="1:25" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="58"/>
-      <c r="B29" s="119"/>
+      <c r="B29" s="191"/>
       <c r="C29" s="60"/>
       <c r="D29" s="61" t="s">
         <v>248</v>
@@ -16726,19 +16732,19 @@
     </row>
     <row r="32" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A32" s="58"/>
-      <c r="B32" s="245" t="s">
-        <v>299</v>
-      </c>
-      <c r="C32" s="243"/>
-      <c r="D32" s="243"/>
-      <c r="E32" s="243"/>
-      <c r="F32" s="243"/>
-      <c r="G32" s="243"/>
-      <c r="H32" s="243"/>
-      <c r="I32" s="243"/>
-      <c r="J32" s="243"/>
-      <c r="K32" s="243"/>
-      <c r="L32" s="243"/>
+      <c r="B32" s="113" t="s">
+        <v>298</v>
+      </c>
+      <c r="C32" s="111"/>
+      <c r="D32" s="111"/>
+      <c r="E32" s="111"/>
+      <c r="F32" s="111"/>
+      <c r="G32" s="111"/>
+      <c r="H32" s="111"/>
+      <c r="I32" s="111"/>
+      <c r="J32" s="111"/>
+      <c r="K32" s="111"/>
+      <c r="L32" s="111"/>
       <c r="M32" s="58"/>
       <c r="N32" s="58"/>
       <c r="O32" s="58"/>
@@ -16755,17 +16761,17 @@
     </row>
     <row r="33" spans="1:25" ht="3.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A33" s="58"/>
-      <c r="B33" s="243"/>
-      <c r="C33" s="243"/>
-      <c r="D33" s="243"/>
-      <c r="E33" s="243"/>
-      <c r="F33" s="243"/>
-      <c r="G33" s="243"/>
-      <c r="H33" s="243"/>
-      <c r="I33" s="243"/>
-      <c r="J33" s="243"/>
-      <c r="K33" s="243"/>
-      <c r="L33" s="243"/>
+      <c r="B33" s="111"/>
+      <c r="C33" s="111"/>
+      <c r="D33" s="111"/>
+      <c r="E33" s="111"/>
+      <c r="F33" s="111"/>
+      <c r="G33" s="111"/>
+      <c r="H33" s="111"/>
+      <c r="I33" s="111"/>
+      <c r="J33" s="111"/>
+      <c r="K33" s="111"/>
+      <c r="L33" s="111"/>
       <c r="M33" s="58"/>
       <c r="N33" s="58"/>
       <c r="O33" s="58"/>
@@ -16782,27 +16788,27 @@
     </row>
     <row r="34" spans="1:25" s="57" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="68"/>
-      <c r="B34" s="244" t="s">
-        <v>287</v>
-      </c>
-      <c r="C34" s="245"/>
-      <c r="D34" s="244" t="s">
+      <c r="B34" s="112" t="s">
+        <v>303</v>
+      </c>
+      <c r="C34" s="113"/>
+      <c r="D34" s="112" t="s">
         <v>271</v>
       </c>
-      <c r="E34" s="245"/>
-      <c r="F34" s="244" t="s">
-        <v>302</v>
-      </c>
-      <c r="G34" s="245"/>
-      <c r="H34" s="244" t="s">
+      <c r="E34" s="113"/>
+      <c r="F34" s="112" t="s">
+        <v>301</v>
+      </c>
+      <c r="G34" s="113"/>
+      <c r="H34" s="112" t="s">
         <v>244</v>
       </c>
-      <c r="I34" s="245"/>
-      <c r="J34" s="244" t="s">
+      <c r="I34" s="113"/>
+      <c r="J34" s="112" t="s">
         <v>96</v>
       </c>
-      <c r="K34" s="245"/>
-      <c r="L34" s="244" t="s">
+      <c r="K34" s="113"/>
+      <c r="L34" s="112" t="s">
         <v>257</v>
       </c>
       <c r="M34" s="68"/>
@@ -16821,28 +16827,28 @@
     </row>
     <row r="35" spans="1:25" ht="18.75" x14ac:dyDescent="0.45">
       <c r="A35" s="58"/>
-      <c r="B35" s="246" t="s">
+      <c r="B35" s="192" t="s">
         <v>247</v>
       </c>
-      <c r="C35" s="243"/>
-      <c r="D35" s="246" t="s">
+      <c r="C35" s="111"/>
+      <c r="D35" s="192" t="s">
         <v>275</v>
       </c>
-      <c r="E35" s="247"/>
-      <c r="F35" s="248" t="s">
+      <c r="E35" s="114"/>
+      <c r="F35" s="193" t="s">
         <v>276</v>
       </c>
-      <c r="G35" s="247"/>
-      <c r="H35" s="248" t="s">
+      <c r="G35" s="114"/>
+      <c r="H35" s="193" t="s">
         <v>36</v>
       </c>
-      <c r="I35" s="247"/>
-      <c r="J35" s="249" t="s">
+      <c r="I35" s="114"/>
+      <c r="J35" s="194" t="s">
         <v>253</v>
       </c>
-      <c r="K35" s="243"/>
-      <c r="L35" s="250" t="s">
-        <v>297</v>
+      <c r="K35" s="111"/>
+      <c r="L35" s="115" t="s">
+        <v>296</v>
       </c>
       <c r="M35" s="58"/>
       <c r="N35" s="58"/>
@@ -16860,18 +16866,18 @@
     </row>
     <row r="36" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A36" s="58"/>
-      <c r="B36" s="246"/>
-      <c r="C36" s="243"/>
-      <c r="D36" s="248"/>
-      <c r="E36" s="247"/>
-      <c r="F36" s="248"/>
-      <c r="G36" s="247"/>
-      <c r="H36" s="248"/>
-      <c r="I36" s="247"/>
-      <c r="J36" s="249"/>
-      <c r="K36" s="243"/>
-      <c r="L36" s="255" t="s">
-        <v>298</v>
+      <c r="B36" s="192"/>
+      <c r="C36" s="111"/>
+      <c r="D36" s="193"/>
+      <c r="E36" s="114"/>
+      <c r="F36" s="193"/>
+      <c r="G36" s="114"/>
+      <c r="H36" s="193"/>
+      <c r="I36" s="114"/>
+      <c r="J36" s="194"/>
+      <c r="K36" s="111"/>
+      <c r="L36" s="120" t="s">
+        <v>297</v>
       </c>
       <c r="M36" s="58"/>
       <c r="N36" s="58"/>
@@ -16889,26 +16895,26 @@
     </row>
     <row r="37" spans="1:25" ht="35.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A37" s="58"/>
-      <c r="B37" s="246"/>
-      <c r="C37" s="243"/>
-      <c r="D37" s="252" t="s">
+      <c r="B37" s="192"/>
+      <c r="C37" s="111"/>
+      <c r="D37" s="117" t="s">
+        <v>287</v>
+      </c>
+      <c r="E37" s="118"/>
+      <c r="F37" s="117" t="s">
         <v>288</v>
       </c>
-      <c r="E37" s="253"/>
-      <c r="F37" s="252" t="s">
-        <v>289</v>
-      </c>
-      <c r="G37" s="253"/>
-      <c r="H37" s="252" t="s">
+      <c r="G37" s="118"/>
+      <c r="H37" s="117" t="s">
+        <v>290</v>
+      </c>
+      <c r="I37" s="118"/>
+      <c r="J37" s="117" t="s">
         <v>291</v>
       </c>
-      <c r="I37" s="253"/>
-      <c r="J37" s="252" t="s">
+      <c r="K37" s="119"/>
+      <c r="L37" s="117" t="s">
         <v>292</v>
-      </c>
-      <c r="K37" s="254"/>
-      <c r="L37" s="252" t="s">
-        <v>293</v>
       </c>
       <c r="M37" s="59"/>
       <c r="N37" s="58"/>
@@ -17007,19 +17013,19 @@
     </row>
     <row r="41" spans="1:25" s="57" customFormat="1" ht="18.75" x14ac:dyDescent="0.15">
       <c r="A41" s="68"/>
-      <c r="B41" s="245" t="s">
-        <v>300</v>
-      </c>
-      <c r="C41" s="245"/>
-      <c r="D41" s="245"/>
-      <c r="E41" s="245"/>
-      <c r="F41" s="245"/>
-      <c r="G41" s="245"/>
-      <c r="H41" s="245"/>
-      <c r="I41" s="245"/>
-      <c r="J41" s="245"/>
-      <c r="K41" s="245"/>
-      <c r="L41" s="245"/>
+      <c r="B41" s="113" t="s">
+        <v>299</v>
+      </c>
+      <c r="C41" s="113"/>
+      <c r="D41" s="113"/>
+      <c r="E41" s="113"/>
+      <c r="F41" s="113"/>
+      <c r="G41" s="113"/>
+      <c r="H41" s="113"/>
+      <c r="I41" s="113"/>
+      <c r="J41" s="113"/>
+      <c r="K41" s="113"/>
+      <c r="L41" s="113"/>
       <c r="M41" s="68"/>
       <c r="N41" s="68"/>
       <c r="O41" s="68"/>
@@ -17036,17 +17042,17 @@
     </row>
     <row r="42" spans="1:25" ht="3.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A42" s="58"/>
-      <c r="B42" s="243"/>
-      <c r="C42" s="243"/>
-      <c r="D42" s="243"/>
-      <c r="E42" s="243"/>
-      <c r="F42" s="243"/>
-      <c r="G42" s="243"/>
-      <c r="H42" s="243"/>
-      <c r="I42" s="243"/>
-      <c r="J42" s="243"/>
-      <c r="K42" s="243"/>
-      <c r="L42" s="243"/>
+      <c r="B42" s="111"/>
+      <c r="C42" s="111"/>
+      <c r="D42" s="111"/>
+      <c r="E42" s="111"/>
+      <c r="F42" s="111"/>
+      <c r="G42" s="111"/>
+      <c r="H42" s="111"/>
+      <c r="I42" s="111"/>
+      <c r="J42" s="111"/>
+      <c r="K42" s="111"/>
+      <c r="L42" s="111"/>
       <c r="M42" s="58"/>
       <c r="N42" s="58"/>
       <c r="O42" s="58"/>
@@ -17063,27 +17069,27 @@
     </row>
     <row r="43" spans="1:25" s="57" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="68"/>
-      <c r="B43" s="244" t="s">
-        <v>287</v>
-      </c>
-      <c r="C43" s="245"/>
-      <c r="D43" s="244" t="s">
+      <c r="B43" s="112" t="s">
+        <v>303</v>
+      </c>
+      <c r="C43" s="113"/>
+      <c r="D43" s="112" t="s">
         <v>271</v>
       </c>
-      <c r="E43" s="245"/>
-      <c r="F43" s="244" t="s">
+      <c r="E43" s="113"/>
+      <c r="F43" s="112" t="s">
         <v>95</v>
       </c>
-      <c r="G43" s="245"/>
-      <c r="H43" s="244" t="s">
+      <c r="G43" s="113"/>
+      <c r="H43" s="112" t="s">
         <v>244</v>
       </c>
-      <c r="I43" s="245"/>
-      <c r="J43" s="244" t="s">
+      <c r="I43" s="113"/>
+      <c r="J43" s="112" t="s">
         <v>96</v>
       </c>
-      <c r="K43" s="245"/>
-      <c r="L43" s="244" t="s">
+      <c r="K43" s="113"/>
+      <c r="L43" s="112" t="s">
         <v>257</v>
       </c>
       <c r="M43" s="68"/>
@@ -17102,28 +17108,28 @@
     </row>
     <row r="44" spans="1:25" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A44" s="58"/>
-      <c r="B44" s="246" t="s">
+      <c r="B44" s="192" t="s">
         <v>247</v>
       </c>
-      <c r="C44" s="243"/>
-      <c r="D44" s="246" t="s">
+      <c r="C44" s="111"/>
+      <c r="D44" s="192" t="s">
         <v>278</v>
       </c>
-      <c r="E44" s="247"/>
-      <c r="F44" s="248" t="s">
+      <c r="E44" s="114"/>
+      <c r="F44" s="193" t="s">
         <v>277</v>
       </c>
-      <c r="G44" s="247"/>
-      <c r="H44" s="248" t="s">
+      <c r="G44" s="114"/>
+      <c r="H44" s="193" t="s">
         <v>260</v>
       </c>
-      <c r="I44" s="247"/>
-      <c r="J44" s="249" t="s">
+      <c r="I44" s="114"/>
+      <c r="J44" s="194" t="s">
         <v>261</v>
       </c>
-      <c r="K44" s="243"/>
-      <c r="L44" s="250" t="s">
-        <v>295</v>
+      <c r="K44" s="111"/>
+      <c r="L44" s="115" t="s">
+        <v>294</v>
       </c>
       <c r="M44" s="58"/>
       <c r="N44" s="58"/>
@@ -17141,18 +17147,18 @@
     </row>
     <row r="45" spans="1:25" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A45" s="58"/>
-      <c r="B45" s="246"/>
-      <c r="C45" s="243"/>
-      <c r="D45" s="248"/>
-      <c r="E45" s="247"/>
-      <c r="F45" s="248"/>
-      <c r="G45" s="247"/>
-      <c r="H45" s="248"/>
-      <c r="I45" s="247"/>
-      <c r="J45" s="249"/>
-      <c r="K45" s="243"/>
-      <c r="L45" s="251" t="s">
-        <v>296</v>
+      <c r="B45" s="192"/>
+      <c r="C45" s="111"/>
+      <c r="D45" s="193"/>
+      <c r="E45" s="114"/>
+      <c r="F45" s="193"/>
+      <c r="G45" s="114"/>
+      <c r="H45" s="193"/>
+      <c r="I45" s="114"/>
+      <c r="J45" s="194"/>
+      <c r="K45" s="111"/>
+      <c r="L45" s="116" t="s">
+        <v>295</v>
       </c>
       <c r="M45" s="58"/>
       <c r="N45" s="58"/>
@@ -17170,26 +17176,26 @@
     </row>
     <row r="46" spans="1:25" ht="35.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A46" s="58"/>
-      <c r="B46" s="246"/>
-      <c r="C46" s="243"/>
-      <c r="D46" s="252" t="s">
+      <c r="B46" s="192"/>
+      <c r="C46" s="111"/>
+      <c r="D46" s="117" t="s">
+        <v>287</v>
+      </c>
+      <c r="E46" s="118"/>
+      <c r="F46" s="117" t="s">
         <v>288</v>
       </c>
-      <c r="E46" s="253"/>
-      <c r="F46" s="252" t="s">
+      <c r="G46" s="118"/>
+      <c r="H46" s="117" t="s">
         <v>289</v>
       </c>
-      <c r="G46" s="253"/>
-      <c r="H46" s="252" t="s">
-        <v>290</v>
-      </c>
-      <c r="I46" s="253"/>
-      <c r="J46" s="252" t="s">
-        <v>294</v>
-      </c>
-      <c r="K46" s="254"/>
-      <c r="L46" s="252" t="s">
+      <c r="I46" s="118"/>
+      <c r="J46" s="117" t="s">
         <v>293</v>
+      </c>
+      <c r="K46" s="119"/>
+      <c r="L46" s="117" t="s">
+        <v>292</v>
       </c>
       <c r="M46" s="59"/>
       <c r="N46" s="58"/>
@@ -17261,18 +17267,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="S11:S12"/>
-    <mergeCell ref="U11:U12"/>
-    <mergeCell ref="B44:B46"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="F44:F45"/>
-    <mergeCell ref="H44:H45"/>
-    <mergeCell ref="J44:J45"/>
-    <mergeCell ref="B35:B37"/>
-    <mergeCell ref="D35:D36"/>
-    <mergeCell ref="F35:F36"/>
-    <mergeCell ref="H35:H36"/>
-    <mergeCell ref="J35:J36"/>
     <mergeCell ref="O5:O6"/>
     <mergeCell ref="U5:U6"/>
     <mergeCell ref="Q5:Q6"/>
@@ -17289,6 +17283,18 @@
     <mergeCell ref="J18:J19"/>
     <mergeCell ref="O11:O12"/>
     <mergeCell ref="Q11:Q12"/>
+    <mergeCell ref="S11:S12"/>
+    <mergeCell ref="U11:U12"/>
+    <mergeCell ref="B44:B46"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="F44:F45"/>
+    <mergeCell ref="H44:H45"/>
+    <mergeCell ref="J44:J45"/>
+    <mergeCell ref="B35:B37"/>
+    <mergeCell ref="D35:D36"/>
+    <mergeCell ref="F35:F36"/>
+    <mergeCell ref="H35:H36"/>
+    <mergeCell ref="J35:J36"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -17324,507 +17330,507 @@
     </row>
     <row r="2" spans="1:9" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="3"/>
-      <c r="B2" s="195" t="s">
+      <c r="B2" s="84" t="s">
         <v>242</v>
       </c>
-      <c r="C2" s="198"/>
-      <c r="D2" s="196"/>
-      <c r="E2" s="198"/>
-      <c r="F2" s="196"/>
-      <c r="G2" s="196"/>
+      <c r="C2" s="87"/>
+      <c r="D2" s="85"/>
+      <c r="E2" s="87"/>
+      <c r="F2" s="85"/>
+      <c r="G2" s="85"/>
       <c r="H2" s="3"/>
     </row>
     <row r="3" spans="1:9" ht="9.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="3"/>
-      <c r="B3" s="197" t="s">
+      <c r="B3" s="86" t="s">
         <v>94</v>
       </c>
-      <c r="C3" s="198"/>
-      <c r="D3" s="197" t="s">
+      <c r="C3" s="87"/>
+      <c r="D3" s="86" t="s">
         <v>95</v>
       </c>
-      <c r="E3" s="198"/>
-      <c r="F3" s="218" t="s">
+      <c r="E3" s="87"/>
+      <c r="F3" s="98" t="s">
         <v>244</v>
       </c>
-      <c r="G3" s="197" t="s">
+      <c r="G3" s="86" t="s">
         <v>96</v>
       </c>
       <c r="H3" s="3"/>
     </row>
     <row r="4" spans="1:9" ht="3.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="26"/>
-      <c r="B4" s="198"/>
-      <c r="C4" s="198"/>
-      <c r="D4" s="219"/>
-      <c r="E4" s="198"/>
-      <c r="F4" s="198"/>
-      <c r="G4" s="198"/>
+      <c r="B4" s="87"/>
+      <c r="C4" s="87"/>
+      <c r="D4" s="99"/>
+      <c r="E4" s="87"/>
+      <c r="F4" s="87"/>
+      <c r="G4" s="87"/>
       <c r="H4" s="26"/>
       <c r="I4" s="27"/>
     </row>
     <row r="5" spans="1:9" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="3"/>
-      <c r="B5" s="220" t="s">
+      <c r="B5" s="177" t="s">
         <v>0</v>
       </c>
-      <c r="C5" s="200"/>
-      <c r="D5" s="256" t="s">
+      <c r="C5" s="88"/>
+      <c r="D5" s="198" t="s">
         <v>1</v>
       </c>
-      <c r="E5" s="257"/>
-      <c r="F5" s="258" t="s">
+      <c r="E5" s="121"/>
+      <c r="F5" s="199" t="s">
         <v>2</v>
       </c>
-      <c r="G5" s="259" t="s">
+      <c r="G5" s="122" t="s">
         <v>3</v>
       </c>
       <c r="H5" s="3"/>
     </row>
     <row r="6" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="3"/>
-      <c r="B6" s="224"/>
-      <c r="C6" s="200"/>
-      <c r="D6" s="256"/>
-      <c r="E6" s="257"/>
-      <c r="F6" s="260"/>
-      <c r="G6" s="261" t="s">
+      <c r="B6" s="178"/>
+      <c r="C6" s="88"/>
+      <c r="D6" s="198"/>
+      <c r="E6" s="121"/>
+      <c r="F6" s="200"/>
+      <c r="G6" s="123" t="s">
         <v>230</v>
       </c>
       <c r="H6" s="3"/>
     </row>
     <row r="7" spans="1:9" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="3"/>
-      <c r="B7" s="224"/>
-      <c r="C7" s="200"/>
-      <c r="D7" s="256"/>
-      <c r="E7" s="257"/>
-      <c r="F7" s="262"/>
-      <c r="G7" s="263" t="s">
+      <c r="B7" s="178"/>
+      <c r="C7" s="88"/>
+      <c r="D7" s="198"/>
+      <c r="E7" s="121"/>
+      <c r="F7" s="201"/>
+      <c r="G7" s="124" t="s">
         <v>6</v>
       </c>
       <c r="H7" s="3"/>
     </row>
     <row r="8" spans="1:9" ht="3.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="3"/>
-      <c r="B8" s="224"/>
-      <c r="C8" s="200"/>
-      <c r="D8" s="256"/>
-      <c r="E8" s="264"/>
-      <c r="F8" s="265"/>
-      <c r="G8" s="265"/>
+      <c r="B8" s="178"/>
+      <c r="C8" s="88"/>
+      <c r="D8" s="198"/>
+      <c r="E8" s="125"/>
+      <c r="F8" s="126"/>
+      <c r="G8" s="126"/>
       <c r="H8" s="26"/>
     </row>
     <row r="9" spans="1:9" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="3"/>
-      <c r="B9" s="224"/>
-      <c r="C9" s="200"/>
-      <c r="D9" s="256"/>
-      <c r="E9" s="257"/>
-      <c r="F9" s="258" t="s">
+      <c r="B9" s="178"/>
+      <c r="C9" s="88"/>
+      <c r="D9" s="198"/>
+      <c r="E9" s="121"/>
+      <c r="F9" s="199" t="s">
         <v>7</v>
       </c>
-      <c r="G9" s="259" t="s">
+      <c r="G9" s="122" t="s">
         <v>3</v>
       </c>
       <c r="H9" s="3"/>
     </row>
     <row r="10" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="3"/>
-      <c r="B10" s="224"/>
-      <c r="C10" s="200"/>
-      <c r="D10" s="256"/>
-      <c r="E10" s="257"/>
-      <c r="F10" s="260"/>
-      <c r="G10" s="261" t="s">
+      <c r="B10" s="178"/>
+      <c r="C10" s="88"/>
+      <c r="D10" s="198"/>
+      <c r="E10" s="121"/>
+      <c r="F10" s="200"/>
+      <c r="G10" s="123" t="s">
         <v>230</v>
       </c>
       <c r="H10" s="3"/>
     </row>
     <row r="11" spans="1:9" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="3"/>
-      <c r="B11" s="224"/>
-      <c r="C11" s="200"/>
-      <c r="D11" s="256"/>
-      <c r="E11" s="257"/>
-      <c r="F11" s="262"/>
-      <c r="G11" s="263" t="s">
+      <c r="B11" s="178"/>
+      <c r="C11" s="88"/>
+      <c r="D11" s="198"/>
+      <c r="E11" s="121"/>
+      <c r="F11" s="201"/>
+      <c r="G11" s="124" t="s">
         <v>6</v>
       </c>
       <c r="H11" s="3"/>
     </row>
     <row r="12" spans="1:9" ht="3.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="3"/>
-      <c r="B12" s="224"/>
-      <c r="C12" s="200"/>
-      <c r="D12" s="256"/>
-      <c r="E12" s="264"/>
-      <c r="F12" s="265"/>
-      <c r="G12" s="265"/>
+      <c r="B12" s="178"/>
+      <c r="C12" s="88"/>
+      <c r="D12" s="198"/>
+      <c r="E12" s="125"/>
+      <c r="F12" s="126"/>
+      <c r="G12" s="126"/>
       <c r="H12" s="26"/>
     </row>
     <row r="13" spans="1:9" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="3"/>
-      <c r="B13" s="224"/>
-      <c r="C13" s="200"/>
-      <c r="D13" s="256"/>
-      <c r="E13" s="257"/>
-      <c r="F13" s="258" t="s">
+      <c r="B13" s="178"/>
+      <c r="C13" s="88"/>
+      <c r="D13" s="198"/>
+      <c r="E13" s="121"/>
+      <c r="F13" s="199" t="s">
         <v>8</v>
       </c>
-      <c r="G13" s="259" t="s">
+      <c r="G13" s="122" t="s">
         <v>3</v>
       </c>
       <c r="H13" s="3"/>
     </row>
     <row r="14" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="3"/>
-      <c r="B14" s="224"/>
-      <c r="C14" s="200"/>
-      <c r="D14" s="256"/>
-      <c r="E14" s="257"/>
-      <c r="F14" s="260"/>
-      <c r="G14" s="261" t="s">
+      <c r="B14" s="178"/>
+      <c r="C14" s="88"/>
+      <c r="D14" s="198"/>
+      <c r="E14" s="121"/>
+      <c r="F14" s="200"/>
+      <c r="G14" s="123" t="s">
         <v>230</v>
       </c>
       <c r="H14" s="3"/>
     </row>
     <row r="15" spans="1:9" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="3"/>
-      <c r="B15" s="224"/>
-      <c r="C15" s="200"/>
-      <c r="D15" s="256"/>
-      <c r="E15" s="257"/>
-      <c r="F15" s="262"/>
-      <c r="G15" s="263" t="s">
+      <c r="B15" s="178"/>
+      <c r="C15" s="88"/>
+      <c r="D15" s="198"/>
+      <c r="E15" s="121"/>
+      <c r="F15" s="201"/>
+      <c r="G15" s="124" t="s">
         <v>6</v>
       </c>
       <c r="H15" s="3"/>
     </row>
     <row r="16" spans="1:9" ht="3.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="3"/>
-      <c r="B16" s="224"/>
-      <c r="C16" s="200"/>
-      <c r="D16" s="256"/>
-      <c r="E16" s="264"/>
-      <c r="F16" s="265"/>
-      <c r="G16" s="265"/>
+      <c r="B16" s="178"/>
+      <c r="C16" s="88"/>
+      <c r="D16" s="198"/>
+      <c r="E16" s="125"/>
+      <c r="F16" s="126"/>
+      <c r="G16" s="126"/>
       <c r="H16" s="26"/>
     </row>
     <row r="17" spans="1:8" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="3"/>
-      <c r="B17" s="224"/>
-      <c r="C17" s="200"/>
-      <c r="D17" s="256"/>
-      <c r="E17" s="257"/>
-      <c r="F17" s="258" t="s">
+      <c r="B17" s="178"/>
+      <c r="C17" s="88"/>
+      <c r="D17" s="198"/>
+      <c r="E17" s="121"/>
+      <c r="F17" s="199" t="s">
         <v>9</v>
       </c>
-      <c r="G17" s="259" t="s">
+      <c r="G17" s="122" t="s">
         <v>3</v>
       </c>
       <c r="H17" s="3"/>
     </row>
     <row r="18" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="3"/>
-      <c r="B18" s="224"/>
-      <c r="C18" s="200"/>
-      <c r="D18" s="256"/>
-      <c r="E18" s="257"/>
-      <c r="F18" s="260"/>
-      <c r="G18" s="261" t="s">
+      <c r="B18" s="178"/>
+      <c r="C18" s="88"/>
+      <c r="D18" s="198"/>
+      <c r="E18" s="121"/>
+      <c r="F18" s="200"/>
+      <c r="G18" s="123" t="s">
         <v>230</v>
       </c>
       <c r="H18" s="3"/>
     </row>
     <row r="19" spans="1:8" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="3"/>
-      <c r="B19" s="224"/>
-      <c r="C19" s="200"/>
-      <c r="D19" s="256"/>
-      <c r="E19" s="257"/>
-      <c r="F19" s="262"/>
-      <c r="G19" s="263" t="s">
+      <c r="B19" s="178"/>
+      <c r="C19" s="88"/>
+      <c r="D19" s="198"/>
+      <c r="E19" s="121"/>
+      <c r="F19" s="201"/>
+      <c r="G19" s="124" t="s">
         <v>6</v>
       </c>
       <c r="H19" s="3"/>
     </row>
     <row r="20" spans="1:8" ht="3.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="3"/>
-      <c r="B20" s="224"/>
-      <c r="C20" s="198"/>
-      <c r="D20" s="266"/>
-      <c r="E20" s="265"/>
-      <c r="F20" s="265"/>
-      <c r="G20" s="265"/>
+      <c r="B20" s="178"/>
+      <c r="C20" s="87"/>
+      <c r="D20" s="127"/>
+      <c r="E20" s="126"/>
+      <c r="F20" s="126"/>
+      <c r="G20" s="126"/>
       <c r="H20" s="26"/>
     </row>
     <row r="21" spans="1:8" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="3"/>
-      <c r="B21" s="224"/>
-      <c r="C21" s="200"/>
-      <c r="D21" s="267" t="s">
+      <c r="B21" s="178"/>
+      <c r="C21" s="88"/>
+      <c r="D21" s="128" t="s">
         <v>10</v>
       </c>
-      <c r="E21" s="264"/>
-      <c r="F21" s="268" t="s">
+      <c r="E21" s="125"/>
+      <c r="F21" s="202" t="s">
         <v>241</v>
       </c>
-      <c r="G21" s="268"/>
+      <c r="G21" s="202"/>
       <c r="H21" s="3"/>
     </row>
     <row r="22" spans="1:8" ht="3.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="3"/>
-      <c r="B22" s="224"/>
-      <c r="C22" s="198"/>
-      <c r="D22" s="266"/>
-      <c r="E22" s="265"/>
-      <c r="F22" s="268"/>
-      <c r="G22" s="268"/>
+      <c r="B22" s="178"/>
+      <c r="C22" s="87"/>
+      <c r="D22" s="127"/>
+      <c r="E22" s="126"/>
+      <c r="F22" s="202"/>
+      <c r="G22" s="202"/>
       <c r="H22" s="3"/>
     </row>
     <row r="23" spans="1:8" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="3"/>
-      <c r="B23" s="224"/>
-      <c r="C23" s="200"/>
-      <c r="D23" s="267" t="s">
+      <c r="B23" s="178"/>
+      <c r="C23" s="88"/>
+      <c r="D23" s="128" t="s">
         <v>12</v>
       </c>
-      <c r="E23" s="264"/>
-      <c r="F23" s="268"/>
-      <c r="G23" s="268"/>
+      <c r="E23" s="125"/>
+      <c r="F23" s="202"/>
+      <c r="G23" s="202"/>
       <c r="H23" s="3"/>
     </row>
     <row r="24" spans="1:8" ht="3.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="3"/>
-      <c r="B24" s="224"/>
-      <c r="C24" s="198"/>
-      <c r="D24" s="266"/>
-      <c r="E24" s="265"/>
-      <c r="F24" s="268"/>
-      <c r="G24" s="268"/>
+      <c r="B24" s="178"/>
+      <c r="C24" s="87"/>
+      <c r="D24" s="127"/>
+      <c r="E24" s="126"/>
+      <c r="F24" s="202"/>
+      <c r="G24" s="202"/>
       <c r="H24" s="3"/>
     </row>
     <row r="25" spans="1:8" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="3"/>
-      <c r="B25" s="224"/>
-      <c r="C25" s="200"/>
-      <c r="D25" s="267" t="s">
+      <c r="B25" s="178"/>
+      <c r="C25" s="88"/>
+      <c r="D25" s="128" t="s">
         <v>13</v>
       </c>
-      <c r="E25" s="264"/>
-      <c r="F25" s="268"/>
-      <c r="G25" s="268"/>
+      <c r="E25" s="125"/>
+      <c r="F25" s="202"/>
+      <c r="G25" s="202"/>
       <c r="H25" s="3"/>
     </row>
     <row r="26" spans="1:8" ht="3.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="3"/>
-      <c r="B26" s="224"/>
-      <c r="C26" s="198"/>
-      <c r="D26" s="266"/>
-      <c r="E26" s="265"/>
-      <c r="F26" s="268"/>
-      <c r="G26" s="268"/>
+      <c r="B26" s="178"/>
+      <c r="C26" s="87"/>
+      <c r="D26" s="127"/>
+      <c r="E26" s="126"/>
+      <c r="F26" s="202"/>
+      <c r="G26" s="202"/>
       <c r="H26" s="3"/>
     </row>
     <row r="27" spans="1:8" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="3"/>
-      <c r="B27" s="224"/>
-      <c r="C27" s="200"/>
-      <c r="D27" s="267" t="s">
+      <c r="B27" s="178"/>
+      <c r="C27" s="88"/>
+      <c r="D27" s="128" t="s">
         <v>14</v>
       </c>
-      <c r="E27" s="264"/>
-      <c r="F27" s="268"/>
-      <c r="G27" s="268"/>
+      <c r="E27" s="125"/>
+      <c r="F27" s="202"/>
+      <c r="G27" s="202"/>
       <c r="H27" s="3"/>
     </row>
     <row r="28" spans="1:8" ht="3.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="3"/>
-      <c r="B28" s="224"/>
-      <c r="C28" s="198"/>
-      <c r="D28" s="266"/>
-      <c r="E28" s="265"/>
-      <c r="F28" s="268"/>
-      <c r="G28" s="268"/>
+      <c r="B28" s="178"/>
+      <c r="C28" s="87"/>
+      <c r="D28" s="127"/>
+      <c r="E28" s="126"/>
+      <c r="F28" s="202"/>
+      <c r="G28" s="202"/>
       <c r="H28" s="3"/>
     </row>
     <row r="29" spans="1:8" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="3"/>
-      <c r="B29" s="224"/>
-      <c r="C29" s="200"/>
-      <c r="D29" s="267" t="s">
+      <c r="B29" s="178"/>
+      <c r="C29" s="88"/>
+      <c r="D29" s="128" t="s">
         <v>15</v>
       </c>
-      <c r="E29" s="264"/>
-      <c r="F29" s="268"/>
-      <c r="G29" s="268"/>
+      <c r="E29" s="125"/>
+      <c r="F29" s="202"/>
+      <c r="G29" s="202"/>
       <c r="H29" s="3"/>
     </row>
     <row r="30" spans="1:8" ht="3.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="3"/>
-      <c r="B30" s="224"/>
-      <c r="C30" s="198"/>
-      <c r="D30" s="266"/>
-      <c r="E30" s="265"/>
-      <c r="F30" s="268"/>
-      <c r="G30" s="268"/>
+      <c r="B30" s="178"/>
+      <c r="C30" s="87"/>
+      <c r="D30" s="127"/>
+      <c r="E30" s="126"/>
+      <c r="F30" s="202"/>
+      <c r="G30" s="202"/>
       <c r="H30" s="3"/>
     </row>
     <row r="31" spans="1:8" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="3"/>
-      <c r="B31" s="224"/>
-      <c r="C31" s="200"/>
-      <c r="D31" s="267" t="s">
+      <c r="B31" s="178"/>
+      <c r="C31" s="88"/>
+      <c r="D31" s="128" t="s">
         <v>16</v>
       </c>
-      <c r="E31" s="264"/>
-      <c r="F31" s="268"/>
-      <c r="G31" s="268"/>
+      <c r="E31" s="125"/>
+      <c r="F31" s="202"/>
+      <c r="G31" s="202"/>
       <c r="H31" s="3"/>
     </row>
     <row r="32" spans="1:8" ht="3.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="3"/>
-      <c r="B32" s="224"/>
-      <c r="C32" s="198"/>
-      <c r="D32" s="266"/>
-      <c r="E32" s="265"/>
-      <c r="F32" s="268"/>
-      <c r="G32" s="268"/>
+      <c r="B32" s="178"/>
+      <c r="C32" s="87"/>
+      <c r="D32" s="127"/>
+      <c r="E32" s="126"/>
+      <c r="F32" s="202"/>
+      <c r="G32" s="202"/>
       <c r="H32" s="3"/>
     </row>
     <row r="33" spans="1:8" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="3"/>
-      <c r="B33" s="224"/>
-      <c r="C33" s="200"/>
-      <c r="D33" s="267" t="s">
+      <c r="B33" s="178"/>
+      <c r="C33" s="88"/>
+      <c r="D33" s="128" t="s">
         <v>233</v>
       </c>
-      <c r="E33" s="264"/>
-      <c r="F33" s="268"/>
-      <c r="G33" s="268"/>
+      <c r="E33" s="125"/>
+      <c r="F33" s="202"/>
+      <c r="G33" s="202"/>
       <c r="H33" s="3"/>
     </row>
     <row r="34" spans="1:8" ht="3.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="3"/>
-      <c r="B34" s="224"/>
-      <c r="C34" s="198"/>
-      <c r="D34" s="269"/>
-      <c r="E34" s="265"/>
-      <c r="F34" s="270"/>
-      <c r="G34" s="270"/>
+      <c r="B34" s="178"/>
+      <c r="C34" s="87"/>
+      <c r="D34" s="129"/>
+      <c r="E34" s="126"/>
+      <c r="F34" s="130"/>
+      <c r="G34" s="130"/>
       <c r="H34" s="26"/>
     </row>
     <row r="35" spans="1:8" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="3"/>
-      <c r="B35" s="224"/>
-      <c r="C35" s="198"/>
-      <c r="D35" s="199" t="s">
+      <c r="B35" s="178"/>
+      <c r="C35" s="87"/>
+      <c r="D35" s="197" t="s">
         <v>232</v>
       </c>
-      <c r="E35" s="271"/>
-      <c r="F35" s="222" t="s">
+      <c r="E35" s="131"/>
+      <c r="F35" s="184" t="s">
         <v>7</v>
       </c>
-      <c r="G35" s="272" t="s">
+      <c r="G35" s="132" t="s">
         <v>3</v>
       </c>
       <c r="H35" s="3"/>
     </row>
     <row r="36" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="3"/>
-      <c r="B36" s="224"/>
-      <c r="C36" s="198"/>
-      <c r="D36" s="224"/>
-      <c r="E36" s="198"/>
-      <c r="F36" s="225"/>
-      <c r="G36" s="232" t="s">
+      <c r="B36" s="178"/>
+      <c r="C36" s="87"/>
+      <c r="D36" s="178"/>
+      <c r="E36" s="87"/>
+      <c r="F36" s="185"/>
+      <c r="G36" s="105" t="s">
         <v>230</v>
       </c>
       <c r="H36" s="3"/>
     </row>
     <row r="37" spans="1:8" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="3"/>
-      <c r="B37" s="224"/>
-      <c r="C37" s="198"/>
-      <c r="D37" s="224"/>
-      <c r="E37" s="198"/>
-      <c r="F37" s="228"/>
-      <c r="G37" s="273" t="s">
+      <c r="B37" s="178"/>
+      <c r="C37" s="87"/>
+      <c r="D37" s="178"/>
+      <c r="E37" s="87"/>
+      <c r="F37" s="186"/>
+      <c r="G37" s="133" t="s">
         <v>6</v>
       </c>
       <c r="H37" s="3"/>
     </row>
     <row r="38" spans="1:8" ht="3.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="3"/>
-      <c r="B38" s="224"/>
-      <c r="C38" s="198"/>
-      <c r="D38" s="224"/>
-      <c r="E38" s="198"/>
-      <c r="F38" s="198"/>
-      <c r="G38" s="198"/>
+      <c r="B38" s="178"/>
+      <c r="C38" s="87"/>
+      <c r="D38" s="178"/>
+      <c r="E38" s="87"/>
+      <c r="F38" s="87"/>
+      <c r="G38" s="87"/>
       <c r="H38" s="26"/>
     </row>
     <row r="39" spans="1:8" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="3"/>
-      <c r="B39" s="224"/>
-      <c r="C39" s="198"/>
-      <c r="D39" s="224"/>
-      <c r="E39" s="198"/>
-      <c r="F39" s="222" t="s">
+      <c r="B39" s="178"/>
+      <c r="C39" s="87"/>
+      <c r="D39" s="178"/>
+      <c r="E39" s="87"/>
+      <c r="F39" s="184" t="s">
         <v>8</v>
       </c>
-      <c r="G39" s="272" t="s">
+      <c r="G39" s="132" t="s">
         <v>3</v>
       </c>
       <c r="H39" s="3"/>
     </row>
     <row r="40" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="3"/>
-      <c r="B40" s="224"/>
-      <c r="C40" s="198"/>
-      <c r="D40" s="224"/>
-      <c r="E40" s="198"/>
-      <c r="F40" s="225"/>
-      <c r="G40" s="232" t="s">
+      <c r="B40" s="178"/>
+      <c r="C40" s="87"/>
+      <c r="D40" s="178"/>
+      <c r="E40" s="87"/>
+      <c r="F40" s="185"/>
+      <c r="G40" s="105" t="s">
         <v>230</v>
       </c>
       <c r="H40" s="3"/>
     </row>
     <row r="41" spans="1:8" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="3"/>
-      <c r="B41" s="224"/>
-      <c r="C41" s="198"/>
-      <c r="D41" s="241"/>
-      <c r="E41" s="198"/>
-      <c r="F41" s="228"/>
-      <c r="G41" s="273" t="s">
+      <c r="B41" s="178"/>
+      <c r="C41" s="87"/>
+      <c r="D41" s="179"/>
+      <c r="E41" s="87"/>
+      <c r="F41" s="186"/>
+      <c r="G41" s="133" t="s">
         <v>5</v>
       </c>
       <c r="H41" s="3"/>
     </row>
     <row r="42" spans="1:8" ht="3.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="3"/>
-      <c r="B42" s="224"/>
-      <c r="C42" s="198"/>
-      <c r="D42" s="198"/>
-      <c r="E42" s="198"/>
-      <c r="F42" s="198"/>
-      <c r="G42" s="198"/>
+      <c r="B42" s="178"/>
+      <c r="C42" s="87"/>
+      <c r="D42" s="87"/>
+      <c r="E42" s="87"/>
+      <c r="F42" s="87"/>
+      <c r="G42" s="87"/>
       <c r="H42" s="3"/>
     </row>
     <row r="43" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="3"/>
-      <c r="B43" s="241"/>
-      <c r="C43" s="198"/>
-      <c r="D43" s="236" t="s">
+      <c r="B43" s="179"/>
+      <c r="C43" s="87"/>
+      <c r="D43" s="109" t="s">
         <v>245</v>
       </c>
-      <c r="E43" s="198"/>
-      <c r="F43" s="239" t="s">
+      <c r="E43" s="87"/>
+      <c r="F43" s="180" t="s">
         <v>245</v>
       </c>
-      <c r="G43" s="240"/>
+      <c r="G43" s="181"/>
       <c r="H43" s="3"/>
     </row>
     <row r="44" spans="1:8" ht="7.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -17898,386 +17904,386 @@
     </row>
     <row r="3" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="3"/>
-      <c r="B3" s="181"/>
-      <c r="C3" s="183" t="s">
+      <c r="B3" s="203"/>
+      <c r="C3" s="205" t="s">
         <v>156</v>
       </c>
-      <c r="D3" s="184"/>
-      <c r="E3" s="185"/>
-      <c r="F3" s="183" t="s">
+      <c r="D3" s="206"/>
+      <c r="E3" s="207"/>
+      <c r="F3" s="205" t="s">
         <v>155</v>
       </c>
-      <c r="G3" s="189"/>
+      <c r="G3" s="211"/>
       <c r="H3" s="3"/>
     </row>
     <row r="4" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="3"/>
-      <c r="B4" s="182"/>
-      <c r="C4" s="186"/>
-      <c r="D4" s="187"/>
-      <c r="E4" s="188"/>
-      <c r="F4" s="186"/>
-      <c r="G4" s="190"/>
+      <c r="B4" s="204"/>
+      <c r="C4" s="208"/>
+      <c r="D4" s="209"/>
+      <c r="E4" s="210"/>
+      <c r="F4" s="208"/>
+      <c r="G4" s="212"/>
       <c r="H4" s="3"/>
     </row>
     <row r="5" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="3"/>
-      <c r="B5" s="169" t="s">
+      <c r="B5" s="213" t="s">
         <v>147</v>
       </c>
-      <c r="C5" s="143" t="s">
+      <c r="C5" s="216" t="s">
         <v>153</v>
       </c>
-      <c r="D5" s="191"/>
-      <c r="E5" s="178"/>
-      <c r="F5" s="143" t="s">
+      <c r="D5" s="218"/>
+      <c r="E5" s="223"/>
+      <c r="F5" s="216" t="s">
         <v>93</v>
       </c>
-      <c r="G5" s="160" t="s">
+      <c r="G5" s="228" t="s">
         <v>157</v>
       </c>
       <c r="H5" s="3"/>
     </row>
     <row r="6" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="3"/>
-      <c r="B6" s="170"/>
-      <c r="C6" s="137"/>
-      <c r="D6" s="192"/>
-      <c r="E6" s="179"/>
-      <c r="F6" s="137"/>
-      <c r="G6" s="161"/>
+      <c r="B6" s="214"/>
+      <c r="C6" s="217"/>
+      <c r="D6" s="219"/>
+      <c r="E6" s="224"/>
+      <c r="F6" s="217"/>
+      <c r="G6" s="229"/>
       <c r="H6" s="3"/>
     </row>
     <row r="7" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="3"/>
-      <c r="B7" s="170"/>
-      <c r="C7" s="137" t="s">
+      <c r="B7" s="214"/>
+      <c r="C7" s="217" t="s">
         <v>154</v>
       </c>
-      <c r="D7" s="192"/>
-      <c r="E7" s="179"/>
-      <c r="F7" s="137" t="s">
+      <c r="D7" s="219"/>
+      <c r="E7" s="224"/>
+      <c r="F7" s="217" t="s">
         <v>174</v>
       </c>
-      <c r="G7" s="161" t="s">
+      <c r="G7" s="229" t="s">
         <v>170</v>
       </c>
       <c r="H7" s="3"/>
     </row>
     <row r="8" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="3"/>
-      <c r="B8" s="174"/>
-      <c r="C8" s="168"/>
-      <c r="D8" s="193"/>
-      <c r="E8" s="180"/>
-      <c r="F8" s="168"/>
-      <c r="G8" s="175"/>
+      <c r="B8" s="215"/>
+      <c r="C8" s="230"/>
+      <c r="D8" s="220"/>
+      <c r="E8" s="225"/>
+      <c r="F8" s="230"/>
+      <c r="G8" s="233"/>
       <c r="H8" s="3"/>
     </row>
     <row r="9" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="3"/>
-      <c r="B9" s="169" t="s">
+      <c r="B9" s="213" t="s">
         <v>148</v>
       </c>
-      <c r="C9" s="143" t="s">
+      <c r="C9" s="216" t="s">
         <v>172</v>
       </c>
-      <c r="D9" s="172" t="s">
+      <c r="D9" s="221" t="s">
         <v>158</v>
       </c>
-      <c r="E9" s="173" t="s">
+      <c r="E9" s="226" t="s">
         <v>160</v>
       </c>
-      <c r="F9" s="143" t="s">
+      <c r="F9" s="216" t="s">
         <v>93</v>
       </c>
-      <c r="G9" s="160" t="s">
+      <c r="G9" s="228" t="s">
         <v>157</v>
       </c>
       <c r="H9" s="3"/>
     </row>
     <row r="10" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="3"/>
-      <c r="B10" s="170"/>
-      <c r="C10" s="137"/>
-      <c r="D10" s="162"/>
-      <c r="E10" s="164"/>
-      <c r="F10" s="137"/>
-      <c r="G10" s="161"/>
+      <c r="B10" s="214"/>
+      <c r="C10" s="217"/>
+      <c r="D10" s="222"/>
+      <c r="E10" s="227"/>
+      <c r="F10" s="217"/>
+      <c r="G10" s="229"/>
       <c r="H10" s="3"/>
     </row>
     <row r="11" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="3"/>
-      <c r="B11" s="170"/>
-      <c r="C11" s="137" t="s">
+      <c r="B11" s="214"/>
+      <c r="C11" s="217" t="s">
         <v>162</v>
       </c>
-      <c r="D11" s="162" t="s">
+      <c r="D11" s="222" t="s">
         <v>159</v>
       </c>
-      <c r="E11" s="164" t="s">
+      <c r="E11" s="227" t="s">
         <v>161</v>
       </c>
-      <c r="F11" s="137" t="s">
+      <c r="F11" s="217" t="s">
         <v>175</v>
       </c>
-      <c r="G11" s="161" t="s">
+      <c r="G11" s="229" t="s">
         <v>170</v>
       </c>
       <c r="H11" s="3"/>
     </row>
     <row r="12" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="3"/>
-      <c r="B12" s="174"/>
-      <c r="C12" s="168"/>
-      <c r="D12" s="176"/>
-      <c r="E12" s="177"/>
-      <c r="F12" s="168"/>
-      <c r="G12" s="175"/>
+      <c r="B12" s="215"/>
+      <c r="C12" s="230"/>
+      <c r="D12" s="231"/>
+      <c r="E12" s="232"/>
+      <c r="F12" s="230"/>
+      <c r="G12" s="233"/>
       <c r="H12" s="3"/>
     </row>
     <row r="13" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="3"/>
-      <c r="B13" s="169" t="s">
+      <c r="B13" s="213" t="s">
         <v>149</v>
       </c>
-      <c r="C13" s="143" t="s">
+      <c r="C13" s="216" t="s">
         <v>163</v>
       </c>
-      <c r="D13" s="172" t="s">
+      <c r="D13" s="221" t="s">
         <v>165</v>
       </c>
-      <c r="E13" s="178"/>
-      <c r="F13" s="143" t="s">
+      <c r="E13" s="223"/>
+      <c r="F13" s="216" t="s">
         <v>93</v>
       </c>
-      <c r="G13" s="160" t="s">
+      <c r="G13" s="228" t="s">
         <v>157</v>
       </c>
       <c r="H13" s="3"/>
     </row>
     <row r="14" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="3"/>
-      <c r="B14" s="170"/>
-      <c r="C14" s="137"/>
-      <c r="D14" s="162"/>
-      <c r="E14" s="179"/>
-      <c r="F14" s="137"/>
-      <c r="G14" s="161"/>
+      <c r="B14" s="214"/>
+      <c r="C14" s="217"/>
+      <c r="D14" s="222"/>
+      <c r="E14" s="224"/>
+      <c r="F14" s="217"/>
+      <c r="G14" s="229"/>
       <c r="H14" s="3"/>
     </row>
     <row r="15" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="3"/>
-      <c r="B15" s="170"/>
-      <c r="C15" s="137" t="s">
+      <c r="B15" s="214"/>
+      <c r="C15" s="217" t="s">
         <v>164</v>
       </c>
-      <c r="D15" s="162" t="s">
+      <c r="D15" s="222" t="s">
         <v>166</v>
       </c>
-      <c r="E15" s="179"/>
-      <c r="F15" s="137" t="s">
+      <c r="E15" s="224"/>
+      <c r="F15" s="217" t="s">
         <v>179</v>
       </c>
-      <c r="G15" s="161" t="s">
+      <c r="G15" s="229" t="s">
         <v>170</v>
       </c>
       <c r="H15" s="3"/>
     </row>
     <row r="16" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="3"/>
-      <c r="B16" s="174"/>
-      <c r="C16" s="168"/>
-      <c r="D16" s="176"/>
-      <c r="E16" s="180"/>
-      <c r="F16" s="168"/>
-      <c r="G16" s="175"/>
+      <c r="B16" s="215"/>
+      <c r="C16" s="230"/>
+      <c r="D16" s="231"/>
+      <c r="E16" s="225"/>
+      <c r="F16" s="230"/>
+      <c r="G16" s="233"/>
       <c r="H16" s="3"/>
     </row>
     <row r="17" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="3"/>
-      <c r="B17" s="169" t="s">
+      <c r="B17" s="213" t="s">
         <v>152</v>
       </c>
-      <c r="C17" s="143" t="s">
+      <c r="C17" s="216" t="s">
         <v>172</v>
       </c>
-      <c r="D17" s="172" t="s">
+      <c r="D17" s="221" t="s">
         <v>158</v>
       </c>
-      <c r="E17" s="173" t="s">
+      <c r="E17" s="226" t="s">
         <v>160</v>
       </c>
-      <c r="F17" s="143" t="s">
+      <c r="F17" s="216" t="s">
         <v>93</v>
       </c>
-      <c r="G17" s="160" t="s">
+      <c r="G17" s="228" t="s">
         <v>157</v>
       </c>
       <c r="H17" s="3"/>
     </row>
     <row r="18" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="3"/>
-      <c r="B18" s="170"/>
-      <c r="C18" s="137"/>
-      <c r="D18" s="162"/>
-      <c r="E18" s="164"/>
-      <c r="F18" s="137"/>
-      <c r="G18" s="161"/>
+      <c r="B18" s="214"/>
+      <c r="C18" s="217"/>
+      <c r="D18" s="222"/>
+      <c r="E18" s="227"/>
+      <c r="F18" s="217"/>
+      <c r="G18" s="229"/>
       <c r="H18" s="3"/>
     </row>
     <row r="19" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="3"/>
-      <c r="B19" s="170"/>
-      <c r="C19" s="137" t="s">
+      <c r="B19" s="214"/>
+      <c r="C19" s="217" t="s">
         <v>162</v>
       </c>
-      <c r="D19" s="162" t="s">
+      <c r="D19" s="222" t="s">
         <v>168</v>
       </c>
-      <c r="E19" s="164" t="s">
+      <c r="E19" s="227" t="s">
         <v>161</v>
       </c>
-      <c r="F19" s="137" t="s">
+      <c r="F19" s="217" t="s">
         <v>180</v>
       </c>
-      <c r="G19" s="161" t="s">
+      <c r="G19" s="229" t="s">
         <v>170</v>
       </c>
       <c r="H19" s="3"/>
     </row>
     <row r="20" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="3"/>
-      <c r="B20" s="174"/>
-      <c r="C20" s="168"/>
-      <c r="D20" s="176"/>
-      <c r="E20" s="177"/>
-      <c r="F20" s="168"/>
-      <c r="G20" s="175"/>
+      <c r="B20" s="215"/>
+      <c r="C20" s="230"/>
+      <c r="D20" s="231"/>
+      <c r="E20" s="232"/>
+      <c r="F20" s="230"/>
+      <c r="G20" s="233"/>
       <c r="H20" s="3"/>
     </row>
     <row r="21" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="3"/>
-      <c r="B21" s="169" t="s">
+      <c r="B21" s="213" t="s">
         <v>150</v>
       </c>
-      <c r="C21" s="143" t="s">
+      <c r="C21" s="216" t="s">
         <v>172</v>
       </c>
-      <c r="D21" s="172" t="s">
+      <c r="D21" s="221" t="s">
         <v>171</v>
       </c>
-      <c r="E21" s="173" t="s">
+      <c r="E21" s="226" t="s">
         <v>160</v>
       </c>
-      <c r="F21" s="143" t="s">
+      <c r="F21" s="216" t="s">
         <v>93</v>
       </c>
-      <c r="G21" s="160" t="s">
+      <c r="G21" s="228" t="s">
         <v>157</v>
       </c>
       <c r="H21" s="3"/>
     </row>
     <row r="22" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="3"/>
-      <c r="B22" s="170"/>
-      <c r="C22" s="137"/>
-      <c r="D22" s="162"/>
-      <c r="E22" s="164"/>
-      <c r="F22" s="137"/>
-      <c r="G22" s="161"/>
+      <c r="B22" s="214"/>
+      <c r="C22" s="217"/>
+      <c r="D22" s="222"/>
+      <c r="E22" s="227"/>
+      <c r="F22" s="217"/>
+      <c r="G22" s="229"/>
       <c r="H22" s="3"/>
     </row>
     <row r="23" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="3"/>
-      <c r="B23" s="170"/>
-      <c r="C23" s="137" t="s">
+      <c r="B23" s="214"/>
+      <c r="C23" s="217" t="s">
         <v>162</v>
       </c>
-      <c r="D23" s="162" t="s">
+      <c r="D23" s="222" t="s">
         <v>154</v>
       </c>
-      <c r="E23" s="164" t="s">
+      <c r="E23" s="227" t="s">
         <v>169</v>
       </c>
-      <c r="F23" s="137" t="s">
+      <c r="F23" s="217" t="s">
         <v>176</v>
       </c>
-      <c r="G23" s="161" t="s">
+      <c r="G23" s="229" t="s">
         <v>170</v>
       </c>
       <c r="H23" s="3"/>
     </row>
     <row r="24" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="3"/>
-      <c r="B24" s="174"/>
-      <c r="C24" s="168"/>
-      <c r="D24" s="176"/>
-      <c r="E24" s="177"/>
-      <c r="F24" s="168"/>
-      <c r="G24" s="175"/>
+      <c r="B24" s="215"/>
+      <c r="C24" s="230"/>
+      <c r="D24" s="231"/>
+      <c r="E24" s="232"/>
+      <c r="F24" s="230"/>
+      <c r="G24" s="233"/>
       <c r="H24" s="3"/>
     </row>
     <row r="25" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="3"/>
-      <c r="B25" s="169" t="s">
+      <c r="B25" s="213" t="s">
         <v>151</v>
       </c>
-      <c r="C25" s="143" t="s">
+      <c r="C25" s="216" t="s">
         <v>172</v>
       </c>
-      <c r="D25" s="172" t="s">
+      <c r="D25" s="221" t="s">
         <v>171</v>
       </c>
-      <c r="E25" s="173" t="s">
+      <c r="E25" s="226" t="s">
         <v>160</v>
       </c>
-      <c r="F25" s="143" t="s">
+      <c r="F25" s="216" t="s">
         <v>93</v>
       </c>
-      <c r="G25" s="160" t="s">
+      <c r="G25" s="228" t="s">
         <v>157</v>
       </c>
       <c r="H25" s="3"/>
     </row>
     <row r="26" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="3"/>
-      <c r="B26" s="170"/>
-      <c r="C26" s="137"/>
-      <c r="D26" s="162"/>
-      <c r="E26" s="164"/>
-      <c r="F26" s="137"/>
-      <c r="G26" s="161"/>
+      <c r="B26" s="214"/>
+      <c r="C26" s="217"/>
+      <c r="D26" s="222"/>
+      <c r="E26" s="227"/>
+      <c r="F26" s="217"/>
+      <c r="G26" s="229"/>
       <c r="H26" s="3"/>
     </row>
     <row r="27" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="3"/>
-      <c r="B27" s="170"/>
-      <c r="C27" s="137" t="s">
+      <c r="B27" s="214"/>
+      <c r="C27" s="217" t="s">
         <v>162</v>
       </c>
-      <c r="D27" s="162" t="s">
+      <c r="D27" s="222" t="s">
         <v>154</v>
       </c>
-      <c r="E27" s="164" t="s">
+      <c r="E27" s="227" t="s">
         <v>161</v>
       </c>
-      <c r="F27" s="137" t="s">
+      <c r="F27" s="217" t="s">
         <v>177</v>
       </c>
-      <c r="G27" s="161" t="s">
+      <c r="G27" s="229" t="s">
         <v>170</v>
       </c>
       <c r="H27" s="3"/>
     </row>
     <row r="28" spans="1:8" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A28" s="3"/>
-      <c r="B28" s="171"/>
-      <c r="C28" s="139"/>
-      <c r="D28" s="163"/>
-      <c r="E28" s="165"/>
-      <c r="F28" s="139"/>
-      <c r="G28" s="166"/>
+      <c r="B28" s="246"/>
+      <c r="C28" s="239"/>
+      <c r="D28" s="240"/>
+      <c r="E28" s="241"/>
+      <c r="F28" s="239"/>
+      <c r="G28" s="242"/>
       <c r="H28" s="3"/>
     </row>
     <row r="29" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
@@ -18293,56 +18299,56 @@
     <row r="30" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="3"/>
       <c r="B30" s="3"/>
-      <c r="C30" s="157" t="s">
+      <c r="C30" s="234" t="s">
         <v>181</v>
       </c>
       <c r="D30" s="3"/>
       <c r="E30" s="3"/>
-      <c r="F30" s="157" t="s">
+      <c r="F30" s="234" t="s">
         <v>178</v>
       </c>
-      <c r="G30" s="157"/>
+      <c r="G30" s="234"/>
       <c r="H30" s="3"/>
     </row>
     <row r="31" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="3"/>
       <c r="B31" s="3"/>
-      <c r="C31" s="157"/>
+      <c r="C31" s="234"/>
       <c r="D31" s="3"/>
       <c r="E31" s="3"/>
-      <c r="F31" s="157"/>
-      <c r="G31" s="157"/>
+      <c r="F31" s="234"/>
+      <c r="G31" s="234"/>
       <c r="H31" s="3"/>
     </row>
     <row r="32" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="3"/>
       <c r="B32" s="3"/>
-      <c r="C32" s="157"/>
+      <c r="C32" s="234"/>
       <c r="D32" s="3"/>
       <c r="E32" s="3"/>
-      <c r="F32" s="157"/>
-      <c r="G32" s="157"/>
+      <c r="F32" s="234"/>
+      <c r="G32" s="234"/>
       <c r="H32" s="3"/>
     </row>
     <row r="33" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="3"/>
       <c r="B33" s="3"/>
-      <c r="C33" s="158" t="s">
+      <c r="C33" s="235" t="s">
         <v>207</v>
       </c>
       <c r="D33" s="3"/>
       <c r="E33" s="3"/>
-      <c r="F33" s="159"/>
+      <c r="F33" s="236"/>
       <c r="G33" s="3"/>
       <c r="H33" s="3"/>
     </row>
     <row r="34" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="3"/>
       <c r="B34" s="3"/>
-      <c r="C34" s="158"/>
+      <c r="C34" s="235"/>
       <c r="D34" s="3"/>
       <c r="E34" s="3"/>
-      <c r="F34" s="159"/>
+      <c r="F34" s="236"/>
       <c r="G34" s="3"/>
       <c r="H34" s="3"/>
     </row>
@@ -18378,13 +18384,13 @@
     </row>
     <row r="38" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="3"/>
-      <c r="B38" s="132" t="s">
+      <c r="B38" s="237" t="s">
         <v>158</v>
       </c>
-      <c r="C38" s="167" t="s">
+      <c r="C38" s="243" t="s">
         <v>198</v>
       </c>
-      <c r="D38" s="133" t="s">
+      <c r="D38" s="244" t="s">
         <v>199</v>
       </c>
       <c r="E38" s="3"/>
@@ -18394,9 +18400,9 @@
     </row>
     <row r="39" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="3"/>
-      <c r="B39" s="128"/>
-      <c r="C39" s="168"/>
-      <c r="D39" s="130"/>
+      <c r="B39" s="238"/>
+      <c r="C39" s="230"/>
+      <c r="D39" s="245"/>
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
       <c r="G39" s="3"/>
@@ -18404,13 +18410,13 @@
     </row>
     <row r="40" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="3"/>
-      <c r="B40" s="122" t="s">
+      <c r="B40" s="247" t="s">
         <v>225</v>
       </c>
-      <c r="C40" s="137" t="s">
+      <c r="C40" s="217" t="s">
         <v>185</v>
       </c>
-      <c r="D40" s="123" t="s">
+      <c r="D40" s="248" t="s">
         <v>201</v>
       </c>
       <c r="E40" s="3"/>
@@ -18420,9 +18426,9 @@
     </row>
     <row r="41" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="3"/>
-      <c r="B41" s="122"/>
-      <c r="C41" s="137"/>
-      <c r="D41" s="123"/>
+      <c r="B41" s="247"/>
+      <c r="C41" s="217"/>
+      <c r="D41" s="248"/>
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
       <c r="G41" s="3"/>
@@ -18430,13 +18436,13 @@
     </row>
     <row r="42" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="3"/>
-      <c r="B42" s="122" t="s">
+      <c r="B42" s="247" t="s">
         <v>224</v>
       </c>
-      <c r="C42" s="137" t="s">
+      <c r="C42" s="217" t="s">
         <v>224</v>
       </c>
-      <c r="D42" s="123" t="s">
+      <c r="D42" s="248" t="s">
         <v>223</v>
       </c>
       <c r="E42" s="3"/>
@@ -18446,9 +18452,9 @@
     </row>
     <row r="43" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="3"/>
-      <c r="B43" s="122"/>
-      <c r="C43" s="137"/>
-      <c r="D43" s="123"/>
+      <c r="B43" s="247"/>
+      <c r="C43" s="217"/>
+      <c r="D43" s="248"/>
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
       <c r="G43" s="3"/>
@@ -18456,13 +18462,13 @@
     </row>
     <row r="44" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="3"/>
-      <c r="B44" s="122" t="s">
+      <c r="B44" s="247" t="s">
         <v>221</v>
       </c>
-      <c r="C44" s="137" t="s">
+      <c r="C44" s="217" t="s">
         <v>221</v>
       </c>
-      <c r="D44" s="123" t="s">
+      <c r="D44" s="248" t="s">
         <v>222</v>
       </c>
       <c r="E44" s="3"/>
@@ -18472,9 +18478,9 @@
     </row>
     <row r="45" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="3"/>
-      <c r="B45" s="122"/>
-      <c r="C45" s="137"/>
-      <c r="D45" s="123"/>
+      <c r="B45" s="247"/>
+      <c r="C45" s="217"/>
+      <c r="D45" s="248"/>
       <c r="E45" s="3"/>
       <c r="F45" s="3"/>
       <c r="G45" s="3"/>
@@ -18482,13 +18488,13 @@
     </row>
     <row r="46" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="3"/>
-      <c r="B46" s="134" t="s">
+      <c r="B46" s="258" t="s">
         <v>184</v>
       </c>
-      <c r="C46" s="146" t="s">
+      <c r="C46" s="259" t="s">
         <v>188</v>
       </c>
-      <c r="D46" s="147" t="s">
+      <c r="D46" s="260" t="s">
         <v>200</v>
       </c>
       <c r="E46" s="3"/>
@@ -18498,9 +18504,9 @@
     </row>
     <row r="47" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="3"/>
-      <c r="B47" s="122"/>
-      <c r="C47" s="137"/>
-      <c r="D47" s="123"/>
+      <c r="B47" s="247"/>
+      <c r="C47" s="217"/>
+      <c r="D47" s="248"/>
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
       <c r="G47" s="3"/>
@@ -18508,13 +18514,13 @@
     </row>
     <row r="48" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="3"/>
-      <c r="B48" s="148" t="s">
+      <c r="B48" s="261" t="s">
         <v>186</v>
       </c>
-      <c r="C48" s="150" t="s">
+      <c r="C48" s="263" t="s">
         <v>189</v>
       </c>
-      <c r="D48" s="126" t="s">
+      <c r="D48" s="264" t="s">
         <v>202</v>
       </c>
       <c r="E48" s="3"/>
@@ -18524,9 +18530,9 @@
     </row>
     <row r="49" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="3"/>
-      <c r="B49" s="149"/>
-      <c r="C49" s="146"/>
-      <c r="D49" s="147"/>
+      <c r="B49" s="262"/>
+      <c r="C49" s="259"/>
+      <c r="D49" s="260"/>
       <c r="E49" s="3"/>
       <c r="F49" s="3"/>
       <c r="G49" s="3"/>
@@ -18534,13 +18540,13 @@
     </row>
     <row r="50" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="3"/>
-      <c r="B50" s="151" t="s">
+      <c r="B50" s="265" t="s">
         <v>187</v>
       </c>
-      <c r="C50" s="153" t="s">
+      <c r="C50" s="249" t="s">
         <v>187</v>
       </c>
-      <c r="D50" s="155" t="s">
+      <c r="D50" s="251" t="s">
         <v>203</v>
       </c>
       <c r="E50" s="3"/>
@@ -18550,9 +18556,9 @@
     </row>
     <row r="51" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="3"/>
-      <c r="B51" s="152"/>
-      <c r="C51" s="154"/>
-      <c r="D51" s="156"/>
+      <c r="B51" s="266"/>
+      <c r="C51" s="250"/>
+      <c r="D51" s="252"/>
       <c r="E51" s="3"/>
       <c r="F51" s="3"/>
       <c r="G51" s="3"/>
@@ -18560,13 +18566,13 @@
     </row>
     <row r="52" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="3"/>
-      <c r="B52" s="140" t="s">
+      <c r="B52" s="253" t="s">
         <v>190</v>
       </c>
-      <c r="C52" s="142" t="s">
+      <c r="C52" s="255" t="s">
         <v>190</v>
       </c>
-      <c r="D52" s="144" t="s">
+      <c r="D52" s="256" t="s">
         <v>204</v>
       </c>
       <c r="E52" s="3"/>
@@ -18576,9 +18582,9 @@
     </row>
     <row r="53" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="3"/>
-      <c r="B53" s="141"/>
-      <c r="C53" s="143"/>
-      <c r="D53" s="145"/>
+      <c r="B53" s="254"/>
+      <c r="C53" s="216"/>
+      <c r="D53" s="257"/>
       <c r="E53" s="3"/>
       <c r="F53" s="3"/>
       <c r="G53" s="3"/>
@@ -18586,13 +18592,13 @@
     </row>
     <row r="54" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="3"/>
-      <c r="B54" s="122" t="s">
+      <c r="B54" s="247" t="s">
         <v>191</v>
       </c>
-      <c r="C54" s="137" t="s">
+      <c r="C54" s="217" t="s">
         <v>194</v>
       </c>
-      <c r="D54" s="123" t="s">
+      <c r="D54" s="248" t="s">
         <v>205</v>
       </c>
       <c r="E54" s="3"/>
@@ -18602,9 +18608,9 @@
     </row>
     <row r="55" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="3"/>
-      <c r="B55" s="122"/>
-      <c r="C55" s="137"/>
-      <c r="D55" s="123"/>
+      <c r="B55" s="247"/>
+      <c r="C55" s="217"/>
+      <c r="D55" s="248"/>
       <c r="E55" s="3"/>
       <c r="F55" s="3"/>
       <c r="G55" s="3"/>
@@ -18612,13 +18618,13 @@
     </row>
     <row r="56" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="3"/>
-      <c r="B56" s="122" t="s">
+      <c r="B56" s="247" t="s">
         <v>192</v>
       </c>
-      <c r="C56" s="137" t="s">
+      <c r="C56" s="217" t="s">
         <v>195</v>
       </c>
-      <c r="D56" s="123" t="s">
+      <c r="D56" s="248" t="s">
         <v>206</v>
       </c>
       <c r="E56" s="3"/>
@@ -18628,9 +18634,9 @@
     </row>
     <row r="57" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="3"/>
-      <c r="B57" s="122"/>
-      <c r="C57" s="137"/>
-      <c r="D57" s="123"/>
+      <c r="B57" s="247"/>
+      <c r="C57" s="217"/>
+      <c r="D57" s="248"/>
       <c r="E57" s="3"/>
       <c r="F57" s="3"/>
       <c r="G57" s="3"/>
@@ -18638,13 +18644,13 @@
     </row>
     <row r="58" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="3"/>
-      <c r="B58" s="122" t="s">
+      <c r="B58" s="247" t="s">
         <v>187</v>
       </c>
-      <c r="C58" s="137" t="s">
+      <c r="C58" s="217" t="s">
         <v>187</v>
       </c>
-      <c r="D58" s="123" t="s">
+      <c r="D58" s="248" t="s">
         <v>203</v>
       </c>
       <c r="E58" s="3"/>
@@ -18654,9 +18660,9 @@
     </row>
     <row r="59" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="3"/>
-      <c r="B59" s="122"/>
-      <c r="C59" s="137"/>
-      <c r="D59" s="123"/>
+      <c r="B59" s="247"/>
+      <c r="C59" s="217"/>
+      <c r="D59" s="248"/>
       <c r="E59" s="3"/>
       <c r="F59" s="3"/>
       <c r="G59" s="3"/>
@@ -18664,13 +18670,13 @@
     </row>
     <row r="60" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="3"/>
-      <c r="B60" s="122" t="s">
+      <c r="B60" s="247" t="s">
         <v>193</v>
       </c>
-      <c r="C60" s="137" t="s">
+      <c r="C60" s="217" t="s">
         <v>197</v>
       </c>
-      <c r="D60" s="123" t="s">
+      <c r="D60" s="248" t="s">
         <v>196</v>
       </c>
       <c r="E60" s="3"/>
@@ -18680,9 +18686,9 @@
     </row>
     <row r="61" spans="1:8" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A61" s="3"/>
-      <c r="B61" s="138"/>
-      <c r="C61" s="139"/>
-      <c r="D61" s="136"/>
+      <c r="B61" s="267"/>
+      <c r="C61" s="239"/>
+      <c r="D61" s="271"/>
       <c r="E61" s="3"/>
       <c r="F61" s="3"/>
       <c r="G61" s="3"/>
@@ -18710,10 +18716,10 @@
     </row>
     <row r="64" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="3"/>
-      <c r="B64" s="132" t="s">
+      <c r="B64" s="237" t="s">
         <v>208</v>
       </c>
-      <c r="C64" s="133"/>
+      <c r="C64" s="244"/>
       <c r="D64" s="3"/>
       <c r="E64" s="3"/>
       <c r="F64" s="3"/>
@@ -18722,8 +18728,8 @@
     </row>
     <row r="65" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="3"/>
-      <c r="B65" s="128"/>
-      <c r="C65" s="130"/>
+      <c r="B65" s="238"/>
+      <c r="C65" s="245"/>
       <c r="D65" s="3"/>
       <c r="E65" s="3"/>
       <c r="F65" s="3"/>
@@ -18732,10 +18738,10 @@
     </row>
     <row r="66" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="3"/>
-      <c r="B66" s="134" t="s">
+      <c r="B66" s="258" t="s">
         <v>209</v>
       </c>
-      <c r="C66" s="135" t="s">
+      <c r="C66" s="270" t="s">
         <v>213</v>
       </c>
       <c r="D66" s="3"/>
@@ -18746,8 +18752,8 @@
     </row>
     <row r="67" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" s="3"/>
-      <c r="B67" s="122"/>
-      <c r="C67" s="123"/>
+      <c r="B67" s="247"/>
+      <c r="C67" s="248"/>
       <c r="D67" s="3"/>
       <c r="E67" s="3"/>
       <c r="F67" s="3"/>
@@ -18756,10 +18762,10 @@
     </row>
     <row r="68" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="3"/>
-      <c r="B68" s="122" t="s">
+      <c r="B68" s="247" t="s">
         <v>210</v>
       </c>
-      <c r="C68" s="123">
+      <c r="C68" s="248">
         <v>1</v>
       </c>
       <c r="D68" s="3"/>
@@ -18770,8 +18776,8 @@
     </row>
     <row r="69" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69" s="3"/>
-      <c r="B69" s="122"/>
-      <c r="C69" s="123"/>
+      <c r="B69" s="247"/>
+      <c r="C69" s="248"/>
       <c r="D69" s="3"/>
       <c r="E69" s="3"/>
       <c r="F69" s="3"/>
@@ -18780,10 +18786,10 @@
     </row>
     <row r="70" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="3"/>
-      <c r="B70" s="122" t="s">
+      <c r="B70" s="247" t="s">
         <v>211</v>
       </c>
-      <c r="C70" s="123">
+      <c r="C70" s="248">
         <v>2</v>
       </c>
       <c r="D70" s="3"/>
@@ -18794,8 +18800,8 @@
     </row>
     <row r="71" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A71" s="3"/>
-      <c r="B71" s="122"/>
-      <c r="C71" s="123"/>
+      <c r="B71" s="247"/>
+      <c r="C71" s="248"/>
       <c r="D71" s="3"/>
       <c r="E71" s="3"/>
       <c r="F71" s="3"/>
@@ -18804,10 +18810,10 @@
     </row>
     <row r="72" spans="1:8" ht="9.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="3"/>
-      <c r="B72" s="128" t="s">
+      <c r="B72" s="238" t="s">
         <v>212</v>
       </c>
-      <c r="C72" s="130">
+      <c r="C72" s="245">
         <v>4</v>
       </c>
       <c r="D72" s="3"/>
@@ -18818,8 +18824,8 @@
     </row>
     <row r="73" spans="1:8" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A73" s="3"/>
-      <c r="B73" s="129"/>
-      <c r="C73" s="131"/>
+      <c r="B73" s="268"/>
+      <c r="C73" s="269"/>
       <c r="D73" s="3"/>
       <c r="E73" s="3"/>
       <c r="F73" s="3"/>
@@ -18848,10 +18854,10 @@
     </row>
     <row r="76" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" s="3"/>
-      <c r="B76" s="132" t="s">
+      <c r="B76" s="237" t="s">
         <v>214</v>
       </c>
-      <c r="C76" s="133" t="s">
+      <c r="C76" s="244" t="s">
         <v>215</v>
       </c>
       <c r="D76" s="3"/>
@@ -18862,8 +18868,8 @@
     </row>
     <row r="77" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="3"/>
-      <c r="B77" s="128"/>
-      <c r="C77" s="130"/>
+      <c r="B77" s="238"/>
+      <c r="C77" s="245"/>
       <c r="D77" s="3"/>
       <c r="E77" s="3"/>
       <c r="F77" s="3"/>
@@ -18872,10 +18878,10 @@
     </row>
     <row r="78" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78" s="3"/>
-      <c r="B78" s="134" t="s">
+      <c r="B78" s="258" t="s">
         <v>216</v>
       </c>
-      <c r="C78" s="135" t="s">
+      <c r="C78" s="270" t="s">
         <v>174</v>
       </c>
       <c r="D78" s="3"/>
@@ -18886,8 +18892,8 @@
     </row>
     <row r="79" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" s="3"/>
-      <c r="B79" s="122"/>
-      <c r="C79" s="123"/>
+      <c r="B79" s="247"/>
+      <c r="C79" s="248"/>
       <c r="D79" s="3"/>
       <c r="E79" s="3"/>
       <c r="F79" s="3"/>
@@ -18896,10 +18902,10 @@
     </row>
     <row r="80" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="3"/>
-      <c r="B80" s="122" t="s">
+      <c r="B80" s="247" t="s">
         <v>217</v>
       </c>
-      <c r="C80" s="123" t="s">
+      <c r="C80" s="248" t="s">
         <v>175</v>
       </c>
       <c r="D80" s="3"/>
@@ -18910,8 +18916,8 @@
     </row>
     <row r="81" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A81" s="3"/>
-      <c r="B81" s="122"/>
-      <c r="C81" s="123"/>
+      <c r="B81" s="247"/>
+      <c r="C81" s="248"/>
       <c r="D81" s="3"/>
       <c r="E81" s="3"/>
       <c r="F81" s="3"/>
@@ -18920,10 +18926,10 @@
     </row>
     <row r="82" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A82" s="3"/>
-      <c r="B82" s="122" t="s">
+      <c r="B82" s="247" t="s">
         <v>218</v>
       </c>
-      <c r="C82" s="123" t="s">
+      <c r="C82" s="248" t="s">
         <v>179</v>
       </c>
       <c r="D82" s="3"/>
@@ -18934,8 +18940,8 @@
     </row>
     <row r="83" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A83" s="3"/>
-      <c r="B83" s="122"/>
-      <c r="C83" s="123"/>
+      <c r="B83" s="247"/>
+      <c r="C83" s="248"/>
       <c r="D83" s="3"/>
       <c r="E83" s="3"/>
       <c r="F83" s="3"/>
@@ -18944,10 +18950,10 @@
     </row>
     <row r="84" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A84" s="3"/>
-      <c r="B84" s="122" t="s">
+      <c r="B84" s="247" t="s">
         <v>219</v>
       </c>
-      <c r="C84" s="123" t="s">
+      <c r="C84" s="248" t="s">
         <v>180</v>
       </c>
       <c r="D84" s="3"/>
@@ -18958,8 +18964,8 @@
     </row>
     <row r="85" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A85" s="3"/>
-      <c r="B85" s="122"/>
-      <c r="C85" s="123"/>
+      <c r="B85" s="247"/>
+      <c r="C85" s="248"/>
       <c r="D85" s="3"/>
       <c r="E85" s="3"/>
       <c r="F85" s="3"/>
@@ -18968,10 +18974,10 @@
     </row>
     <row r="86" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="3"/>
-      <c r="B86" s="122" t="s">
+      <c r="B86" s="247" t="s">
         <v>220</v>
       </c>
-      <c r="C86" s="123" t="s">
+      <c r="C86" s="248" t="s">
         <v>176</v>
       </c>
       <c r="D86" s="3"/>
@@ -18982,8 +18988,8 @@
     </row>
     <row r="87" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A87" s="3"/>
-      <c r="B87" s="122"/>
-      <c r="C87" s="123"/>
+      <c r="B87" s="247"/>
+      <c r="C87" s="248"/>
       <c r="D87" s="3"/>
       <c r="E87" s="3"/>
       <c r="F87" s="3"/>
@@ -18992,10 +18998,10 @@
     </row>
     <row r="88" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A88" s="3"/>
-      <c r="B88" s="122" t="s">
+      <c r="B88" s="247" t="s">
         <v>226</v>
       </c>
-      <c r="C88" s="123" t="s">
+      <c r="C88" s="248" t="s">
         <v>227</v>
       </c>
       <c r="D88" s="3"/>
@@ -19006,8 +19012,8 @@
     </row>
     <row r="89" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A89" s="3"/>
-      <c r="B89" s="122"/>
-      <c r="C89" s="123"/>
+      <c r="B89" s="247"/>
+      <c r="C89" s="248"/>
       <c r="D89" s="3"/>
       <c r="E89" s="3"/>
       <c r="F89" s="3"/>
@@ -19016,10 +19022,10 @@
     </row>
     <row r="90" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A90" s="3"/>
-      <c r="B90" s="124" t="s">
+      <c r="B90" s="272" t="s">
         <v>228</v>
       </c>
-      <c r="C90" s="126" t="s">
+      <c r="C90" s="264" t="s">
         <v>229</v>
       </c>
       <c r="D90" s="3"/>
@@ -19030,8 +19036,8 @@
     </row>
     <row r="91" spans="1:8" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A91" s="3"/>
-      <c r="B91" s="125"/>
-      <c r="C91" s="127"/>
+      <c r="B91" s="273"/>
+      <c r="C91" s="274"/>
       <c r="D91" s="3"/>
       <c r="E91" s="3"/>
       <c r="F91" s="3"/>
@@ -19838,37 +19844,83 @@
     <row r="174" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <mergeCells count="132">
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:E4"/>
-    <mergeCell ref="F3:G4"/>
-    <mergeCell ref="B5:B8"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D8"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="E13:E16"/>
-    <mergeCell ref="E17:E18"/>
-    <mergeCell ref="F17:F18"/>
-    <mergeCell ref="G17:G18"/>
-    <mergeCell ref="C19:C20"/>
-    <mergeCell ref="D19:D20"/>
-    <mergeCell ref="E19:E20"/>
-    <mergeCell ref="E5:E8"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="G5:G6"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="G9:G10"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="F11:F12"/>
-    <mergeCell ref="G11:G12"/>
-    <mergeCell ref="B9:B12"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="E9:E10"/>
-    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="B88:B89"/>
+    <mergeCell ref="C88:C89"/>
+    <mergeCell ref="B90:B91"/>
+    <mergeCell ref="C90:C91"/>
+    <mergeCell ref="B80:B81"/>
+    <mergeCell ref="C80:C81"/>
+    <mergeCell ref="B82:B83"/>
+    <mergeCell ref="C82:C83"/>
+    <mergeCell ref="B84:B85"/>
+    <mergeCell ref="C84:C85"/>
+    <mergeCell ref="B86:B87"/>
+    <mergeCell ref="C86:C87"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="C72:C73"/>
+    <mergeCell ref="B76:B77"/>
+    <mergeCell ref="C76:C77"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="D60:D61"/>
+    <mergeCell ref="B64:B65"/>
+    <mergeCell ref="C64:C65"/>
+    <mergeCell ref="B66:B67"/>
+    <mergeCell ref="C66:C67"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="C68:C69"/>
+    <mergeCell ref="B56:B57"/>
+    <mergeCell ref="C56:C57"/>
+    <mergeCell ref="D56:D57"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="D58:D59"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="C60:C61"/>
+    <mergeCell ref="B70:B71"/>
+    <mergeCell ref="C70:C71"/>
+    <mergeCell ref="B52:B53"/>
+    <mergeCell ref="C52:C53"/>
+    <mergeCell ref="D52:D53"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="C54:C55"/>
+    <mergeCell ref="C44:C45"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="B46:B47"/>
+    <mergeCell ref="C46:C47"/>
+    <mergeCell ref="D46:D47"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="C48:C49"/>
+    <mergeCell ref="D48:D49"/>
+    <mergeCell ref="B50:B51"/>
+    <mergeCell ref="D54:D55"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="D40:D41"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="C42:C43"/>
+    <mergeCell ref="D42:D43"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="C50:C51"/>
+    <mergeCell ref="D50:D51"/>
+    <mergeCell ref="C30:C32"/>
+    <mergeCell ref="F30:G32"/>
+    <mergeCell ref="C33:C34"/>
+    <mergeCell ref="F33:F34"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="F25:F26"/>
+    <mergeCell ref="G25:G26"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="E27:E28"/>
+    <mergeCell ref="F27:F28"/>
+    <mergeCell ref="G27:G28"/>
+    <mergeCell ref="C38:C39"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="B25:B28"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="E25:E26"/>
     <mergeCell ref="B21:B24"/>
     <mergeCell ref="C21:C22"/>
     <mergeCell ref="D21:D22"/>
@@ -19893,83 +19945,37 @@
     <mergeCell ref="D17:D18"/>
     <mergeCell ref="B13:B16"/>
     <mergeCell ref="C13:C14"/>
-    <mergeCell ref="C30:C32"/>
-    <mergeCell ref="F30:G32"/>
-    <mergeCell ref="C33:C34"/>
-    <mergeCell ref="F33:F34"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="F25:F26"/>
-    <mergeCell ref="G25:G26"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="D27:D28"/>
-    <mergeCell ref="E27:E28"/>
-    <mergeCell ref="F27:F28"/>
-    <mergeCell ref="G27:G28"/>
-    <mergeCell ref="C38:C39"/>
-    <mergeCell ref="D38:D39"/>
-    <mergeCell ref="B25:B28"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="D25:D26"/>
-    <mergeCell ref="E25:E26"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="D40:D41"/>
-    <mergeCell ref="B42:B43"/>
-    <mergeCell ref="C42:C43"/>
-    <mergeCell ref="D42:D43"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="C50:C51"/>
-    <mergeCell ref="D50:D51"/>
-    <mergeCell ref="B52:B53"/>
-    <mergeCell ref="C52:C53"/>
-    <mergeCell ref="D52:D53"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="C54:C55"/>
-    <mergeCell ref="C44:C45"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="B46:B47"/>
-    <mergeCell ref="C46:C47"/>
-    <mergeCell ref="D46:D47"/>
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="C48:C49"/>
-    <mergeCell ref="D48:D49"/>
-    <mergeCell ref="B50:B51"/>
-    <mergeCell ref="D54:D55"/>
-    <mergeCell ref="B56:B57"/>
-    <mergeCell ref="C56:C57"/>
-    <mergeCell ref="D56:D57"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="C58:C59"/>
-    <mergeCell ref="D58:D59"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="C60:C61"/>
-    <mergeCell ref="B70:B71"/>
-    <mergeCell ref="C70:C71"/>
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="C72:C73"/>
-    <mergeCell ref="B76:B77"/>
-    <mergeCell ref="C76:C77"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="D60:D61"/>
-    <mergeCell ref="B64:B65"/>
-    <mergeCell ref="C64:C65"/>
-    <mergeCell ref="B66:B67"/>
-    <mergeCell ref="C66:C67"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="C68:C69"/>
-    <mergeCell ref="B88:B89"/>
-    <mergeCell ref="C88:C89"/>
-    <mergeCell ref="B90:B91"/>
-    <mergeCell ref="C90:C91"/>
-    <mergeCell ref="B80:B81"/>
-    <mergeCell ref="C80:C81"/>
-    <mergeCell ref="B82:B83"/>
-    <mergeCell ref="C82:C83"/>
-    <mergeCell ref="B84:B85"/>
-    <mergeCell ref="C84:C85"/>
-    <mergeCell ref="B86:B87"/>
-    <mergeCell ref="C86:C87"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="E19:E20"/>
+    <mergeCell ref="E5:E8"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="G9:G10"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:E4"/>
+    <mergeCell ref="F3:G4"/>
+    <mergeCell ref="B5:B8"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D8"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="E13:E16"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="F17:F18"/>
+    <mergeCell ref="G17:G18"/>
+    <mergeCell ref="B9:B12"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
